--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.69972041667</v>
+        <v>46065.86638708333</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55529023148</v>
+        <v>46092.72195689815</v>
       </c>
       <c r="D4" s="5">
-        <v>46133.603651701385</v>
+        <v>46133.77031836806</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.69972087963</v>
+        <v>46065.866387546295</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.555256886575</v>
+        <v>46092.72192355324</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55529099537</v>
+        <v>46092.72195766204</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1612,13 +1612,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.69972138889</v>
+        <v>46065.866388055554</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55525744213</v>
+        <v>46092.721924108795</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55529188657</v>
+        <v>46092.721958553244</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1677,13 +1677,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.69972192129</v>
+        <v>46065.866388587965</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55525792824</v>
+        <v>46092.72192459491</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.555291296296</v>
+        <v>46092.72195796296</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1742,13 +1742,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.69972236111</v>
+        <v>46065.86638902778</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55525841435</v>
+        <v>46092.721925081016</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.6233396412</v>
+        <v>46100.79000630787</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1807,13 +1807,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.69972283565</v>
+        <v>46065.86638950232</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55525921297</v>
+        <v>46092.721925879625</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55529192129</v>
+        <v>46092.721958587965</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1872,11 +1872,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.69972333334</v>
+        <v>46065.866389999996</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.3876528588</v>
+        <v>46097.55431952546</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1919,13 +1919,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.699723680555</v>
+        <v>46065.86639034722</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.38764217593</v>
+        <v>46097.55430884259</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.38766100694</v>
+        <v>46097.55432767361</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1984,11 +1984,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.69972405092</v>
+        <v>46065.866390717594</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46137.026501875</v>
+        <v>46137.193168541664</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2047,13 +2047,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.69972444444</v>
+        <v>46065.86639111111</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.35589099537</v>
+        <v>46114.522557662036</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.35590498842</v>
+        <v>46114.52257165509</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2100,13 +2100,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.6997184375</v>
+        <v>46065.866385104164</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.38671878472</v>
+        <v>46097.55338545139</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.386736678236</v>
+        <v>46097.55340334491</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2165,13 +2165,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.69972413195</v>
+        <v>46065.86639079861</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.557669560185</v>
+        <v>46107.72433622685</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.55768900463</v>
+        <v>46107.72435567129</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2230,13 +2230,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.6997255787</v>
+        <v>46065.86639224537</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.55771945602</v>
+        <v>46107.72438612269</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.55773701389</v>
+        <v>46107.72440368056</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2295,13 +2295,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.69972638889</v>
+        <v>46065.866393055556</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.35587568287</v>
+        <v>46114.522542349536</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.35589112269</v>
+        <v>46114.52255778935</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2360,13 +2360,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.69972674768</v>
+        <v>46065.866393414355</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.35593553241</v>
+        <v>46114.522602199075</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.355957997686</v>
+        <v>46114.52262466435</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2413,13 +2413,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.69972708334</v>
+        <v>46065.866393749995</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.386754328705</v>
+        <v>46097.55342099537</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.387491747686</v>
+        <v>46097.55415841435</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -2478,13 +2478,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.69972747685</v>
+        <v>46065.86639414352</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.38667216436</v>
+        <v>46097.553338831014</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.55769261574</v>
+        <v>46107.72435928241</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2543,13 +2543,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.69972790509</v>
+        <v>46065.866394571756</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.38769659722</v>
+        <v>46097.55436326389</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.38771902778</v>
+        <v>46097.55438569444</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2608,13 +2608,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.69972824074</v>
+        <v>46065.86639490741</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.393608240745</v>
+        <v>46113.5602749074</v>
       </c>
       <c r="D22" s="5">
-        <v>46113.39361032407</v>
+        <v>46113.56027699074</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2673,13 +2673,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.699718703705</v>
+        <v>46065.86638537037</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.35591884259</v>
+        <v>46114.52258550926</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.35640158565</v>
+        <v>46114.52306825231</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2738,13 +2738,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.6997191088</v>
+        <v>46065.86638577546</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.55799318287</v>
+        <v>46107.72465984954</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.55801064815</v>
+        <v>46107.724677314814</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2803,11 +2803,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.69971940972</v>
+        <v>46065.86638607639</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46174.486404282405</v>
+        <v>46174.653070949076</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2852,13 +2852,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.69971969907</v>
+        <v>46065.86638636574</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.709235937495</v>
+        <v>46155.875902604166</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.70925018519</v>
+        <v>46155.87591685185</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2917,13 +2917,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.69972001157</v>
+        <v>46065.866386678244</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.38682175926</v>
+        <v>46097.553488425925</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.3868233449</v>
+        <v>46097.553490011574</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2978,13 +2978,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.69972030092</v>
+        <v>46065.866386967595</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.709218055556</v>
+        <v>46155.87588472222</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.70921930556</v>
+        <v>46155.87588597222</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3039,13 +3039,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.69972059027</v>
+        <v>46065.866387256945</v>
       </c>
       <c r="C29" s="8">
-        <v>46122.47842777778</v>
+        <v>46122.645094444444</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.01609658565</v>
+        <v>46128.18276325232</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3104,13 +3104,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.699720902776</v>
+        <v>46065.86638756945</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.38788888889</v>
+        <v>46097.55455555556</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.3878903588</v>
+        <v>46097.55455702546</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3165,13 +3165,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.6997212037</v>
+        <v>46065.86638787037</v>
       </c>
       <c r="C31" s="8">
-        <v>46122.47841251157</v>
+        <v>46122.64507917824</v>
       </c>
       <c r="D31" s="8">
-        <v>46122.47841388889</v>
+        <v>46122.64508055555</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3226,13 +3226,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.69972150463</v>
+        <v>46065.8663881713</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.72490068287</v>
+        <v>46155.891567349536</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.724920231485</v>
+        <v>46155.89158689815</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3291,13 +3291,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.699717696756</v>
+        <v>46065.86638436343</v>
       </c>
       <c r="C33" s="8">
-        <v>46139.627010729164</v>
+        <v>46139.793677395835</v>
       </c>
       <c r="D33" s="8">
-        <v>46139.628311423614</v>
+        <v>46139.79497809028</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3352,13 +3352,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46065.699718090276</v>
+        <v>46065.86638475694</v>
       </c>
       <c r="C34" s="5">
-        <v>46155.724885891206</v>
+        <v>46155.89155255787</v>
       </c>
       <c r="D34" s="5">
-        <v>46155.724887372686</v>
+        <v>46155.89155403935</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3413,13 +3413,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46065.6997183912</v>
+        <v>46065.866385057874</v>
       </c>
       <c r="C35" s="8">
-        <v>46174.48638369213</v>
+        <v>46174.6530503588</v>
       </c>
       <c r="D35" s="8">
-        <v>46174.486394837964</v>
+        <v>46174.65306150463</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3478,13 +3478,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46065.69971868055</v>
+        <v>46065.866385347224</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.38739834491</v>
+        <v>46097.55406501157</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.67490680555</v>
+        <v>46169.84157347222</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3539,13 +3539,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46065.6997189699</v>
+        <v>46065.866385636575</v>
       </c>
       <c r="C37" s="8">
-        <v>46174.48632372685</v>
+        <v>46174.652990393515</v>
       </c>
       <c r="D37" s="8">
-        <v>46174.48632570602</v>
+        <v>46174.652992372685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3600,13 +3600,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.69971927084</v>
+        <v>46065.8663859375</v>
       </c>
       <c r="C38" s="5">
-        <v>46174.48636920139</v>
+        <v>46174.653035868054</v>
       </c>
       <c r="D38" s="5">
-        <v>46174.48637082176</v>
+        <v>46174.653037488424</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3661,13 +3661,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.69971954861</v>
+        <v>46065.866386215275</v>
       </c>
       <c r="C39" s="8">
-        <v>46118.6700700463</v>
+        <v>46118.83673671296</v>
       </c>
       <c r="D39" s="8">
-        <v>46118.670083125</v>
+        <v>46118.83674979166</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3726,13 +3726,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.699719826385</v>
+        <v>46065.86638649306</v>
       </c>
       <c r="C40" s="5">
-        <v>46118.669840532406</v>
+        <v>46118.83650719907</v>
       </c>
       <c r="D40" s="5">
-        <v>46118.66984232639</v>
+        <v>46118.83650899306</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3787,13 +3787,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.69972010417</v>
+        <v>46065.86638677084</v>
       </c>
       <c r="C41" s="8">
-        <v>46118.670056840274</v>
+        <v>46118.836723506945</v>
       </c>
       <c r="D41" s="8">
-        <v>46118.67005832176</v>
+        <v>46118.836724988425</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3848,13 +3848,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46065.69972038195</v>
+        <v>46065.86638704861</v>
       </c>
       <c r="C42" s="5">
-        <v>46118.672245740745</v>
+        <v>46118.83891240741</v>
       </c>
       <c r="D42" s="5">
-        <v>46133.0292046875</v>
+        <v>46133.19587135417</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3913,13 +3913,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.69972002315</v>
+        <v>46065.86638668981</v>
       </c>
       <c r="C43" s="8">
-        <v>46118.672182152775</v>
+        <v>46118.83884881945</v>
       </c>
       <c r="D43" s="8">
-        <v>46118.67218368055</v>
+        <v>46118.83885034722</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3974,13 +3974,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46065.69972040509</v>
+        <v>46065.86638707176</v>
       </c>
       <c r="C44" s="5">
-        <v>46118.67223113426</v>
+        <v>46118.838897800924</v>
       </c>
       <c r="D44" s="5">
-        <v>46118.67223251157</v>
+        <v>46118.83889917824</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4035,11 +4035,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46065.69972070602</v>
+        <v>46065.866387372684</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46107.55921043982</v>
+        <v>46107.72587710648</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4084,13 +4084,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.57748881944</v>
+        <v>46070.744155486114</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.559126168984</v>
+        <v>46107.72579283565</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.55914474537</v>
+        <v>46107.725811412034</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4149,13 +4149,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.6997209838</v>
+        <v>46065.86638765046</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.55918997685</v>
+        <v>46107.72585664352</v>
       </c>
       <c r="D47" s="8">
-        <v>46174.48638537037</v>
+        <v>46174.653052037036</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4214,13 +4214,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46090.582982002314</v>
+        <v>46090.74964866898</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.55926100694</v>
+        <v>46107.725927673615</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.559284166666</v>
+        <v>46107.72595083334</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4279,11 +4279,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46090.58315702547</v>
+        <v>46090.74982369213</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46170.01697292824</v>
+        <v>46170.18363959491</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4342,13 +4342,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.69972127315</v>
+        <v>46065.866387939815</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.46892471064</v>
+        <v>46127.635591377315</v>
       </c>
       <c r="D50" s="5">
-        <v>46127.468940983796</v>
+        <v>46127.63560765046</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4395,13 +4395,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.699721550925</v>
+        <v>46065.86638821759</v>
       </c>
       <c r="C51" s="8">
-        <v>46122.476305069446</v>
+        <v>46122.64297173611</v>
       </c>
       <c r="D51" s="8">
-        <v>46122.47632221065</v>
+        <v>46122.64298887731</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>185</v>
@@ -4460,13 +4460,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.6997218287</v>
+        <v>46065.86638849537</v>
       </c>
       <c r="C52" s="5">
-        <v>46127.4689035301</v>
+        <v>46127.635570196755</v>
       </c>
       <c r="D52" s="5">
-        <v>46127.4689250463</v>
+        <v>46127.63559171296</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4525,13 +4525,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.69972209491</v>
+        <v>46065.86638876157</v>
       </c>
       <c r="C53" s="8">
-        <v>46167.43130704861</v>
+        <v>46167.59797371528</v>
       </c>
       <c r="D53" s="8">
-        <v>46167.43131892361</v>
+        <v>46167.59798559028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4578,13 +4578,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.69972234954</v>
+        <v>46065.8663890162</v>
       </c>
       <c r="C54" s="5">
-        <v>46167.37834422453</v>
+        <v>46167.545010891205</v>
       </c>
       <c r="D54" s="5">
-        <v>46167.378359803246</v>
+        <v>46167.5450264699</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4643,13 +4643,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.69972265046</v>
+        <v>46065.86638931713</v>
       </c>
       <c r="C55" s="8">
-        <v>46167.43123873843</v>
+        <v>46167.59790540509</v>
       </c>
       <c r="D55" s="8">
-        <v>46167.431259652774</v>
+        <v>46167.597926319446</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4708,13 +4708,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.699718206015</v>
+        <v>46065.86638487269</v>
       </c>
       <c r="C56" s="5">
-        <v>46167.43129097222</v>
+        <v>46167.59795763889</v>
       </c>
       <c r="D56" s="5">
-        <v>46167.43130710648</v>
+        <v>46167.59797377315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4773,11 +4773,11 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.69971862268</v>
+        <v>46065.86638528935</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46122.47856425926</v>
+        <v>46122.645230925926</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4820,11 +4820,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.69971893518</v>
+        <v>46065.866385601854</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46155.70922787037</v>
+        <v>46155.875894537035</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4883,11 +4883,11 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.699719236116</v>
+        <v>46065.86638590277</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46155.72490246528</v>
+        <v>46155.89156913194</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4946,11 +4946,11 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.699719571756</v>
+        <v>46065.86638623843</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46174.48634378472</v>
+        <v>46174.65301045139</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5009,11 +5009,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.69971987269</v>
+        <v>46065.86638653935</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46130.00833434028</v>
+        <v>46130.175001006945</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5072,13 +5072,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.69972016204</v>
+        <v>46065.866386828704</v>
       </c>
       <c r="C62" s="5">
-        <v>46122.478558622686</v>
+        <v>46122.64522528935</v>
       </c>
       <c r="D62" s="5">
-        <v>46143.00568688658</v>
+        <v>46143.17235355324</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -5137,11 +5137,11 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.69972047454</v>
+        <v>46065.8663871412</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46090.588649178244</v>
+        <v>46090.75531584491</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5184,11 +5184,11 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.69972077546</v>
+        <v>46065.86638744213</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46167.4313081713</v>
+        <v>46167.59797483796</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5247,11 +5247,11 @@
         <v>232</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.699721111116</v>
+        <v>46065.86638777777</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46168.00925690972</v>
+        <v>46168.17592357639</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5310,11 +5310,11 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.69971853009</v>
+        <v>46065.86638519676</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46151.03269211805</v>
+        <v>46151.199358784725</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5373,11 +5373,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.69971893518</v>
+        <v>46065.866385601854</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46155.009008761575</v>
+        <v>46155.17567542824</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5436,11 +5436,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.69971929398</v>
+        <v>46065.866385960646</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46148.01867075231</v>
+        <v>46148.18533741898</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5499,11 +5499,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.69971959491</v>
+        <v>46065.86638626158</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46169.02761638889</v>
+        <v>46169.194283055556</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5560,11 +5560,11 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.699719895834</v>
+        <v>46065.8663865625</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46171.038164756945</v>
+        <v>46171.204831423616</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5621,11 +5621,11 @@
         <v>251</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.69972019676</v>
+        <v>46065.866386863425</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.58864962963</v>
+        <v>46090.7553162963</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>252</v>
@@ -5668,11 +5668,11 @@
         <v>254</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.69972052083</v>
+        <v>46065.8663871875</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46172.01269791667</v>
+        <v>46172.17936458334</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>
@@ -5729,11 +5729,11 @@
         <v>257</v>
       </c>
       <c r="B73" s="8">
-        <v>46065.69972081018</v>
+        <v>46065.86638747685</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46177.03259962963</v>
+        <v>46177.199266296295</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>258</v>
@@ -5792,11 +5792,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46065.69972109953</v>
+        <v>46065.866387766204</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46178.036477013884</v>
+        <v>46178.203143680556</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>262</v>
@@ -5853,11 +5853,11 @@
         <v>266</v>
       </c>
       <c r="B75" s="8">
-        <v>46065.69972150463</v>
+        <v>46065.8663881713</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46179.018358518515</v>
+        <v>46179.18502518519</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>267</v>
@@ -5914,11 +5914,11 @@
         <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46065.69971767361</v>
+        <v>46065.866384340276</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.58864890046</v>
+        <v>46090.755315567134</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>270</v>
@@ -5961,11 +5961,11 @@
         <v>272</v>
       </c>
       <c r="B77" s="8">
-        <v>46065.69971847222</v>
+        <v>46065.866385138885</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46182.03446342592</v>
+        <v>46182.201130092595</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -6024,11 +6024,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46065.699718749995</v>
+        <v>46065.866385416666</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46182.03446335648</v>
+        <v>46182.20113002315</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6087,11 +6087,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.583335821764</v>
+        <v>46090.75000248842</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.58969721065</v>
+        <v>46090.75636387731</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6140,11 +6140,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.58361796296</v>
+        <v>46090.75028462963</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46182.03446336805</v>
+        <v>46182.20113003472</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6203,11 +6203,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.58391190972</v>
+        <v>46090.75057857639</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.697063217594</v>
+        <v>46090.86372988426</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -5965,7 +5965,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46182.201130092595</v>
+        <v>46189.12545385417</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46182.20113002315</v>
+        <v>46189.12536952546</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46182.20113003472</v>
+        <v>46189.25031092593</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -5965,7 +5965,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46189.12545385417</v>
+        <v>46190.20534189815</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -6015,8 +6015,8 @@
       <c r="T77" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="U77" s="12" t="s">
-        <v>157</v>
+      <c r="U77" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46189.12536952546</v>
+        <v>46190.205348206015</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6078,8 +6078,8 @@
       <c r="T78" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="U78" s="12" t="s">
-        <v>157</v>
+      <c r="U78" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46189.25031092593</v>
+        <v>46190.205342534726</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6194,8 +6194,8 @@
       <c r="T80" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="U80" s="12" t="s">
-        <v>157</v>
+      <c r="U80" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -6207,7 +6207,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46090.86372988426</v>
+        <v>46191.20339054398</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>
@@ -6257,8 +6257,8 @@
       <c r="T81" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="U81" s="10" t="s">
-        <v>109</v>
+      <c r="U81" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46167.59797483796</v>
+        <v>46195.57220603009</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -5141,7 +5141,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46090.75531584491</v>
+        <v>46195.86651877315</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5186,9 +5186,11 @@
       <c r="B64" s="5">
         <v>46065.86638744213</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46195.866510844906</v>
+      </c>
       <c r="D64" s="5">
-        <v>46195.57220603009</v>
+        <v>46195.86652894676</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5233,10 +5235,10 @@
         <v>46147</v>
       </c>
       <c r="S64" s="6">
-        <v>0</v>
-      </c>
-      <c r="T64" s="12" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="T64" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U64" s="11" t="s">
         <v>32</v>
@@ -5251,7 +5253,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46168.17592357639</v>
+        <v>46195.86733721065</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5314,7 +5316,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46151.199358784725</v>
+        <v>46195.866517546296</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5377,7 +5379,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46155.17567542824</v>
+        <v>46195.86651821759</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -5253,7 +5253,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46195.86733721065</v>
+        <v>46196.87454020833</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -5141,7 +5141,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.86651877315</v>
+        <v>46197.50378652778</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5251,9 +5251,11 @@
       <c r="B65" s="8">
         <v>46065.86638777777</v>
       </c>
-      <c r="C65" s="9"/>
+      <c r="C65" s="8">
+        <v>46197.50371587963</v>
+      </c>
       <c r="D65" s="8">
-        <v>46196.87454020833</v>
+        <v>46197.50373502314</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5298,10 +5300,10 @@
         <v>46167</v>
       </c>
       <c r="S65" s="9">
-        <v>0</v>
-      </c>
-      <c r="T65" s="11" t="s">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="T65" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U65" s="11" t="s">
         <v>32</v>
@@ -5314,9 +5316,11 @@
       <c r="B66" s="5">
         <v>46065.86638519676</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46197.50377947917</v>
+      </c>
       <c r="D66" s="5">
-        <v>46195.866517546296</v>
+        <v>46197.50400935185</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5361,10 +5365,10 @@
         <v>46150</v>
       </c>
       <c r="S66" s="6">
-        <v>0</v>
-      </c>
-      <c r="T66" s="11" t="s">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="T66" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>32</v>
@@ -5379,7 +5383,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46195.86651821759</v>
+        <v>46197.50378688658</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5505,7 +5509,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46169.194283055556</v>
+        <v>46197.50378604166</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="287">
   <si>
     <t xml:space="preserve">50001497 - XEMORTIZ IMMSA STA. BBR  </t>
   </si>
@@ -5139,9 +5139,11 @@
       <c r="B63" s="8">
         <v>46065.8663871412</v>
       </c>
-      <c r="C63" s="9"/>
+      <c r="C63" s="8">
+        <v>46197.59918284722</v>
+      </c>
       <c r="D63" s="8">
-        <v>46197.50378652778</v>
+        <v>46197.59920001157</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5175,8 +5177,12 @@
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
-      <c r="S63" s="9"/>
-      <c r="T63" s="9"/>
+      <c r="S63" s="9">
+        <v>1</v>
+      </c>
+      <c r="T63" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="U63" s="9"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -5143,7 +5143,7 @@
         <v>46197.59918284722</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.59920001157</v>
+        <v>46197.60713444444</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5450,9 +5450,11 @@
       <c r="B68" s="5">
         <v>46065.866385960646</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46197.607128483796</v>
+      </c>
       <c r="D68" s="5">
-        <v>46148.18533741898</v>
+        <v>46197.60726340278</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5497,10 +5499,10 @@
         <v>46147</v>
       </c>
       <c r="S68" s="6">
-        <v>0</v>
-      </c>
-      <c r="T68" s="12" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="T68" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U68" s="11" t="s">
         <v>32</v>
@@ -5515,7 +5517,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.50378604166</v>
+        <v>46197.60713396991</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.86638708333</v>
+        <v>46065.69972041667</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72195689815</v>
+        <v>46092.55529023148</v>
       </c>
       <c r="D4" s="5">
-        <v>46133.77031836806</v>
+        <v>46133.603651701385</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.866387546295</v>
+        <v>46065.69972087963</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72192355324</v>
+        <v>46092.555256886575</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.72195766204</v>
+        <v>46092.55529099537</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1612,13 +1612,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.866388055554</v>
+        <v>46065.69972138889</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.721924108795</v>
+        <v>46092.55525744213</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.721958553244</v>
+        <v>46092.55529188657</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1677,13 +1677,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.866388587965</v>
+        <v>46065.69972192129</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.72192459491</v>
+        <v>46092.55525792824</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72195796296</v>
+        <v>46092.555291296296</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1742,13 +1742,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.86638902778</v>
+        <v>46065.69972236111</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.721925081016</v>
+        <v>46092.55525841435</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.79000630787</v>
+        <v>46100.6233396412</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1807,13 +1807,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.86638950232</v>
+        <v>46065.69972283565</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.721925879625</v>
+        <v>46092.55525921297</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.721958587965</v>
+        <v>46092.55529192129</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1872,11 +1872,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.866389999996</v>
+        <v>46065.69972333334</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.55431952546</v>
+        <v>46097.3876528588</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1919,13 +1919,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.86639034722</v>
+        <v>46065.699723680555</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.55430884259</v>
+        <v>46097.38764217593</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.55432767361</v>
+        <v>46097.38766100694</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1984,11 +1984,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.866390717594</v>
+        <v>46065.69972405092</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46137.193168541664</v>
+        <v>46137.026501875</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2047,13 +2047,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.86639111111</v>
+        <v>46065.69972444444</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.522557662036</v>
+        <v>46114.35589099537</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.52257165509</v>
+        <v>46114.35590498842</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2100,13 +2100,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.866385104164</v>
+        <v>46065.6997184375</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.55338545139</v>
+        <v>46097.38671878472</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.55340334491</v>
+        <v>46097.386736678236</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2165,13 +2165,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.86639079861</v>
+        <v>46065.69972413195</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.72433622685</v>
+        <v>46107.557669560185</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.72435567129</v>
+        <v>46107.55768900463</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2230,13 +2230,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.86639224537</v>
+        <v>46065.6997255787</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.72438612269</v>
+        <v>46107.55771945602</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.72440368056</v>
+        <v>46107.55773701389</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2295,13 +2295,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.866393055556</v>
+        <v>46065.69972638889</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.522542349536</v>
+        <v>46114.35587568287</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.52255778935</v>
+        <v>46114.35589112269</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2360,13 +2360,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.866393414355</v>
+        <v>46065.69972674768</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.522602199075</v>
+        <v>46114.35593553241</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.52262466435</v>
+        <v>46114.355957997686</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2413,13 +2413,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.866393749995</v>
+        <v>46065.69972708334</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.55342099537</v>
+        <v>46097.386754328705</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.55415841435</v>
+        <v>46097.387491747686</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -2478,13 +2478,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.86639414352</v>
+        <v>46065.69972747685</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.553338831014</v>
+        <v>46097.38667216436</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.72435928241</v>
+        <v>46107.55769261574</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2543,13 +2543,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.866394571756</v>
+        <v>46065.69972790509</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.55436326389</v>
+        <v>46097.38769659722</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.55438569444</v>
+        <v>46097.38771902778</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2608,13 +2608,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.86639490741</v>
+        <v>46065.69972824074</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.5602749074</v>
+        <v>46113.393608240745</v>
       </c>
       <c r="D22" s="5">
-        <v>46113.56027699074</v>
+        <v>46113.39361032407</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2673,13 +2673,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.86638537037</v>
+        <v>46065.699718703705</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.52258550926</v>
+        <v>46114.35591884259</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.52306825231</v>
+        <v>46114.35640158565</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2738,13 +2738,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.86638577546</v>
+        <v>46065.6997191088</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.72465984954</v>
+        <v>46107.55799318287</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.724677314814</v>
+        <v>46107.55801064815</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2803,11 +2803,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.86638607639</v>
+        <v>46065.69971940972</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46174.653070949076</v>
+        <v>46174.486404282405</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2852,13 +2852,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.86638636574</v>
+        <v>46065.69971969907</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.875902604166</v>
+        <v>46155.709235937495</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.87591685185</v>
+        <v>46155.70925018519</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2917,13 +2917,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.866386678244</v>
+        <v>46065.69972001157</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.553488425925</v>
+        <v>46097.38682175926</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.553490011574</v>
+        <v>46097.3868233449</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2978,13 +2978,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.866386967595</v>
+        <v>46065.69972030092</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.87588472222</v>
+        <v>46155.709218055556</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.87588597222</v>
+        <v>46155.70921930556</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3039,13 +3039,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.866387256945</v>
+        <v>46065.69972059027</v>
       </c>
       <c r="C29" s="8">
-        <v>46122.645094444444</v>
+        <v>46122.47842777778</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.18276325232</v>
+        <v>46128.01609658565</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3104,13 +3104,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.86638756945</v>
+        <v>46065.699720902776</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.55455555556</v>
+        <v>46097.38788888889</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.55455702546</v>
+        <v>46097.3878903588</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3165,13 +3165,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.86638787037</v>
+        <v>46065.6997212037</v>
       </c>
       <c r="C31" s="8">
-        <v>46122.64507917824</v>
+        <v>46122.47841251157</v>
       </c>
       <c r="D31" s="8">
-        <v>46122.64508055555</v>
+        <v>46122.47841388889</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3226,13 +3226,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.8663881713</v>
+        <v>46065.69972150463</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.891567349536</v>
+        <v>46155.72490068287</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.89158689815</v>
+        <v>46155.724920231485</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3291,13 +3291,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.86638436343</v>
+        <v>46065.699717696756</v>
       </c>
       <c r="C33" s="8">
-        <v>46139.793677395835</v>
+        <v>46139.627010729164</v>
       </c>
       <c r="D33" s="8">
-        <v>46139.79497809028</v>
+        <v>46139.628311423614</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3352,13 +3352,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46065.86638475694</v>
+        <v>46065.699718090276</v>
       </c>
       <c r="C34" s="5">
-        <v>46155.89155255787</v>
+        <v>46155.724885891206</v>
       </c>
       <c r="D34" s="5">
-        <v>46155.89155403935</v>
+        <v>46155.724887372686</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3413,13 +3413,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46065.866385057874</v>
+        <v>46065.6997183912</v>
       </c>
       <c r="C35" s="8">
-        <v>46174.6530503588</v>
+        <v>46174.48638369213</v>
       </c>
       <c r="D35" s="8">
-        <v>46174.65306150463</v>
+        <v>46174.486394837964</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3478,13 +3478,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46065.866385347224</v>
+        <v>46065.69971868055</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.55406501157</v>
+        <v>46097.38739834491</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.84157347222</v>
+        <v>46169.67490680555</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3539,13 +3539,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46065.866385636575</v>
+        <v>46065.6997189699</v>
       </c>
       <c r="C37" s="8">
-        <v>46174.652990393515</v>
+        <v>46174.48632372685</v>
       </c>
       <c r="D37" s="8">
-        <v>46174.652992372685</v>
+        <v>46174.48632570602</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3600,13 +3600,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.8663859375</v>
+        <v>46065.69971927084</v>
       </c>
       <c r="C38" s="5">
-        <v>46174.653035868054</v>
+        <v>46174.48636920139</v>
       </c>
       <c r="D38" s="5">
-        <v>46174.653037488424</v>
+        <v>46174.48637082176</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3661,13 +3661,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.866386215275</v>
+        <v>46065.69971954861</v>
       </c>
       <c r="C39" s="8">
-        <v>46118.83673671296</v>
+        <v>46118.6700700463</v>
       </c>
       <c r="D39" s="8">
-        <v>46118.83674979166</v>
+        <v>46118.670083125</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3726,13 +3726,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.86638649306</v>
+        <v>46065.699719826385</v>
       </c>
       <c r="C40" s="5">
-        <v>46118.83650719907</v>
+        <v>46118.669840532406</v>
       </c>
       <c r="D40" s="5">
-        <v>46118.83650899306</v>
+        <v>46118.66984232639</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3787,13 +3787,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.86638677084</v>
+        <v>46065.69972010417</v>
       </c>
       <c r="C41" s="8">
-        <v>46118.836723506945</v>
+        <v>46118.670056840274</v>
       </c>
       <c r="D41" s="8">
-        <v>46118.836724988425</v>
+        <v>46118.67005832176</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3848,13 +3848,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46065.86638704861</v>
+        <v>46065.69972038195</v>
       </c>
       <c r="C42" s="5">
-        <v>46118.83891240741</v>
+        <v>46118.672245740745</v>
       </c>
       <c r="D42" s="5">
-        <v>46133.19587135417</v>
+        <v>46133.0292046875</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3913,13 +3913,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.86638668981</v>
+        <v>46065.69972002315</v>
       </c>
       <c r="C43" s="8">
-        <v>46118.83884881945</v>
+        <v>46118.672182152775</v>
       </c>
       <c r="D43" s="8">
-        <v>46118.83885034722</v>
+        <v>46118.67218368055</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3974,13 +3974,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46065.86638707176</v>
+        <v>46065.69972040509</v>
       </c>
       <c r="C44" s="5">
-        <v>46118.838897800924</v>
+        <v>46118.67223113426</v>
       </c>
       <c r="D44" s="5">
-        <v>46118.83889917824</v>
+        <v>46118.67223251157</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4035,11 +4035,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46065.866387372684</v>
+        <v>46065.69972070602</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46107.72587710648</v>
+        <v>46107.55921043982</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4084,13 +4084,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.744155486114</v>
+        <v>46070.57748881944</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.72579283565</v>
+        <v>46107.559126168984</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.725811412034</v>
+        <v>46107.55914474537</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4149,13 +4149,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.86638765046</v>
+        <v>46065.6997209838</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.72585664352</v>
+        <v>46107.55918997685</v>
       </c>
       <c r="D47" s="8">
-        <v>46174.653052037036</v>
+        <v>46174.48638537037</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4214,13 +4214,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46090.74964866898</v>
+        <v>46090.582982002314</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.725927673615</v>
+        <v>46107.55926100694</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.72595083334</v>
+        <v>46107.559284166666</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4279,11 +4279,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46090.74982369213</v>
+        <v>46090.58315702547</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46170.18363959491</v>
+        <v>46170.01697292824</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4342,13 +4342,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.866387939815</v>
+        <v>46065.69972127315</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.635591377315</v>
+        <v>46127.46892471064</v>
       </c>
       <c r="D50" s="5">
-        <v>46127.63560765046</v>
+        <v>46127.468940983796</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4395,13 +4395,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.86638821759</v>
+        <v>46065.699721550925</v>
       </c>
       <c r="C51" s="8">
-        <v>46122.64297173611</v>
+        <v>46122.476305069446</v>
       </c>
       <c r="D51" s="8">
-        <v>46122.64298887731</v>
+        <v>46122.47632221065</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>185</v>
@@ -4460,13 +4460,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.86638849537</v>
+        <v>46065.6997218287</v>
       </c>
       <c r="C52" s="5">
-        <v>46127.635570196755</v>
+        <v>46127.4689035301</v>
       </c>
       <c r="D52" s="5">
-        <v>46127.63559171296</v>
+        <v>46127.4689250463</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4525,13 +4525,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.86638876157</v>
+        <v>46065.69972209491</v>
       </c>
       <c r="C53" s="8">
-        <v>46167.59797371528</v>
+        <v>46167.43130704861</v>
       </c>
       <c r="D53" s="8">
-        <v>46167.59798559028</v>
+        <v>46167.43131892361</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4578,13 +4578,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.8663890162</v>
+        <v>46065.69972234954</v>
       </c>
       <c r="C54" s="5">
-        <v>46167.545010891205</v>
+        <v>46167.37834422453</v>
       </c>
       <c r="D54" s="5">
-        <v>46167.5450264699</v>
+        <v>46167.378359803246</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4643,13 +4643,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.86638931713</v>
+        <v>46065.69972265046</v>
       </c>
       <c r="C55" s="8">
-        <v>46167.59790540509</v>
+        <v>46167.43123873843</v>
       </c>
       <c r="D55" s="8">
-        <v>46167.597926319446</v>
+        <v>46167.431259652774</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4708,13 +4708,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.86638487269</v>
+        <v>46065.699718206015</v>
       </c>
       <c r="C56" s="5">
-        <v>46167.59795763889</v>
+        <v>46167.43129097222</v>
       </c>
       <c r="D56" s="5">
-        <v>46167.59797377315</v>
+        <v>46167.43130710648</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4773,11 +4773,11 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.86638528935</v>
+        <v>46065.69971862268</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46122.645230925926</v>
+        <v>46122.47856425926</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4820,11 +4820,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.866385601854</v>
+        <v>46065.69971893518</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46155.875894537035</v>
+        <v>46155.70922787037</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4883,11 +4883,11 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.86638590277</v>
+        <v>46065.699719236116</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46155.89156913194</v>
+        <v>46155.72490246528</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4946,11 +4946,11 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.86638623843</v>
+        <v>46065.699719571756</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46174.65301045139</v>
+        <v>46174.48634378472</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5009,11 +5009,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.86638653935</v>
+        <v>46065.69971987269</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46130.175001006945</v>
+        <v>46130.00833434028</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5072,13 +5072,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.866386828704</v>
+        <v>46065.69972016204</v>
       </c>
       <c r="C62" s="5">
-        <v>46122.64522528935</v>
+        <v>46122.478558622686</v>
       </c>
       <c r="D62" s="5">
-        <v>46143.17235355324</v>
+        <v>46143.00568688658</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -5137,13 +5137,13 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.8663871412</v>
+        <v>46065.69972047454</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.59918284722</v>
+        <v>46197.43251618056</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.60713444444</v>
+        <v>46197.44046777778</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5190,13 +5190,13 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.86638744213</v>
+        <v>46065.69972077546</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.866510844906</v>
+        <v>46195.69984417824</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.86652894676</v>
+        <v>46195.69986228009</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5255,13 +5255,13 @@
         <v>232</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.86638777777</v>
+        <v>46065.699721111116</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.50371587963</v>
+        <v>46197.33704921296</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.50373502314</v>
+        <v>46197.337068356486</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5320,13 +5320,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.86638519676</v>
+        <v>46065.69971853009</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.50377947917</v>
+        <v>46197.3371128125</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.50400935185</v>
+        <v>46197.33734268519</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5385,11 +5385,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.866385601854</v>
+        <v>46065.69971893518</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46197.50378688658</v>
+        <v>46197.337120219905</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5448,13 +5448,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.866385960646</v>
+        <v>46065.69971929398</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.607128483796</v>
+        <v>46197.440461817125</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.60726340278</v>
+        <v>46197.44059673611</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5513,11 +5513,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.86638626158</v>
+        <v>46065.69971959491</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.60713396991</v>
+        <v>46197.44046730324</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5574,11 +5574,11 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.8663865625</v>
+        <v>46065.699719895834</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46171.204831423616</v>
+        <v>46171.038164756945</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5635,11 +5635,11 @@
         <v>251</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.866386863425</v>
+        <v>46065.69972019676</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.7553162963</v>
+        <v>46090.58864962963</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>252</v>
@@ -5682,11 +5682,11 @@
         <v>254</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.8663871875</v>
+        <v>46065.69972052083</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46172.17936458334</v>
+        <v>46172.01269791667</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>
@@ -5743,11 +5743,11 @@
         <v>257</v>
       </c>
       <c r="B73" s="8">
-        <v>46065.86638747685</v>
+        <v>46065.69972081018</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46177.199266296295</v>
+        <v>46177.03259962963</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>258</v>
@@ -5806,11 +5806,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46065.866387766204</v>
+        <v>46065.69972109953</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46178.203143680556</v>
+        <v>46178.036477013884</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>262</v>
@@ -5867,11 +5867,11 @@
         <v>266</v>
       </c>
       <c r="B75" s="8">
-        <v>46065.8663881713</v>
+        <v>46065.69972150463</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46179.18502518519</v>
+        <v>46179.018358518515</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>267</v>
@@ -5928,11 +5928,11 @@
         <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46065.866384340276</v>
+        <v>46065.69971767361</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.755315567134</v>
+        <v>46090.58864890046</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>270</v>
@@ -5975,11 +5975,11 @@
         <v>272</v>
       </c>
       <c r="B77" s="8">
-        <v>46065.866385138885</v>
+        <v>46065.69971847222</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46190.20534189815</v>
+        <v>46190.03867523148</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -6038,11 +6038,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46065.866385416666</v>
+        <v>46065.699718749995</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46190.205348206015</v>
+        <v>46190.03868153935</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6101,11 +6101,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.75000248842</v>
+        <v>46090.583335821764</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.75636387731</v>
+        <v>46090.58969721065</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6154,11 +6154,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.75028462963</v>
+        <v>46090.58361796296</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46190.205342534726</v>
+        <v>46190.038675868054</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6217,11 +6217,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.75057857639</v>
+        <v>46090.58391190972</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46191.20339054398</v>
+        <v>46191.03672387732</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.69972041667</v>
+        <v>46065.86638708333</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55529023148</v>
+        <v>46092.72195689815</v>
       </c>
       <c r="D4" s="5">
-        <v>46133.603651701385</v>
+        <v>46133.77031836806</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.69972087963</v>
+        <v>46065.866387546295</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.555256886575</v>
+        <v>46092.72192355324</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55529099537</v>
+        <v>46092.72195766204</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1612,13 +1612,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.69972138889</v>
+        <v>46065.866388055554</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55525744213</v>
+        <v>46092.721924108795</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55529188657</v>
+        <v>46092.721958553244</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1677,13 +1677,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.69972192129</v>
+        <v>46065.866388587965</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55525792824</v>
+        <v>46092.72192459491</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.555291296296</v>
+        <v>46092.72195796296</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1742,13 +1742,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.69972236111</v>
+        <v>46065.86638902778</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55525841435</v>
+        <v>46092.721925081016</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.6233396412</v>
+        <v>46100.79000630787</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1807,13 +1807,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.69972283565</v>
+        <v>46065.86638950232</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55525921297</v>
+        <v>46092.721925879625</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55529192129</v>
+        <v>46092.721958587965</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1872,11 +1872,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.69972333334</v>
+        <v>46065.866389999996</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.3876528588</v>
+        <v>46097.55431952546</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1919,13 +1919,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.699723680555</v>
+        <v>46065.86639034722</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.38764217593</v>
+        <v>46097.55430884259</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.38766100694</v>
+        <v>46097.55432767361</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1984,11 +1984,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.69972405092</v>
+        <v>46065.866390717594</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46137.026501875</v>
+        <v>46137.193168541664</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2047,13 +2047,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.69972444444</v>
+        <v>46065.86639111111</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.35589099537</v>
+        <v>46114.522557662036</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.35590498842</v>
+        <v>46114.52257165509</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2100,13 +2100,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.6997184375</v>
+        <v>46065.866385104164</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.38671878472</v>
+        <v>46097.55338545139</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.386736678236</v>
+        <v>46097.55340334491</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2165,13 +2165,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.69972413195</v>
+        <v>46065.86639079861</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.557669560185</v>
+        <v>46107.72433622685</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.55768900463</v>
+        <v>46107.72435567129</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2230,13 +2230,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.6997255787</v>
+        <v>46065.86639224537</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.55771945602</v>
+        <v>46107.72438612269</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.55773701389</v>
+        <v>46107.72440368056</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2295,13 +2295,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.69972638889</v>
+        <v>46065.866393055556</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.35587568287</v>
+        <v>46114.522542349536</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.35589112269</v>
+        <v>46114.52255778935</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2360,13 +2360,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.69972674768</v>
+        <v>46065.866393414355</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.35593553241</v>
+        <v>46114.522602199075</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.355957997686</v>
+        <v>46114.52262466435</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2413,13 +2413,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.69972708334</v>
+        <v>46065.866393749995</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.386754328705</v>
+        <v>46097.55342099537</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.387491747686</v>
+        <v>46097.55415841435</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -2478,13 +2478,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.69972747685</v>
+        <v>46065.86639414352</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.38667216436</v>
+        <v>46097.553338831014</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.55769261574</v>
+        <v>46107.72435928241</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2543,13 +2543,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.69972790509</v>
+        <v>46065.866394571756</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.38769659722</v>
+        <v>46097.55436326389</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.38771902778</v>
+        <v>46097.55438569444</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2608,13 +2608,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.69972824074</v>
+        <v>46065.86639490741</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.393608240745</v>
+        <v>46113.5602749074</v>
       </c>
       <c r="D22" s="5">
-        <v>46113.39361032407</v>
+        <v>46113.56027699074</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2673,13 +2673,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.699718703705</v>
+        <v>46065.86638537037</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.35591884259</v>
+        <v>46114.52258550926</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.35640158565</v>
+        <v>46114.52306825231</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2738,13 +2738,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.6997191088</v>
+        <v>46065.86638577546</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.55799318287</v>
+        <v>46107.72465984954</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.55801064815</v>
+        <v>46107.724677314814</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2803,11 +2803,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.69971940972</v>
+        <v>46065.86638607639</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46174.486404282405</v>
+        <v>46174.653070949076</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2852,13 +2852,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.69971969907</v>
+        <v>46065.86638636574</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.709235937495</v>
+        <v>46155.875902604166</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.70925018519</v>
+        <v>46155.87591685185</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2917,13 +2917,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.69972001157</v>
+        <v>46065.866386678244</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.38682175926</v>
+        <v>46097.553488425925</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.3868233449</v>
+        <v>46097.553490011574</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2978,13 +2978,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.69972030092</v>
+        <v>46065.866386967595</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.709218055556</v>
+        <v>46155.87588472222</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.70921930556</v>
+        <v>46155.87588597222</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3039,13 +3039,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.69972059027</v>
+        <v>46065.866387256945</v>
       </c>
       <c r="C29" s="8">
-        <v>46122.47842777778</v>
+        <v>46122.645094444444</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.01609658565</v>
+        <v>46128.18276325232</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3104,13 +3104,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.699720902776</v>
+        <v>46065.86638756945</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.38788888889</v>
+        <v>46097.55455555556</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.3878903588</v>
+        <v>46097.55455702546</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3165,13 +3165,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.6997212037</v>
+        <v>46065.86638787037</v>
       </c>
       <c r="C31" s="8">
-        <v>46122.47841251157</v>
+        <v>46122.64507917824</v>
       </c>
       <c r="D31" s="8">
-        <v>46122.47841388889</v>
+        <v>46122.64508055555</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3226,13 +3226,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.69972150463</v>
+        <v>46065.8663881713</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.72490068287</v>
+        <v>46155.891567349536</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.724920231485</v>
+        <v>46155.89158689815</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3291,13 +3291,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.699717696756</v>
+        <v>46065.86638436343</v>
       </c>
       <c r="C33" s="8">
-        <v>46139.627010729164</v>
+        <v>46139.793677395835</v>
       </c>
       <c r="D33" s="8">
-        <v>46139.628311423614</v>
+        <v>46139.79497809028</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3352,13 +3352,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46065.699718090276</v>
+        <v>46065.86638475694</v>
       </c>
       <c r="C34" s="5">
-        <v>46155.724885891206</v>
+        <v>46155.89155255787</v>
       </c>
       <c r="D34" s="5">
-        <v>46155.724887372686</v>
+        <v>46155.89155403935</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3413,13 +3413,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46065.6997183912</v>
+        <v>46065.866385057874</v>
       </c>
       <c r="C35" s="8">
-        <v>46174.48638369213</v>
+        <v>46174.6530503588</v>
       </c>
       <c r="D35" s="8">
-        <v>46174.486394837964</v>
+        <v>46174.65306150463</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3478,13 +3478,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46065.69971868055</v>
+        <v>46065.866385347224</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.38739834491</v>
+        <v>46097.55406501157</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.67490680555</v>
+        <v>46169.84157347222</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3539,13 +3539,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46065.6997189699</v>
+        <v>46065.866385636575</v>
       </c>
       <c r="C37" s="8">
-        <v>46174.48632372685</v>
+        <v>46174.652990393515</v>
       </c>
       <c r="D37" s="8">
-        <v>46174.48632570602</v>
+        <v>46174.652992372685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3600,13 +3600,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.69971927084</v>
+        <v>46065.8663859375</v>
       </c>
       <c r="C38" s="5">
-        <v>46174.48636920139</v>
+        <v>46174.653035868054</v>
       </c>
       <c r="D38" s="5">
-        <v>46174.48637082176</v>
+        <v>46174.653037488424</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3661,13 +3661,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.69971954861</v>
+        <v>46065.866386215275</v>
       </c>
       <c r="C39" s="8">
-        <v>46118.6700700463</v>
+        <v>46118.83673671296</v>
       </c>
       <c r="D39" s="8">
-        <v>46118.670083125</v>
+        <v>46118.83674979166</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3726,13 +3726,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.699719826385</v>
+        <v>46065.86638649306</v>
       </c>
       <c r="C40" s="5">
-        <v>46118.669840532406</v>
+        <v>46118.83650719907</v>
       </c>
       <c r="D40" s="5">
-        <v>46118.66984232639</v>
+        <v>46118.83650899306</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3787,13 +3787,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.69972010417</v>
+        <v>46065.86638677084</v>
       </c>
       <c r="C41" s="8">
-        <v>46118.670056840274</v>
+        <v>46118.836723506945</v>
       </c>
       <c r="D41" s="8">
-        <v>46118.67005832176</v>
+        <v>46118.836724988425</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3848,13 +3848,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46065.69972038195</v>
+        <v>46065.86638704861</v>
       </c>
       <c r="C42" s="5">
-        <v>46118.672245740745</v>
+        <v>46118.83891240741</v>
       </c>
       <c r="D42" s="5">
-        <v>46133.0292046875</v>
+        <v>46133.19587135417</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3913,13 +3913,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.69972002315</v>
+        <v>46065.86638668981</v>
       </c>
       <c r="C43" s="8">
-        <v>46118.672182152775</v>
+        <v>46118.83884881945</v>
       </c>
       <c r="D43" s="8">
-        <v>46118.67218368055</v>
+        <v>46118.83885034722</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3974,13 +3974,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46065.69972040509</v>
+        <v>46065.86638707176</v>
       </c>
       <c r="C44" s="5">
-        <v>46118.67223113426</v>
+        <v>46118.838897800924</v>
       </c>
       <c r="D44" s="5">
-        <v>46118.67223251157</v>
+        <v>46118.83889917824</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4035,11 +4035,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46065.69972070602</v>
+        <v>46065.866387372684</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46107.55921043982</v>
+        <v>46107.72587710648</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4084,13 +4084,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.57748881944</v>
+        <v>46070.744155486114</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.559126168984</v>
+        <v>46107.72579283565</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.55914474537</v>
+        <v>46107.725811412034</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4149,13 +4149,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.6997209838</v>
+        <v>46065.86638765046</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.55918997685</v>
+        <v>46107.72585664352</v>
       </c>
       <c r="D47" s="8">
-        <v>46174.48638537037</v>
+        <v>46174.653052037036</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4214,13 +4214,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46090.582982002314</v>
+        <v>46090.74964866898</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.55926100694</v>
+        <v>46107.725927673615</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.559284166666</v>
+        <v>46107.72595083334</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4279,11 +4279,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46090.58315702547</v>
+        <v>46090.74982369213</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46170.01697292824</v>
+        <v>46170.18363959491</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4342,13 +4342,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.69972127315</v>
+        <v>46065.866387939815</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.46892471064</v>
+        <v>46127.635591377315</v>
       </c>
       <c r="D50" s="5">
-        <v>46127.468940983796</v>
+        <v>46127.63560765046</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4395,13 +4395,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.699721550925</v>
+        <v>46065.86638821759</v>
       </c>
       <c r="C51" s="8">
-        <v>46122.476305069446</v>
+        <v>46122.64297173611</v>
       </c>
       <c r="D51" s="8">
-        <v>46122.47632221065</v>
+        <v>46122.64298887731</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>185</v>
@@ -4460,13 +4460,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.6997218287</v>
+        <v>46065.86638849537</v>
       </c>
       <c r="C52" s="5">
-        <v>46127.4689035301</v>
+        <v>46127.635570196755</v>
       </c>
       <c r="D52" s="5">
-        <v>46127.4689250463</v>
+        <v>46127.63559171296</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4525,13 +4525,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.69972209491</v>
+        <v>46065.86638876157</v>
       </c>
       <c r="C53" s="8">
-        <v>46167.43130704861</v>
+        <v>46167.59797371528</v>
       </c>
       <c r="D53" s="8">
-        <v>46167.43131892361</v>
+        <v>46167.59798559028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4578,13 +4578,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.69972234954</v>
+        <v>46065.8663890162</v>
       </c>
       <c r="C54" s="5">
-        <v>46167.37834422453</v>
+        <v>46167.545010891205</v>
       </c>
       <c r="D54" s="5">
-        <v>46167.378359803246</v>
+        <v>46167.5450264699</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4643,13 +4643,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.69972265046</v>
+        <v>46065.86638931713</v>
       </c>
       <c r="C55" s="8">
-        <v>46167.43123873843</v>
+        <v>46167.59790540509</v>
       </c>
       <c r="D55" s="8">
-        <v>46167.431259652774</v>
+        <v>46167.597926319446</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4708,13 +4708,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.699718206015</v>
+        <v>46065.86638487269</v>
       </c>
       <c r="C56" s="5">
-        <v>46167.43129097222</v>
+        <v>46167.59795763889</v>
       </c>
       <c r="D56" s="5">
-        <v>46167.43130710648</v>
+        <v>46167.59797377315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4773,11 +4773,11 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.69971862268</v>
+        <v>46065.86638528935</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46122.47856425926</v>
+        <v>46122.645230925926</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4820,11 +4820,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.69971893518</v>
+        <v>46065.866385601854</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46155.70922787037</v>
+        <v>46155.875894537035</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4883,11 +4883,11 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.699719236116</v>
+        <v>46065.86638590277</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46155.72490246528</v>
+        <v>46155.89156913194</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4946,11 +4946,11 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.699719571756</v>
+        <v>46065.86638623843</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46174.48634378472</v>
+        <v>46174.65301045139</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5009,11 +5009,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.69971987269</v>
+        <v>46065.86638653935</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46130.00833434028</v>
+        <v>46130.175001006945</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5072,13 +5072,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.69972016204</v>
+        <v>46065.866386828704</v>
       </c>
       <c r="C62" s="5">
-        <v>46122.478558622686</v>
+        <v>46122.64522528935</v>
       </c>
       <c r="D62" s="5">
-        <v>46143.00568688658</v>
+        <v>46143.17235355324</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -5137,13 +5137,13 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.69972047454</v>
+        <v>46065.8663871412</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.43251618056</v>
+        <v>46197.59918284722</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.44046777778</v>
+        <v>46197.60713444444</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5190,13 +5190,13 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.69972077546</v>
+        <v>46065.86638744213</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.69984417824</v>
+        <v>46195.866510844906</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.69986228009</v>
+        <v>46195.86652894676</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5255,13 +5255,13 @@
         <v>232</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.699721111116</v>
+        <v>46065.86638777777</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.33704921296</v>
+        <v>46197.50371587963</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.337068356486</v>
+        <v>46197.50373502314</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5320,13 +5320,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.69971853009</v>
+        <v>46065.86638519676</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.3371128125</v>
+        <v>46197.50377947917</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.33734268519</v>
+        <v>46197.50400935185</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5385,11 +5385,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.69971893518</v>
+        <v>46065.866385601854</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46197.337120219905</v>
+        <v>46197.50378688658</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5448,13 +5448,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.69971929398</v>
+        <v>46065.866385960646</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.440461817125</v>
+        <v>46197.607128483796</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.44059673611</v>
+        <v>46197.60726340278</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5513,11 +5513,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.69971959491</v>
+        <v>46065.86638626158</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.44046730324</v>
+        <v>46197.60713396991</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5574,11 +5574,11 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.699719895834</v>
+        <v>46065.8663865625</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46171.038164756945</v>
+        <v>46171.204831423616</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5635,11 +5635,11 @@
         <v>251</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.69972019676</v>
+        <v>46065.866386863425</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.58864962963</v>
+        <v>46090.7553162963</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>252</v>
@@ -5682,11 +5682,11 @@
         <v>254</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.69972052083</v>
+        <v>46065.8663871875</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46172.01269791667</v>
+        <v>46172.17936458334</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>
@@ -5743,11 +5743,11 @@
         <v>257</v>
       </c>
       <c r="B73" s="8">
-        <v>46065.69972081018</v>
+        <v>46065.86638747685</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46177.03259962963</v>
+        <v>46177.199266296295</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>258</v>
@@ -5806,11 +5806,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46065.69972109953</v>
+        <v>46065.866387766204</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46178.036477013884</v>
+        <v>46178.203143680556</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>262</v>
@@ -5867,11 +5867,11 @@
         <v>266</v>
       </c>
       <c r="B75" s="8">
-        <v>46065.69972150463</v>
+        <v>46065.8663881713</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46179.018358518515</v>
+        <v>46179.18502518519</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>267</v>
@@ -5928,11 +5928,11 @@
         <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46065.69971767361</v>
+        <v>46065.866384340276</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.58864890046</v>
+        <v>46090.755315567134</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>270</v>
@@ -5975,11 +5975,11 @@
         <v>272</v>
       </c>
       <c r="B77" s="8">
-        <v>46065.69971847222</v>
+        <v>46065.866385138885</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46190.03867523148</v>
+        <v>46190.20534189815</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -6038,11 +6038,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46065.699718749995</v>
+        <v>46065.866385416666</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46190.03868153935</v>
+        <v>46190.205348206015</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6101,11 +6101,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.583335821764</v>
+        <v>46090.75000248842</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.58969721065</v>
+        <v>46090.75636387731</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6154,11 +6154,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.58361796296</v>
+        <v>46090.75028462963</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46190.038675868054</v>
+        <v>46190.205342534726</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6217,11 +6217,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.58391190972</v>
+        <v>46090.75057857639</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46191.03672387732</v>
+        <v>46191.20339054398</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -6221,7 +6221,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46191.20339054398</v>
+        <v>46198.25027788195</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.86638708333</v>
+        <v>46065.69972041667</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72195689815</v>
+        <v>46092.55529023148</v>
       </c>
       <c r="D4" s="5">
-        <v>46133.77031836806</v>
+        <v>46133.603651701385</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.866387546295</v>
+        <v>46065.69972087963</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72192355324</v>
+        <v>46092.555256886575</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.72195766204</v>
+        <v>46092.55529099537</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1612,13 +1612,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.866388055554</v>
+        <v>46065.69972138889</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.721924108795</v>
+        <v>46092.55525744213</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.721958553244</v>
+        <v>46092.55529188657</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1677,13 +1677,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.866388587965</v>
+        <v>46065.69972192129</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.72192459491</v>
+        <v>46092.55525792824</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72195796296</v>
+        <v>46092.555291296296</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1742,13 +1742,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.86638902778</v>
+        <v>46065.69972236111</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.721925081016</v>
+        <v>46092.55525841435</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.79000630787</v>
+        <v>46100.6233396412</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1807,13 +1807,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.86638950232</v>
+        <v>46065.69972283565</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.721925879625</v>
+        <v>46092.55525921297</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.721958587965</v>
+        <v>46092.55529192129</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1872,11 +1872,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.866389999996</v>
+        <v>46065.69972333334</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.55431952546</v>
+        <v>46097.3876528588</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1919,13 +1919,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.86639034722</v>
+        <v>46065.699723680555</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.55430884259</v>
+        <v>46097.38764217593</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.55432767361</v>
+        <v>46097.38766100694</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1984,11 +1984,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.866390717594</v>
+        <v>46065.69972405092</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46137.193168541664</v>
+        <v>46137.026501875</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2047,13 +2047,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.86639111111</v>
+        <v>46065.69972444444</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.522557662036</v>
+        <v>46114.35589099537</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.52257165509</v>
+        <v>46114.35590498842</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2100,13 +2100,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.866385104164</v>
+        <v>46065.6997184375</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.55338545139</v>
+        <v>46097.38671878472</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.55340334491</v>
+        <v>46097.386736678236</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2165,13 +2165,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.86639079861</v>
+        <v>46065.69972413195</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.72433622685</v>
+        <v>46107.557669560185</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.72435567129</v>
+        <v>46107.55768900463</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2230,13 +2230,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.86639224537</v>
+        <v>46065.6997255787</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.72438612269</v>
+        <v>46107.55771945602</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.72440368056</v>
+        <v>46107.55773701389</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2295,13 +2295,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.866393055556</v>
+        <v>46065.69972638889</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.522542349536</v>
+        <v>46114.35587568287</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.52255778935</v>
+        <v>46114.35589112269</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2360,13 +2360,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.866393414355</v>
+        <v>46065.69972674768</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.522602199075</v>
+        <v>46114.35593553241</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.52262466435</v>
+        <v>46114.355957997686</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2413,13 +2413,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.866393749995</v>
+        <v>46065.69972708334</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.55342099537</v>
+        <v>46097.386754328705</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.55415841435</v>
+        <v>46097.387491747686</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -2478,13 +2478,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.86639414352</v>
+        <v>46065.69972747685</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.553338831014</v>
+        <v>46097.38667216436</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.72435928241</v>
+        <v>46107.55769261574</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2543,13 +2543,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.866394571756</v>
+        <v>46065.69972790509</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.55436326389</v>
+        <v>46097.38769659722</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.55438569444</v>
+        <v>46097.38771902778</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2608,13 +2608,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.86639490741</v>
+        <v>46065.69972824074</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.5602749074</v>
+        <v>46113.393608240745</v>
       </c>
       <c r="D22" s="5">
-        <v>46113.56027699074</v>
+        <v>46113.39361032407</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2673,13 +2673,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.86638537037</v>
+        <v>46065.699718703705</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.52258550926</v>
+        <v>46114.35591884259</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.52306825231</v>
+        <v>46114.35640158565</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2738,13 +2738,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.86638577546</v>
+        <v>46065.6997191088</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.72465984954</v>
+        <v>46107.55799318287</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.724677314814</v>
+        <v>46107.55801064815</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2803,11 +2803,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.86638607639</v>
+        <v>46065.69971940972</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46174.653070949076</v>
+        <v>46174.486404282405</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2852,13 +2852,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.86638636574</v>
+        <v>46065.69971969907</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.875902604166</v>
+        <v>46155.709235937495</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.87591685185</v>
+        <v>46155.70925018519</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2917,13 +2917,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.866386678244</v>
+        <v>46065.69972001157</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.553488425925</v>
+        <v>46097.38682175926</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.553490011574</v>
+        <v>46097.3868233449</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2978,13 +2978,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.866386967595</v>
+        <v>46065.69972030092</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.87588472222</v>
+        <v>46155.709218055556</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.87588597222</v>
+        <v>46155.70921930556</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3039,13 +3039,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.866387256945</v>
+        <v>46065.69972059027</v>
       </c>
       <c r="C29" s="8">
-        <v>46122.645094444444</v>
+        <v>46122.47842777778</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.18276325232</v>
+        <v>46128.01609658565</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3104,13 +3104,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.86638756945</v>
+        <v>46065.699720902776</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.55455555556</v>
+        <v>46097.38788888889</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.55455702546</v>
+        <v>46097.3878903588</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3165,13 +3165,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.86638787037</v>
+        <v>46065.6997212037</v>
       </c>
       <c r="C31" s="8">
-        <v>46122.64507917824</v>
+        <v>46122.47841251157</v>
       </c>
       <c r="D31" s="8">
-        <v>46122.64508055555</v>
+        <v>46122.47841388889</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3226,13 +3226,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.8663881713</v>
+        <v>46065.69972150463</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.891567349536</v>
+        <v>46155.72490068287</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.89158689815</v>
+        <v>46155.724920231485</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3291,13 +3291,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.86638436343</v>
+        <v>46065.699717696756</v>
       </c>
       <c r="C33" s="8">
-        <v>46139.793677395835</v>
+        <v>46139.627010729164</v>
       </c>
       <c r="D33" s="8">
-        <v>46139.79497809028</v>
+        <v>46139.628311423614</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3352,13 +3352,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46065.86638475694</v>
+        <v>46065.699718090276</v>
       </c>
       <c r="C34" s="5">
-        <v>46155.89155255787</v>
+        <v>46155.724885891206</v>
       </c>
       <c r="D34" s="5">
-        <v>46155.89155403935</v>
+        <v>46155.724887372686</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3413,13 +3413,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46065.866385057874</v>
+        <v>46065.6997183912</v>
       </c>
       <c r="C35" s="8">
-        <v>46174.6530503588</v>
+        <v>46174.48638369213</v>
       </c>
       <c r="D35" s="8">
-        <v>46174.65306150463</v>
+        <v>46174.486394837964</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3478,13 +3478,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46065.866385347224</v>
+        <v>46065.69971868055</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.55406501157</v>
+        <v>46097.38739834491</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.84157347222</v>
+        <v>46169.67490680555</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3539,13 +3539,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46065.866385636575</v>
+        <v>46065.6997189699</v>
       </c>
       <c r="C37" s="8">
-        <v>46174.652990393515</v>
+        <v>46174.48632372685</v>
       </c>
       <c r="D37" s="8">
-        <v>46174.652992372685</v>
+        <v>46174.48632570602</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3600,13 +3600,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.8663859375</v>
+        <v>46065.69971927084</v>
       </c>
       <c r="C38" s="5">
-        <v>46174.653035868054</v>
+        <v>46174.48636920139</v>
       </c>
       <c r="D38" s="5">
-        <v>46174.653037488424</v>
+        <v>46174.48637082176</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3661,13 +3661,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.866386215275</v>
+        <v>46065.69971954861</v>
       </c>
       <c r="C39" s="8">
-        <v>46118.83673671296</v>
+        <v>46118.6700700463</v>
       </c>
       <c r="D39" s="8">
-        <v>46118.83674979166</v>
+        <v>46118.670083125</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3726,13 +3726,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.86638649306</v>
+        <v>46065.699719826385</v>
       </c>
       <c r="C40" s="5">
-        <v>46118.83650719907</v>
+        <v>46118.669840532406</v>
       </c>
       <c r="D40" s="5">
-        <v>46118.83650899306</v>
+        <v>46118.66984232639</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3787,13 +3787,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.86638677084</v>
+        <v>46065.69972010417</v>
       </c>
       <c r="C41" s="8">
-        <v>46118.836723506945</v>
+        <v>46118.670056840274</v>
       </c>
       <c r="D41" s="8">
-        <v>46118.836724988425</v>
+        <v>46118.67005832176</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3848,13 +3848,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46065.86638704861</v>
+        <v>46065.69972038195</v>
       </c>
       <c r="C42" s="5">
-        <v>46118.83891240741</v>
+        <v>46118.672245740745</v>
       </c>
       <c r="D42" s="5">
-        <v>46133.19587135417</v>
+        <v>46133.0292046875</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3913,13 +3913,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.86638668981</v>
+        <v>46065.69972002315</v>
       </c>
       <c r="C43" s="8">
-        <v>46118.83884881945</v>
+        <v>46118.672182152775</v>
       </c>
       <c r="D43" s="8">
-        <v>46118.83885034722</v>
+        <v>46118.67218368055</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3974,13 +3974,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46065.86638707176</v>
+        <v>46065.69972040509</v>
       </c>
       <c r="C44" s="5">
-        <v>46118.838897800924</v>
+        <v>46118.67223113426</v>
       </c>
       <c r="D44" s="5">
-        <v>46118.83889917824</v>
+        <v>46118.67223251157</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4035,11 +4035,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46065.866387372684</v>
+        <v>46065.69972070602</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46107.72587710648</v>
+        <v>46107.55921043982</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4084,13 +4084,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.744155486114</v>
+        <v>46070.57748881944</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.72579283565</v>
+        <v>46107.559126168984</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.725811412034</v>
+        <v>46107.55914474537</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4149,13 +4149,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.86638765046</v>
+        <v>46065.6997209838</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.72585664352</v>
+        <v>46107.55918997685</v>
       </c>
       <c r="D47" s="8">
-        <v>46174.653052037036</v>
+        <v>46174.48638537037</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4214,13 +4214,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46090.74964866898</v>
+        <v>46090.582982002314</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.725927673615</v>
+        <v>46107.55926100694</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.72595083334</v>
+        <v>46107.559284166666</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4279,11 +4279,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46090.74982369213</v>
+        <v>46090.58315702547</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46170.18363959491</v>
+        <v>46170.01697292824</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4342,13 +4342,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.866387939815</v>
+        <v>46065.69972127315</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.635591377315</v>
+        <v>46127.46892471064</v>
       </c>
       <c r="D50" s="5">
-        <v>46127.63560765046</v>
+        <v>46127.468940983796</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4395,13 +4395,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.86638821759</v>
+        <v>46065.699721550925</v>
       </c>
       <c r="C51" s="8">
-        <v>46122.64297173611</v>
+        <v>46122.476305069446</v>
       </c>
       <c r="D51" s="8">
-        <v>46122.64298887731</v>
+        <v>46122.47632221065</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>185</v>
@@ -4460,13 +4460,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.86638849537</v>
+        <v>46065.6997218287</v>
       </c>
       <c r="C52" s="5">
-        <v>46127.635570196755</v>
+        <v>46127.4689035301</v>
       </c>
       <c r="D52" s="5">
-        <v>46127.63559171296</v>
+        <v>46127.4689250463</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4525,13 +4525,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.86638876157</v>
+        <v>46065.69972209491</v>
       </c>
       <c r="C53" s="8">
-        <v>46167.59797371528</v>
+        <v>46167.43130704861</v>
       </c>
       <c r="D53" s="8">
-        <v>46167.59798559028</v>
+        <v>46167.43131892361</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4578,13 +4578,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.8663890162</v>
+        <v>46065.69972234954</v>
       </c>
       <c r="C54" s="5">
-        <v>46167.545010891205</v>
+        <v>46167.37834422453</v>
       </c>
       <c r="D54" s="5">
-        <v>46167.5450264699</v>
+        <v>46167.378359803246</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4643,13 +4643,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.86638931713</v>
+        <v>46065.69972265046</v>
       </c>
       <c r="C55" s="8">
-        <v>46167.59790540509</v>
+        <v>46167.43123873843</v>
       </c>
       <c r="D55" s="8">
-        <v>46167.597926319446</v>
+        <v>46167.431259652774</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4708,13 +4708,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.86638487269</v>
+        <v>46065.699718206015</v>
       </c>
       <c r="C56" s="5">
-        <v>46167.59795763889</v>
+        <v>46167.43129097222</v>
       </c>
       <c r="D56" s="5">
-        <v>46167.59797377315</v>
+        <v>46167.43130710648</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4773,11 +4773,11 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.86638528935</v>
+        <v>46065.69971862268</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46122.645230925926</v>
+        <v>46122.47856425926</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4820,11 +4820,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.866385601854</v>
+        <v>46065.69971893518</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46155.875894537035</v>
+        <v>46155.70922787037</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4883,11 +4883,11 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.86638590277</v>
+        <v>46065.699719236116</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46155.89156913194</v>
+        <v>46155.72490246528</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4946,11 +4946,11 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.86638623843</v>
+        <v>46065.699719571756</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46174.65301045139</v>
+        <v>46174.48634378472</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5009,11 +5009,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.86638653935</v>
+        <v>46065.69971987269</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46130.175001006945</v>
+        <v>46130.00833434028</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5072,13 +5072,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.866386828704</v>
+        <v>46065.69972016204</v>
       </c>
       <c r="C62" s="5">
-        <v>46122.64522528935</v>
+        <v>46122.478558622686</v>
       </c>
       <c r="D62" s="5">
-        <v>46143.17235355324</v>
+        <v>46143.00568688658</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -5137,13 +5137,13 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.8663871412</v>
+        <v>46065.69972047454</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.59918284722</v>
+        <v>46197.43251618056</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.60713444444</v>
+        <v>46197.44046777778</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5190,13 +5190,13 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.86638744213</v>
+        <v>46065.69972077546</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.866510844906</v>
+        <v>46195.69984417824</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.86652894676</v>
+        <v>46195.69986228009</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5255,13 +5255,13 @@
         <v>232</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.86638777777</v>
+        <v>46065.699721111116</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.50371587963</v>
+        <v>46197.33704921296</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.50373502314</v>
+        <v>46197.337068356486</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5320,13 +5320,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.86638519676</v>
+        <v>46065.69971853009</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.50377947917</v>
+        <v>46197.3371128125</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.50400935185</v>
+        <v>46197.33734268519</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5385,11 +5385,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.866385601854</v>
+        <v>46065.69971893518</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46197.50378688658</v>
+        <v>46197.337120219905</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5448,13 +5448,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.866385960646</v>
+        <v>46065.69971929398</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.607128483796</v>
+        <v>46197.440461817125</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.60726340278</v>
+        <v>46197.44059673611</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5513,11 +5513,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.86638626158</v>
+        <v>46065.69971959491</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.60713396991</v>
+        <v>46197.44046730324</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5574,11 +5574,11 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.8663865625</v>
+        <v>46065.699719895834</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46171.204831423616</v>
+        <v>46171.038164756945</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5635,11 +5635,11 @@
         <v>251</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.866386863425</v>
+        <v>46065.69972019676</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.7553162963</v>
+        <v>46090.58864962963</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>252</v>
@@ -5682,11 +5682,11 @@
         <v>254</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.8663871875</v>
+        <v>46065.69972052083</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46172.17936458334</v>
+        <v>46172.01269791667</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>
@@ -5743,11 +5743,11 @@
         <v>257</v>
       </c>
       <c r="B73" s="8">
-        <v>46065.86638747685</v>
+        <v>46065.69972081018</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46177.199266296295</v>
+        <v>46177.03259962963</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>258</v>
@@ -5806,11 +5806,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46065.866387766204</v>
+        <v>46065.69972109953</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46178.203143680556</v>
+        <v>46178.036477013884</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>262</v>
@@ -5867,11 +5867,11 @@
         <v>266</v>
       </c>
       <c r="B75" s="8">
-        <v>46065.8663881713</v>
+        <v>46065.69972150463</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46179.18502518519</v>
+        <v>46179.018358518515</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>267</v>
@@ -5928,11 +5928,11 @@
         <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46065.866384340276</v>
+        <v>46065.69971767361</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.755315567134</v>
+        <v>46090.58864890046</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>270</v>
@@ -5975,11 +5975,11 @@
         <v>272</v>
       </c>
       <c r="B77" s="8">
-        <v>46065.866385138885</v>
+        <v>46065.69971847222</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46190.20534189815</v>
+        <v>46190.03867523148</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -6038,11 +6038,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46065.866385416666</v>
+        <v>46065.699718749995</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46190.205348206015</v>
+        <v>46190.03868153935</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6101,11 +6101,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.75000248842</v>
+        <v>46090.583335821764</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.75636387731</v>
+        <v>46090.58969721065</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6154,11 +6154,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.75028462963</v>
+        <v>46090.58361796296</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46190.205342534726</v>
+        <v>46190.038675868054</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6217,11 +6217,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.75057857639</v>
+        <v>46090.58391190972</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46198.25027788195</v>
+        <v>46198.083611215276</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.69972041667</v>
+        <v>46065.86638708333</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55529023148</v>
+        <v>46092.72195689815</v>
       </c>
       <c r="D4" s="5">
-        <v>46133.603651701385</v>
+        <v>46133.77031836806</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.69972087963</v>
+        <v>46065.866387546295</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.555256886575</v>
+        <v>46092.72192355324</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55529099537</v>
+        <v>46092.72195766204</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1612,13 +1612,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.69972138889</v>
+        <v>46065.866388055554</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55525744213</v>
+        <v>46092.721924108795</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55529188657</v>
+        <v>46092.721958553244</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1677,13 +1677,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.69972192129</v>
+        <v>46065.866388587965</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55525792824</v>
+        <v>46092.72192459491</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.555291296296</v>
+        <v>46092.72195796296</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1742,13 +1742,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.69972236111</v>
+        <v>46065.86638902778</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55525841435</v>
+        <v>46092.721925081016</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.6233396412</v>
+        <v>46100.79000630787</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1807,13 +1807,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.69972283565</v>
+        <v>46065.86638950232</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55525921297</v>
+        <v>46092.721925879625</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55529192129</v>
+        <v>46092.721958587965</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1872,11 +1872,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.69972333334</v>
+        <v>46065.866389999996</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.3876528588</v>
+        <v>46097.55431952546</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1919,13 +1919,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.699723680555</v>
+        <v>46065.86639034722</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.38764217593</v>
+        <v>46097.55430884259</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.38766100694</v>
+        <v>46097.55432767361</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1984,11 +1984,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.69972405092</v>
+        <v>46065.866390717594</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46137.026501875</v>
+        <v>46137.193168541664</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2047,13 +2047,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.69972444444</v>
+        <v>46065.86639111111</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.35589099537</v>
+        <v>46114.522557662036</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.35590498842</v>
+        <v>46114.52257165509</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2100,13 +2100,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.6997184375</v>
+        <v>46065.866385104164</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.38671878472</v>
+        <v>46097.55338545139</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.386736678236</v>
+        <v>46097.55340334491</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2165,13 +2165,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.69972413195</v>
+        <v>46065.86639079861</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.557669560185</v>
+        <v>46107.72433622685</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.55768900463</v>
+        <v>46107.72435567129</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2230,13 +2230,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.6997255787</v>
+        <v>46065.86639224537</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.55771945602</v>
+        <v>46107.72438612269</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.55773701389</v>
+        <v>46107.72440368056</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2295,13 +2295,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.69972638889</v>
+        <v>46065.866393055556</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.35587568287</v>
+        <v>46114.522542349536</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.35589112269</v>
+        <v>46114.52255778935</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2360,13 +2360,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.69972674768</v>
+        <v>46065.866393414355</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.35593553241</v>
+        <v>46114.522602199075</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.355957997686</v>
+        <v>46114.52262466435</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2413,13 +2413,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.69972708334</v>
+        <v>46065.866393749995</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.386754328705</v>
+        <v>46097.55342099537</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.387491747686</v>
+        <v>46097.55415841435</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -2478,13 +2478,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.69972747685</v>
+        <v>46065.86639414352</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.38667216436</v>
+        <v>46097.553338831014</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.55769261574</v>
+        <v>46107.72435928241</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2543,13 +2543,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.69972790509</v>
+        <v>46065.866394571756</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.38769659722</v>
+        <v>46097.55436326389</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.38771902778</v>
+        <v>46097.55438569444</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2608,13 +2608,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.69972824074</v>
+        <v>46065.86639490741</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.393608240745</v>
+        <v>46113.5602749074</v>
       </c>
       <c r="D22" s="5">
-        <v>46113.39361032407</v>
+        <v>46113.56027699074</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2673,13 +2673,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.699718703705</v>
+        <v>46065.86638537037</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.35591884259</v>
+        <v>46114.52258550926</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.35640158565</v>
+        <v>46114.52306825231</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2738,13 +2738,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.6997191088</v>
+        <v>46065.86638577546</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.55799318287</v>
+        <v>46107.72465984954</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.55801064815</v>
+        <v>46107.724677314814</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2803,11 +2803,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.69971940972</v>
+        <v>46065.86638607639</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46174.486404282405</v>
+        <v>46174.653070949076</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2852,13 +2852,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.69971969907</v>
+        <v>46065.86638636574</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.709235937495</v>
+        <v>46155.875902604166</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.70925018519</v>
+        <v>46155.87591685185</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2917,13 +2917,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.69972001157</v>
+        <v>46065.866386678244</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.38682175926</v>
+        <v>46097.553488425925</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.3868233449</v>
+        <v>46097.553490011574</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2978,13 +2978,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.69972030092</v>
+        <v>46065.866386967595</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.709218055556</v>
+        <v>46155.87588472222</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.70921930556</v>
+        <v>46155.87588597222</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3039,13 +3039,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.69972059027</v>
+        <v>46065.866387256945</v>
       </c>
       <c r="C29" s="8">
-        <v>46122.47842777778</v>
+        <v>46122.645094444444</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.01609658565</v>
+        <v>46128.18276325232</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3104,13 +3104,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.699720902776</v>
+        <v>46065.86638756945</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.38788888889</v>
+        <v>46097.55455555556</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.3878903588</v>
+        <v>46097.55455702546</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3165,13 +3165,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.6997212037</v>
+        <v>46065.86638787037</v>
       </c>
       <c r="C31" s="8">
-        <v>46122.47841251157</v>
+        <v>46122.64507917824</v>
       </c>
       <c r="D31" s="8">
-        <v>46122.47841388889</v>
+        <v>46122.64508055555</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3226,13 +3226,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.69972150463</v>
+        <v>46065.8663881713</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.72490068287</v>
+        <v>46155.891567349536</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.724920231485</v>
+        <v>46155.89158689815</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3291,13 +3291,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.699717696756</v>
+        <v>46065.86638436343</v>
       </c>
       <c r="C33" s="8">
-        <v>46139.627010729164</v>
+        <v>46139.793677395835</v>
       </c>
       <c r="D33" s="8">
-        <v>46139.628311423614</v>
+        <v>46139.79497809028</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3352,13 +3352,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46065.699718090276</v>
+        <v>46065.86638475694</v>
       </c>
       <c r="C34" s="5">
-        <v>46155.724885891206</v>
+        <v>46155.89155255787</v>
       </c>
       <c r="D34" s="5">
-        <v>46155.724887372686</v>
+        <v>46155.89155403935</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3413,13 +3413,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46065.6997183912</v>
+        <v>46065.866385057874</v>
       </c>
       <c r="C35" s="8">
-        <v>46174.48638369213</v>
+        <v>46174.6530503588</v>
       </c>
       <c r="D35" s="8">
-        <v>46174.486394837964</v>
+        <v>46174.65306150463</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3478,13 +3478,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46065.69971868055</v>
+        <v>46065.866385347224</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.38739834491</v>
+        <v>46097.55406501157</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.67490680555</v>
+        <v>46169.84157347222</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3539,13 +3539,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46065.6997189699</v>
+        <v>46065.866385636575</v>
       </c>
       <c r="C37" s="8">
-        <v>46174.48632372685</v>
+        <v>46174.652990393515</v>
       </c>
       <c r="D37" s="8">
-        <v>46174.48632570602</v>
+        <v>46174.652992372685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3600,13 +3600,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.69971927084</v>
+        <v>46065.8663859375</v>
       </c>
       <c r="C38" s="5">
-        <v>46174.48636920139</v>
+        <v>46174.653035868054</v>
       </c>
       <c r="D38" s="5">
-        <v>46174.48637082176</v>
+        <v>46174.653037488424</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3661,13 +3661,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.69971954861</v>
+        <v>46065.866386215275</v>
       </c>
       <c r="C39" s="8">
-        <v>46118.6700700463</v>
+        <v>46118.83673671296</v>
       </c>
       <c r="D39" s="8">
-        <v>46118.670083125</v>
+        <v>46118.83674979166</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3726,13 +3726,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.699719826385</v>
+        <v>46065.86638649306</v>
       </c>
       <c r="C40" s="5">
-        <v>46118.669840532406</v>
+        <v>46118.83650719907</v>
       </c>
       <c r="D40" s="5">
-        <v>46118.66984232639</v>
+        <v>46118.83650899306</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3787,13 +3787,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.69972010417</v>
+        <v>46065.86638677084</v>
       </c>
       <c r="C41" s="8">
-        <v>46118.670056840274</v>
+        <v>46118.836723506945</v>
       </c>
       <c r="D41" s="8">
-        <v>46118.67005832176</v>
+        <v>46118.836724988425</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3848,13 +3848,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46065.69972038195</v>
+        <v>46065.86638704861</v>
       </c>
       <c r="C42" s="5">
-        <v>46118.672245740745</v>
+        <v>46118.83891240741</v>
       </c>
       <c r="D42" s="5">
-        <v>46133.0292046875</v>
+        <v>46133.19587135417</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3913,13 +3913,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.69972002315</v>
+        <v>46065.86638668981</v>
       </c>
       <c r="C43" s="8">
-        <v>46118.672182152775</v>
+        <v>46118.83884881945</v>
       </c>
       <c r="D43" s="8">
-        <v>46118.67218368055</v>
+        <v>46118.83885034722</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3974,13 +3974,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46065.69972040509</v>
+        <v>46065.86638707176</v>
       </c>
       <c r="C44" s="5">
-        <v>46118.67223113426</v>
+        <v>46118.838897800924</v>
       </c>
       <c r="D44" s="5">
-        <v>46118.67223251157</v>
+        <v>46118.83889917824</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4035,11 +4035,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46065.69972070602</v>
+        <v>46065.866387372684</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46107.55921043982</v>
+        <v>46107.72587710648</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4084,13 +4084,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.57748881944</v>
+        <v>46070.744155486114</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.559126168984</v>
+        <v>46107.72579283565</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.55914474537</v>
+        <v>46107.725811412034</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4149,13 +4149,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.6997209838</v>
+        <v>46065.86638765046</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.55918997685</v>
+        <v>46107.72585664352</v>
       </c>
       <c r="D47" s="8">
-        <v>46174.48638537037</v>
+        <v>46174.653052037036</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4214,13 +4214,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46090.582982002314</v>
+        <v>46090.74964866898</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.55926100694</v>
+        <v>46107.725927673615</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.559284166666</v>
+        <v>46107.72595083334</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4279,11 +4279,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46090.58315702547</v>
+        <v>46090.74982369213</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46170.01697292824</v>
+        <v>46170.18363959491</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4342,13 +4342,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.69972127315</v>
+        <v>46065.866387939815</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.46892471064</v>
+        <v>46127.635591377315</v>
       </c>
       <c r="D50" s="5">
-        <v>46127.468940983796</v>
+        <v>46127.63560765046</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4395,13 +4395,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.699721550925</v>
+        <v>46065.86638821759</v>
       </c>
       <c r="C51" s="8">
-        <v>46122.476305069446</v>
+        <v>46122.64297173611</v>
       </c>
       <c r="D51" s="8">
-        <v>46122.47632221065</v>
+        <v>46122.64298887731</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>185</v>
@@ -4460,13 +4460,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.6997218287</v>
+        <v>46065.86638849537</v>
       </c>
       <c r="C52" s="5">
-        <v>46127.4689035301</v>
+        <v>46127.635570196755</v>
       </c>
       <c r="D52" s="5">
-        <v>46127.4689250463</v>
+        <v>46127.63559171296</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4525,13 +4525,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.69972209491</v>
+        <v>46065.86638876157</v>
       </c>
       <c r="C53" s="8">
-        <v>46167.43130704861</v>
+        <v>46167.59797371528</v>
       </c>
       <c r="D53" s="8">
-        <v>46167.43131892361</v>
+        <v>46167.59798559028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4578,13 +4578,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.69972234954</v>
+        <v>46065.8663890162</v>
       </c>
       <c r="C54" s="5">
-        <v>46167.37834422453</v>
+        <v>46167.545010891205</v>
       </c>
       <c r="D54" s="5">
-        <v>46167.378359803246</v>
+        <v>46167.5450264699</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4643,13 +4643,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.69972265046</v>
+        <v>46065.86638931713</v>
       </c>
       <c r="C55" s="8">
-        <v>46167.43123873843</v>
+        <v>46167.59790540509</v>
       </c>
       <c r="D55" s="8">
-        <v>46167.431259652774</v>
+        <v>46167.597926319446</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4708,13 +4708,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.699718206015</v>
+        <v>46065.86638487269</v>
       </c>
       <c r="C56" s="5">
-        <v>46167.43129097222</v>
+        <v>46167.59795763889</v>
       </c>
       <c r="D56" s="5">
-        <v>46167.43130710648</v>
+        <v>46167.59797377315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4773,11 +4773,11 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.69971862268</v>
+        <v>46065.86638528935</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46122.47856425926</v>
+        <v>46122.645230925926</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4820,11 +4820,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.69971893518</v>
+        <v>46065.866385601854</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46155.70922787037</v>
+        <v>46155.875894537035</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4883,11 +4883,11 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.699719236116</v>
+        <v>46065.86638590277</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46155.72490246528</v>
+        <v>46155.89156913194</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4946,11 +4946,11 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.699719571756</v>
+        <v>46065.86638623843</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46174.48634378472</v>
+        <v>46174.65301045139</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5009,11 +5009,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.69971987269</v>
+        <v>46065.86638653935</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46130.00833434028</v>
+        <v>46130.175001006945</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5072,13 +5072,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.69972016204</v>
+        <v>46065.866386828704</v>
       </c>
       <c r="C62" s="5">
-        <v>46122.478558622686</v>
+        <v>46122.64522528935</v>
       </c>
       <c r="D62" s="5">
-        <v>46143.00568688658</v>
+        <v>46143.17235355324</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -5137,13 +5137,13 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.69972047454</v>
+        <v>46065.8663871412</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.43251618056</v>
+        <v>46197.59918284722</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.44046777778</v>
+        <v>46197.60713444444</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5190,13 +5190,13 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.69972077546</v>
+        <v>46065.86638744213</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.69984417824</v>
+        <v>46195.866510844906</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.69986228009</v>
+        <v>46195.86652894676</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5255,13 +5255,13 @@
         <v>232</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.699721111116</v>
+        <v>46065.86638777777</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.33704921296</v>
+        <v>46197.50371587963</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.337068356486</v>
+        <v>46197.50373502314</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5320,13 +5320,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.69971853009</v>
+        <v>46065.86638519676</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.3371128125</v>
+        <v>46197.50377947917</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.33734268519</v>
+        <v>46197.50400935185</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5385,11 +5385,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.69971893518</v>
+        <v>46065.866385601854</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46197.337120219905</v>
+        <v>46197.50378688658</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5448,13 +5448,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.69971929398</v>
+        <v>46065.866385960646</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.440461817125</v>
+        <v>46197.607128483796</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.44059673611</v>
+        <v>46197.60726340278</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5513,11 +5513,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.69971959491</v>
+        <v>46065.86638626158</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.44046730324</v>
+        <v>46197.60713396991</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5574,11 +5574,11 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.699719895834</v>
+        <v>46065.8663865625</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46171.038164756945</v>
+        <v>46171.204831423616</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5635,11 +5635,11 @@
         <v>251</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.69972019676</v>
+        <v>46065.866386863425</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.58864962963</v>
+        <v>46090.7553162963</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>252</v>
@@ -5682,11 +5682,11 @@
         <v>254</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.69972052083</v>
+        <v>46065.8663871875</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46172.01269791667</v>
+        <v>46172.17936458334</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>
@@ -5743,11 +5743,11 @@
         <v>257</v>
       </c>
       <c r="B73" s="8">
-        <v>46065.69972081018</v>
+        <v>46065.86638747685</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46177.03259962963</v>
+        <v>46177.199266296295</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>258</v>
@@ -5806,11 +5806,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46065.69972109953</v>
+        <v>46065.866387766204</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46178.036477013884</v>
+        <v>46178.203143680556</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>262</v>
@@ -5867,11 +5867,11 @@
         <v>266</v>
       </c>
       <c r="B75" s="8">
-        <v>46065.69972150463</v>
+        <v>46065.8663881713</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46179.018358518515</v>
+        <v>46179.18502518519</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>267</v>
@@ -5928,11 +5928,11 @@
         <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46065.69971767361</v>
+        <v>46065.866384340276</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.58864890046</v>
+        <v>46090.755315567134</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>270</v>
@@ -5975,11 +5975,11 @@
         <v>272</v>
       </c>
       <c r="B77" s="8">
-        <v>46065.69971847222</v>
+        <v>46065.866385138885</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46190.03867523148</v>
+        <v>46190.20534189815</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -6038,11 +6038,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46065.699718749995</v>
+        <v>46065.866385416666</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46190.03868153935</v>
+        <v>46190.205348206015</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6101,11 +6101,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.583335821764</v>
+        <v>46090.75000248842</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.58969721065</v>
+        <v>46090.75636387731</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6154,11 +6154,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.58361796296</v>
+        <v>46090.75028462963</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46190.038675868054</v>
+        <v>46190.205342534726</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6217,11 +6217,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.58391190972</v>
+        <v>46090.75057857639</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46198.083611215276</v>
+        <v>46198.25027788195</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46122.645230925926</v>
+        <v>46198.825604212965</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4822,9 +4822,11 @@
       <c r="B58" s="5">
         <v>46065.866385601854</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46198.824122164355</v>
+      </c>
       <c r="D58" s="5">
-        <v>46155.875894537035</v>
+        <v>46198.824139675926</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4869,10 +4871,10 @@
         <v>46148</v>
       </c>
       <c r="S58" s="6">
-        <v>0</v>
-      </c>
-      <c r="T58" s="12" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="T58" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U58" s="11" t="s">
         <v>32</v>
@@ -4948,9 +4950,11 @@
       <c r="B60" s="5">
         <v>46065.86638623843</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46198.82559879629</v>
+      </c>
       <c r="D60" s="5">
-        <v>46174.65301045139</v>
+        <v>46198.82561377315</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -4995,10 +4999,10 @@
         <v>46163</v>
       </c>
       <c r="S60" s="6">
-        <v>0</v>
-      </c>
-      <c r="T60" s="12" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="T60" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U60" s="11" t="s">
         <v>32</v>
@@ -5261,7 +5265,7 @@
         <v>46197.50371587963</v>
       </c>
       <c r="D65" s="8">
-        <v>46197.50373502314</v>
+        <v>46198.82561393519</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5308,8 +5312,8 @@
       <c r="S65" s="9">
         <v>1</v>
       </c>
-      <c r="T65" s="10" t="s">
-        <v>31</v>
+      <c r="T65" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="U65" s="11" t="s">
         <v>32</v>
@@ -5326,7 +5330,7 @@
         <v>46197.50377947917</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.50400935185</v>
+        <v>46198.82414078704</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5373,8 +5377,8 @@
       <c r="S66" s="6">
         <v>1</v>
       </c>
-      <c r="T66" s="10" t="s">
-        <v>31</v>
+      <c r="T66" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>32</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -6225,7 +6225,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46198.25027788195</v>
+        <v>46199.19411842593</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>
@@ -6275,8 +6275,8 @@
       <c r="T81" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="U81" s="12" t="s">
-        <v>157</v>
+      <c r="U81" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.86638708333</v>
+        <v>46065.69972041667</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72195689815</v>
+        <v>46092.55529023148</v>
       </c>
       <c r="D4" s="5">
-        <v>46133.77031836806</v>
+        <v>46133.603651701385</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.866387546295</v>
+        <v>46065.69972087963</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72192355324</v>
+        <v>46092.555256886575</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.72195766204</v>
+        <v>46092.55529099537</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1612,13 +1612,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.866388055554</v>
+        <v>46065.69972138889</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.721924108795</v>
+        <v>46092.55525744213</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.721958553244</v>
+        <v>46092.55529188657</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1677,13 +1677,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.866388587965</v>
+        <v>46065.69972192129</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.72192459491</v>
+        <v>46092.55525792824</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72195796296</v>
+        <v>46092.555291296296</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1742,13 +1742,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.86638902778</v>
+        <v>46065.69972236111</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.721925081016</v>
+        <v>46092.55525841435</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.79000630787</v>
+        <v>46100.6233396412</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1807,13 +1807,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.86638950232</v>
+        <v>46065.69972283565</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.721925879625</v>
+        <v>46092.55525921297</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.721958587965</v>
+        <v>46092.55529192129</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1872,11 +1872,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.866389999996</v>
+        <v>46065.69972333334</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.55431952546</v>
+        <v>46097.3876528588</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1919,13 +1919,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.86639034722</v>
+        <v>46065.699723680555</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.55430884259</v>
+        <v>46097.38764217593</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.55432767361</v>
+        <v>46097.38766100694</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1984,11 +1984,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.866390717594</v>
+        <v>46065.69972405092</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46137.193168541664</v>
+        <v>46137.026501875</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2047,13 +2047,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.86639111111</v>
+        <v>46065.69972444444</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.522557662036</v>
+        <v>46114.35589099537</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.52257165509</v>
+        <v>46114.35590498842</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2100,13 +2100,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.866385104164</v>
+        <v>46065.6997184375</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.55338545139</v>
+        <v>46097.38671878472</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.55340334491</v>
+        <v>46097.386736678236</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2165,13 +2165,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.86639079861</v>
+        <v>46065.69972413195</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.72433622685</v>
+        <v>46107.557669560185</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.72435567129</v>
+        <v>46107.55768900463</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2230,13 +2230,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.86639224537</v>
+        <v>46065.6997255787</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.72438612269</v>
+        <v>46107.55771945602</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.72440368056</v>
+        <v>46107.55773701389</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2295,13 +2295,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.866393055556</v>
+        <v>46065.69972638889</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.522542349536</v>
+        <v>46114.35587568287</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.52255778935</v>
+        <v>46114.35589112269</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2360,13 +2360,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.866393414355</v>
+        <v>46065.69972674768</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.522602199075</v>
+        <v>46114.35593553241</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.52262466435</v>
+        <v>46114.355957997686</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2413,13 +2413,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.866393749995</v>
+        <v>46065.69972708334</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.55342099537</v>
+        <v>46097.386754328705</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.55415841435</v>
+        <v>46097.387491747686</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -2478,13 +2478,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.86639414352</v>
+        <v>46065.69972747685</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.553338831014</v>
+        <v>46097.38667216436</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.72435928241</v>
+        <v>46107.55769261574</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2543,13 +2543,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.866394571756</v>
+        <v>46065.69972790509</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.55436326389</v>
+        <v>46097.38769659722</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.55438569444</v>
+        <v>46097.38771902778</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2608,13 +2608,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.86639490741</v>
+        <v>46065.69972824074</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.5602749074</v>
+        <v>46113.393608240745</v>
       </c>
       <c r="D22" s="5">
-        <v>46113.56027699074</v>
+        <v>46113.39361032407</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2673,13 +2673,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.86638537037</v>
+        <v>46065.699718703705</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.52258550926</v>
+        <v>46114.35591884259</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.52306825231</v>
+        <v>46114.35640158565</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2738,13 +2738,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.86638577546</v>
+        <v>46065.6997191088</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.72465984954</v>
+        <v>46107.55799318287</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.724677314814</v>
+        <v>46107.55801064815</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2803,11 +2803,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.86638607639</v>
+        <v>46065.69971940972</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46174.653070949076</v>
+        <v>46174.486404282405</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2852,13 +2852,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.86638636574</v>
+        <v>46065.69971969907</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.875902604166</v>
+        <v>46155.709235937495</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.87591685185</v>
+        <v>46155.70925018519</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2917,13 +2917,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.866386678244</v>
+        <v>46065.69972001157</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.553488425925</v>
+        <v>46097.38682175926</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.553490011574</v>
+        <v>46097.3868233449</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2978,13 +2978,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.866386967595</v>
+        <v>46065.69972030092</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.87588472222</v>
+        <v>46155.709218055556</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.87588597222</v>
+        <v>46155.70921930556</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3039,13 +3039,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.866387256945</v>
+        <v>46065.69972059027</v>
       </c>
       <c r="C29" s="8">
-        <v>46122.645094444444</v>
+        <v>46122.47842777778</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.18276325232</v>
+        <v>46128.01609658565</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3104,13 +3104,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.86638756945</v>
+        <v>46065.699720902776</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.55455555556</v>
+        <v>46097.38788888889</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.55455702546</v>
+        <v>46097.3878903588</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3165,13 +3165,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.86638787037</v>
+        <v>46065.6997212037</v>
       </c>
       <c r="C31" s="8">
-        <v>46122.64507917824</v>
+        <v>46122.47841251157</v>
       </c>
       <c r="D31" s="8">
-        <v>46122.64508055555</v>
+        <v>46122.47841388889</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3226,13 +3226,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.8663881713</v>
+        <v>46065.69972150463</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.891567349536</v>
+        <v>46155.72490068287</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.89158689815</v>
+        <v>46155.724920231485</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3291,13 +3291,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.86638436343</v>
+        <v>46065.699717696756</v>
       </c>
       <c r="C33" s="8">
-        <v>46139.793677395835</v>
+        <v>46139.627010729164</v>
       </c>
       <c r="D33" s="8">
-        <v>46139.79497809028</v>
+        <v>46139.628311423614</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3352,13 +3352,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46065.86638475694</v>
+        <v>46065.699718090276</v>
       </c>
       <c r="C34" s="5">
-        <v>46155.89155255787</v>
+        <v>46155.724885891206</v>
       </c>
       <c r="D34" s="5">
-        <v>46155.89155403935</v>
+        <v>46155.724887372686</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3413,13 +3413,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46065.866385057874</v>
+        <v>46065.6997183912</v>
       </c>
       <c r="C35" s="8">
-        <v>46174.6530503588</v>
+        <v>46174.48638369213</v>
       </c>
       <c r="D35" s="8">
-        <v>46174.65306150463</v>
+        <v>46174.486394837964</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3478,13 +3478,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46065.866385347224</v>
+        <v>46065.69971868055</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.55406501157</v>
+        <v>46097.38739834491</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.84157347222</v>
+        <v>46169.67490680555</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3539,13 +3539,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46065.866385636575</v>
+        <v>46065.6997189699</v>
       </c>
       <c r="C37" s="8">
-        <v>46174.652990393515</v>
+        <v>46174.48632372685</v>
       </c>
       <c r="D37" s="8">
-        <v>46174.652992372685</v>
+        <v>46174.48632570602</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3600,13 +3600,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.8663859375</v>
+        <v>46065.69971927084</v>
       </c>
       <c r="C38" s="5">
-        <v>46174.653035868054</v>
+        <v>46174.48636920139</v>
       </c>
       <c r="D38" s="5">
-        <v>46174.653037488424</v>
+        <v>46174.48637082176</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3661,13 +3661,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.866386215275</v>
+        <v>46065.69971954861</v>
       </c>
       <c r="C39" s="8">
-        <v>46118.83673671296</v>
+        <v>46118.6700700463</v>
       </c>
       <c r="D39" s="8">
-        <v>46118.83674979166</v>
+        <v>46118.670083125</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3726,13 +3726,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.86638649306</v>
+        <v>46065.699719826385</v>
       </c>
       <c r="C40" s="5">
-        <v>46118.83650719907</v>
+        <v>46118.669840532406</v>
       </c>
       <c r="D40" s="5">
-        <v>46118.83650899306</v>
+        <v>46118.66984232639</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3787,13 +3787,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.86638677084</v>
+        <v>46065.69972010417</v>
       </c>
       <c r="C41" s="8">
-        <v>46118.836723506945</v>
+        <v>46118.670056840274</v>
       </c>
       <c r="D41" s="8">
-        <v>46118.836724988425</v>
+        <v>46118.67005832176</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3848,13 +3848,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46065.86638704861</v>
+        <v>46065.69972038195</v>
       </c>
       <c r="C42" s="5">
-        <v>46118.83891240741</v>
+        <v>46118.672245740745</v>
       </c>
       <c r="D42" s="5">
-        <v>46133.19587135417</v>
+        <v>46133.0292046875</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3913,13 +3913,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.86638668981</v>
+        <v>46065.69972002315</v>
       </c>
       <c r="C43" s="8">
-        <v>46118.83884881945</v>
+        <v>46118.672182152775</v>
       </c>
       <c r="D43" s="8">
-        <v>46118.83885034722</v>
+        <v>46118.67218368055</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3974,13 +3974,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46065.86638707176</v>
+        <v>46065.69972040509</v>
       </c>
       <c r="C44" s="5">
-        <v>46118.838897800924</v>
+        <v>46118.67223113426</v>
       </c>
       <c r="D44" s="5">
-        <v>46118.83889917824</v>
+        <v>46118.67223251157</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4035,11 +4035,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46065.866387372684</v>
+        <v>46065.69972070602</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46107.72587710648</v>
+        <v>46107.55921043982</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4084,13 +4084,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.744155486114</v>
+        <v>46070.57748881944</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.72579283565</v>
+        <v>46107.559126168984</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.725811412034</v>
+        <v>46107.55914474537</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4149,13 +4149,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.86638765046</v>
+        <v>46065.6997209838</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.72585664352</v>
+        <v>46107.55918997685</v>
       </c>
       <c r="D47" s="8">
-        <v>46174.653052037036</v>
+        <v>46174.48638537037</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4214,13 +4214,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46090.74964866898</v>
+        <v>46090.582982002314</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.725927673615</v>
+        <v>46107.55926100694</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.72595083334</v>
+        <v>46107.559284166666</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4279,11 +4279,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46090.74982369213</v>
+        <v>46090.58315702547</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46170.18363959491</v>
+        <v>46170.01697292824</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4342,13 +4342,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.866387939815</v>
+        <v>46065.69972127315</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.635591377315</v>
+        <v>46127.46892471064</v>
       </c>
       <c r="D50" s="5">
-        <v>46127.63560765046</v>
+        <v>46127.468940983796</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4395,13 +4395,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.86638821759</v>
+        <v>46065.699721550925</v>
       </c>
       <c r="C51" s="8">
-        <v>46122.64297173611</v>
+        <v>46122.476305069446</v>
       </c>
       <c r="D51" s="8">
-        <v>46122.64298887731</v>
+        <v>46122.47632221065</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>185</v>
@@ -4460,13 +4460,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.86638849537</v>
+        <v>46065.6997218287</v>
       </c>
       <c r="C52" s="5">
-        <v>46127.635570196755</v>
+        <v>46127.4689035301</v>
       </c>
       <c r="D52" s="5">
-        <v>46127.63559171296</v>
+        <v>46127.4689250463</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4525,13 +4525,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.86638876157</v>
+        <v>46065.69972209491</v>
       </c>
       <c r="C53" s="8">
-        <v>46167.59797371528</v>
+        <v>46167.43130704861</v>
       </c>
       <c r="D53" s="8">
-        <v>46167.59798559028</v>
+        <v>46167.43131892361</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4578,13 +4578,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.8663890162</v>
+        <v>46065.69972234954</v>
       </c>
       <c r="C54" s="5">
-        <v>46167.545010891205</v>
+        <v>46167.37834422453</v>
       </c>
       <c r="D54" s="5">
-        <v>46167.5450264699</v>
+        <v>46167.378359803246</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4643,13 +4643,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.86638931713</v>
+        <v>46065.69972265046</v>
       </c>
       <c r="C55" s="8">
-        <v>46167.59790540509</v>
+        <v>46167.43123873843</v>
       </c>
       <c r="D55" s="8">
-        <v>46167.597926319446</v>
+        <v>46167.431259652774</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4708,13 +4708,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.86638487269</v>
+        <v>46065.699718206015</v>
       </c>
       <c r="C56" s="5">
-        <v>46167.59795763889</v>
+        <v>46167.43129097222</v>
       </c>
       <c r="D56" s="5">
-        <v>46167.59797377315</v>
+        <v>46167.43130710648</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4773,11 +4773,11 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.86638528935</v>
+        <v>46065.69971862268</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46198.825604212965</v>
+        <v>46198.65893754629</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4820,13 +4820,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.866385601854</v>
+        <v>46065.69971893518</v>
       </c>
       <c r="C58" s="5">
-        <v>46198.824122164355</v>
+        <v>46198.65745549768</v>
       </c>
       <c r="D58" s="5">
-        <v>46198.824139675926</v>
+        <v>46198.657473009254</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4885,11 +4885,11 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.86638590277</v>
+        <v>46065.699719236116</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46155.89156913194</v>
+        <v>46155.72490246528</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4948,13 +4948,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.86638623843</v>
+        <v>46065.699719571756</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.82559879629</v>
+        <v>46198.658932129634</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.82561377315</v>
+        <v>46198.65894710648</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5013,11 +5013,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.86638653935</v>
+        <v>46065.69971987269</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46130.175001006945</v>
+        <v>46130.00833434028</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5076,13 +5076,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.866386828704</v>
+        <v>46065.69972016204</v>
       </c>
       <c r="C62" s="5">
-        <v>46122.64522528935</v>
+        <v>46122.478558622686</v>
       </c>
       <c r="D62" s="5">
-        <v>46143.17235355324</v>
+        <v>46143.00568688658</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -5141,13 +5141,13 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.8663871412</v>
+        <v>46065.69972047454</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.59918284722</v>
+        <v>46197.43251618056</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.60713444444</v>
+        <v>46197.44046777778</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5194,13 +5194,13 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.86638744213</v>
+        <v>46065.69972077546</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.866510844906</v>
+        <v>46195.69984417824</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.86652894676</v>
+        <v>46195.69986228009</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5259,13 +5259,13 @@
         <v>232</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.86638777777</v>
+        <v>46065.699721111116</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.50371587963</v>
+        <v>46197.33704921296</v>
       </c>
       <c r="D65" s="8">
-        <v>46198.82561393519</v>
+        <v>46198.658947268515</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5324,13 +5324,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.86638519676</v>
+        <v>46065.69971853009</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.50377947917</v>
+        <v>46197.3371128125</v>
       </c>
       <c r="D66" s="5">
-        <v>46198.82414078704</v>
+        <v>46198.657474120366</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5389,11 +5389,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.866385601854</v>
+        <v>46065.69971893518</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46197.50378688658</v>
+        <v>46197.337120219905</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5452,13 +5452,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.866385960646</v>
+        <v>46065.69971929398</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.607128483796</v>
+        <v>46197.440461817125</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.60726340278</v>
+        <v>46197.44059673611</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5517,11 +5517,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.86638626158</v>
+        <v>46065.69971959491</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.60713396991</v>
+        <v>46197.44046730324</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5578,11 +5578,11 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.8663865625</v>
+        <v>46065.699719895834</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46171.204831423616</v>
+        <v>46171.038164756945</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5639,11 +5639,11 @@
         <v>251</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.866386863425</v>
+        <v>46065.69972019676</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.7553162963</v>
+        <v>46090.58864962963</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>252</v>
@@ -5686,11 +5686,11 @@
         <v>254</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.8663871875</v>
+        <v>46065.69972052083</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46172.17936458334</v>
+        <v>46172.01269791667</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>
@@ -5747,11 +5747,11 @@
         <v>257</v>
       </c>
       <c r="B73" s="8">
-        <v>46065.86638747685</v>
+        <v>46065.69972081018</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46177.199266296295</v>
+        <v>46177.03259962963</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>258</v>
@@ -5810,11 +5810,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46065.866387766204</v>
+        <v>46065.69972109953</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46178.203143680556</v>
+        <v>46178.036477013884</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>262</v>
@@ -5871,11 +5871,11 @@
         <v>266</v>
       </c>
       <c r="B75" s="8">
-        <v>46065.8663881713</v>
+        <v>46065.69972150463</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46179.18502518519</v>
+        <v>46179.018358518515</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>267</v>
@@ -5932,11 +5932,11 @@
         <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46065.866384340276</v>
+        <v>46065.69971767361</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.755315567134</v>
+        <v>46090.58864890046</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>270</v>
@@ -5979,11 +5979,11 @@
         <v>272</v>
       </c>
       <c r="B77" s="8">
-        <v>46065.866385138885</v>
+        <v>46065.69971847222</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46190.20534189815</v>
+        <v>46190.03867523148</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -6042,11 +6042,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46065.866385416666</v>
+        <v>46065.699718749995</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46190.205348206015</v>
+        <v>46190.03868153935</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6105,11 +6105,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.75000248842</v>
+        <v>46090.583335821764</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.75636387731</v>
+        <v>46090.58969721065</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6158,11 +6158,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.75028462963</v>
+        <v>46090.58361796296</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46190.205342534726</v>
+        <v>46190.038675868054</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6221,11 +6221,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.75057857639</v>
+        <v>46090.58391190972</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46199.19411842593</v>
+        <v>46199.02745175926</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -1498,13 +1498,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.69972041667</v>
+        <v>46065.86638708333</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55529023148</v>
+        <v>46092.72195689815</v>
       </c>
       <c r="D4" s="5">
-        <v>46133.603651701385</v>
+        <v>46133.77031836806</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1547,13 +1547,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.69972087963</v>
+        <v>46065.866387546295</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.555256886575</v>
+        <v>46092.72192355324</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55529099537</v>
+        <v>46092.72195766204</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1612,13 +1612,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.69972138889</v>
+        <v>46065.866388055554</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55525744213</v>
+        <v>46092.721924108795</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55529188657</v>
+        <v>46092.721958553244</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1677,13 +1677,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.69972192129</v>
+        <v>46065.866388587965</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55525792824</v>
+        <v>46092.72192459491</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.555291296296</v>
+        <v>46092.72195796296</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1742,13 +1742,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.69972236111</v>
+        <v>46065.86638902778</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55525841435</v>
+        <v>46092.721925081016</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.6233396412</v>
+        <v>46100.79000630787</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1807,13 +1807,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.69972283565</v>
+        <v>46065.86638950232</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55525921297</v>
+        <v>46092.721925879625</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55529192129</v>
+        <v>46092.721958587965</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1872,11 +1872,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.69972333334</v>
+        <v>46065.866389999996</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.3876528588</v>
+        <v>46097.55431952546</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1919,13 +1919,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.699723680555</v>
+        <v>46065.86639034722</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.38764217593</v>
+        <v>46097.55430884259</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.38766100694</v>
+        <v>46097.55432767361</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1984,11 +1984,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.69972405092</v>
+        <v>46065.866390717594</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46137.026501875</v>
+        <v>46137.193168541664</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2047,13 +2047,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.69972444444</v>
+        <v>46065.86639111111</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.35589099537</v>
+        <v>46114.522557662036</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.35590498842</v>
+        <v>46114.52257165509</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2100,13 +2100,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.6997184375</v>
+        <v>46065.866385104164</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.38671878472</v>
+        <v>46097.55338545139</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.386736678236</v>
+        <v>46097.55340334491</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2165,13 +2165,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.69972413195</v>
+        <v>46065.86639079861</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.557669560185</v>
+        <v>46107.72433622685</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.55768900463</v>
+        <v>46107.72435567129</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2230,13 +2230,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.6997255787</v>
+        <v>46065.86639224537</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.55771945602</v>
+        <v>46107.72438612269</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.55773701389</v>
+        <v>46107.72440368056</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2295,13 +2295,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.69972638889</v>
+        <v>46065.866393055556</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.35587568287</v>
+        <v>46114.522542349536</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.35589112269</v>
+        <v>46114.52255778935</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2360,13 +2360,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.69972674768</v>
+        <v>46065.866393414355</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.35593553241</v>
+        <v>46114.522602199075</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.355957997686</v>
+        <v>46114.52262466435</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2413,13 +2413,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.69972708334</v>
+        <v>46065.866393749995</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.386754328705</v>
+        <v>46097.55342099537</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.387491747686</v>
+        <v>46097.55415841435</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -2478,13 +2478,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.69972747685</v>
+        <v>46065.86639414352</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.38667216436</v>
+        <v>46097.553338831014</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.55769261574</v>
+        <v>46107.72435928241</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2543,13 +2543,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.69972790509</v>
+        <v>46065.866394571756</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.38769659722</v>
+        <v>46097.55436326389</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.38771902778</v>
+        <v>46097.55438569444</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2608,13 +2608,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.69972824074</v>
+        <v>46065.86639490741</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.393608240745</v>
+        <v>46113.5602749074</v>
       </c>
       <c r="D22" s="5">
-        <v>46113.39361032407</v>
+        <v>46113.56027699074</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2673,13 +2673,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.699718703705</v>
+        <v>46065.86638537037</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.35591884259</v>
+        <v>46114.52258550926</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.35640158565</v>
+        <v>46114.52306825231</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2738,13 +2738,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.6997191088</v>
+        <v>46065.86638577546</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.55799318287</v>
+        <v>46107.72465984954</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.55801064815</v>
+        <v>46107.724677314814</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2803,11 +2803,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.69971940972</v>
+        <v>46065.86638607639</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46174.486404282405</v>
+        <v>46174.653070949076</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2852,13 +2852,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.69971969907</v>
+        <v>46065.86638636574</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.709235937495</v>
+        <v>46155.875902604166</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.70925018519</v>
+        <v>46155.87591685185</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2917,13 +2917,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.69972001157</v>
+        <v>46065.866386678244</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.38682175926</v>
+        <v>46097.553488425925</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.3868233449</v>
+        <v>46097.553490011574</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2978,13 +2978,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.69972030092</v>
+        <v>46065.866386967595</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.709218055556</v>
+        <v>46155.87588472222</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.70921930556</v>
+        <v>46155.87588597222</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3039,13 +3039,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.69972059027</v>
+        <v>46065.866387256945</v>
       </c>
       <c r="C29" s="8">
-        <v>46122.47842777778</v>
+        <v>46122.645094444444</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.01609658565</v>
+        <v>46128.18276325232</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3104,13 +3104,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.699720902776</v>
+        <v>46065.86638756945</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.38788888889</v>
+        <v>46097.55455555556</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.3878903588</v>
+        <v>46097.55455702546</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3165,13 +3165,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.6997212037</v>
+        <v>46065.86638787037</v>
       </c>
       <c r="C31" s="8">
-        <v>46122.47841251157</v>
+        <v>46122.64507917824</v>
       </c>
       <c r="D31" s="8">
-        <v>46122.47841388889</v>
+        <v>46122.64508055555</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3226,13 +3226,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.69972150463</v>
+        <v>46065.8663881713</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.72490068287</v>
+        <v>46155.891567349536</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.724920231485</v>
+        <v>46155.89158689815</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3291,13 +3291,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.699717696756</v>
+        <v>46065.86638436343</v>
       </c>
       <c r="C33" s="8">
-        <v>46139.627010729164</v>
+        <v>46139.793677395835</v>
       </c>
       <c r="D33" s="8">
-        <v>46139.628311423614</v>
+        <v>46139.79497809028</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3352,13 +3352,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46065.699718090276</v>
+        <v>46065.86638475694</v>
       </c>
       <c r="C34" s="5">
-        <v>46155.724885891206</v>
+        <v>46155.89155255787</v>
       </c>
       <c r="D34" s="5">
-        <v>46155.724887372686</v>
+        <v>46155.89155403935</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3413,13 +3413,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46065.6997183912</v>
+        <v>46065.866385057874</v>
       </c>
       <c r="C35" s="8">
-        <v>46174.48638369213</v>
+        <v>46174.6530503588</v>
       </c>
       <c r="D35" s="8">
-        <v>46174.486394837964</v>
+        <v>46174.65306150463</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3478,13 +3478,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46065.69971868055</v>
+        <v>46065.866385347224</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.38739834491</v>
+        <v>46097.55406501157</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.67490680555</v>
+        <v>46169.84157347222</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3539,13 +3539,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46065.6997189699</v>
+        <v>46065.866385636575</v>
       </c>
       <c r="C37" s="8">
-        <v>46174.48632372685</v>
+        <v>46174.652990393515</v>
       </c>
       <c r="D37" s="8">
-        <v>46174.48632570602</v>
+        <v>46174.652992372685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3600,13 +3600,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.69971927084</v>
+        <v>46065.8663859375</v>
       </c>
       <c r="C38" s="5">
-        <v>46174.48636920139</v>
+        <v>46174.653035868054</v>
       </c>
       <c r="D38" s="5">
-        <v>46174.48637082176</v>
+        <v>46174.653037488424</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3661,13 +3661,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.69971954861</v>
+        <v>46065.866386215275</v>
       </c>
       <c r="C39" s="8">
-        <v>46118.6700700463</v>
+        <v>46118.83673671296</v>
       </c>
       <c r="D39" s="8">
-        <v>46118.670083125</v>
+        <v>46118.83674979166</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3726,13 +3726,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.699719826385</v>
+        <v>46065.86638649306</v>
       </c>
       <c r="C40" s="5">
-        <v>46118.669840532406</v>
+        <v>46118.83650719907</v>
       </c>
       <c r="D40" s="5">
-        <v>46118.66984232639</v>
+        <v>46118.83650899306</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3787,13 +3787,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.69972010417</v>
+        <v>46065.86638677084</v>
       </c>
       <c r="C41" s="8">
-        <v>46118.670056840274</v>
+        <v>46118.836723506945</v>
       </c>
       <c r="D41" s="8">
-        <v>46118.67005832176</v>
+        <v>46118.836724988425</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3848,13 +3848,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46065.69972038195</v>
+        <v>46065.86638704861</v>
       </c>
       <c r="C42" s="5">
-        <v>46118.672245740745</v>
+        <v>46118.83891240741</v>
       </c>
       <c r="D42" s="5">
-        <v>46133.0292046875</v>
+        <v>46133.19587135417</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3913,13 +3913,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.69972002315</v>
+        <v>46065.86638668981</v>
       </c>
       <c r="C43" s="8">
-        <v>46118.672182152775</v>
+        <v>46118.83884881945</v>
       </c>
       <c r="D43" s="8">
-        <v>46118.67218368055</v>
+        <v>46118.83885034722</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3974,13 +3974,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46065.69972040509</v>
+        <v>46065.86638707176</v>
       </c>
       <c r="C44" s="5">
-        <v>46118.67223113426</v>
+        <v>46118.838897800924</v>
       </c>
       <c r="D44" s="5">
-        <v>46118.67223251157</v>
+        <v>46118.83889917824</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4035,11 +4035,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46065.69972070602</v>
+        <v>46065.866387372684</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46107.55921043982</v>
+        <v>46107.72587710648</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4084,13 +4084,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.57748881944</v>
+        <v>46070.744155486114</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.559126168984</v>
+        <v>46107.72579283565</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.55914474537</v>
+        <v>46107.725811412034</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4149,13 +4149,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.6997209838</v>
+        <v>46065.86638765046</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.55918997685</v>
+        <v>46107.72585664352</v>
       </c>
       <c r="D47" s="8">
-        <v>46174.48638537037</v>
+        <v>46174.653052037036</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4214,13 +4214,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46090.582982002314</v>
+        <v>46090.74964866898</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.55926100694</v>
+        <v>46107.725927673615</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.559284166666</v>
+        <v>46107.72595083334</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4279,11 +4279,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46090.58315702547</v>
+        <v>46090.74982369213</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46170.01697292824</v>
+        <v>46170.18363959491</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4342,13 +4342,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.69972127315</v>
+        <v>46065.866387939815</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.46892471064</v>
+        <v>46127.635591377315</v>
       </c>
       <c r="D50" s="5">
-        <v>46127.468940983796</v>
+        <v>46127.63560765046</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4395,13 +4395,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.699721550925</v>
+        <v>46065.86638821759</v>
       </c>
       <c r="C51" s="8">
-        <v>46122.476305069446</v>
+        <v>46122.64297173611</v>
       </c>
       <c r="D51" s="8">
-        <v>46122.47632221065</v>
+        <v>46122.64298887731</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>185</v>
@@ -4460,13 +4460,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.6997218287</v>
+        <v>46065.86638849537</v>
       </c>
       <c r="C52" s="5">
-        <v>46127.4689035301</v>
+        <v>46127.635570196755</v>
       </c>
       <c r="D52" s="5">
-        <v>46127.4689250463</v>
+        <v>46127.63559171296</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4525,13 +4525,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.69972209491</v>
+        <v>46065.86638876157</v>
       </c>
       <c r="C53" s="8">
-        <v>46167.43130704861</v>
+        <v>46167.59797371528</v>
       </c>
       <c r="D53" s="8">
-        <v>46167.43131892361</v>
+        <v>46167.59798559028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4578,13 +4578,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.69972234954</v>
+        <v>46065.8663890162</v>
       </c>
       <c r="C54" s="5">
-        <v>46167.37834422453</v>
+        <v>46167.545010891205</v>
       </c>
       <c r="D54" s="5">
-        <v>46167.378359803246</v>
+        <v>46167.5450264699</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4643,13 +4643,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.69972265046</v>
+        <v>46065.86638931713</v>
       </c>
       <c r="C55" s="8">
-        <v>46167.43123873843</v>
+        <v>46167.59790540509</v>
       </c>
       <c r="D55" s="8">
-        <v>46167.431259652774</v>
+        <v>46167.597926319446</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4708,13 +4708,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.699718206015</v>
+        <v>46065.86638487269</v>
       </c>
       <c r="C56" s="5">
-        <v>46167.43129097222</v>
+        <v>46167.59795763889</v>
       </c>
       <c r="D56" s="5">
-        <v>46167.43130710648</v>
+        <v>46167.59797377315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4773,11 +4773,11 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.69971862268</v>
+        <v>46065.86638528935</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46198.65893754629</v>
+        <v>46198.825604212965</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4820,13 +4820,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.69971893518</v>
+        <v>46065.866385601854</v>
       </c>
       <c r="C58" s="5">
-        <v>46198.65745549768</v>
+        <v>46198.824122164355</v>
       </c>
       <c r="D58" s="5">
-        <v>46198.657473009254</v>
+        <v>46198.824139675926</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4885,11 +4885,11 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.699719236116</v>
+        <v>46065.86638590277</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46155.72490246528</v>
+        <v>46155.89156913194</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4948,13 +4948,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.699719571756</v>
+        <v>46065.86638623843</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.658932129634</v>
+        <v>46198.82559879629</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.65894710648</v>
+        <v>46198.82561377315</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5013,11 +5013,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.69971987269</v>
+        <v>46065.86638653935</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46130.00833434028</v>
+        <v>46130.175001006945</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5076,13 +5076,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.69972016204</v>
+        <v>46065.866386828704</v>
       </c>
       <c r="C62" s="5">
-        <v>46122.478558622686</v>
+        <v>46122.64522528935</v>
       </c>
       <c r="D62" s="5">
-        <v>46143.00568688658</v>
+        <v>46143.17235355324</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -5141,13 +5141,13 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.69972047454</v>
+        <v>46065.8663871412</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.43251618056</v>
+        <v>46197.59918284722</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.44046777778</v>
+        <v>46197.60713444444</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5194,13 +5194,13 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.69972077546</v>
+        <v>46065.86638744213</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.69984417824</v>
+        <v>46195.866510844906</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.69986228009</v>
+        <v>46195.86652894676</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5259,13 +5259,13 @@
         <v>232</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.699721111116</v>
+        <v>46065.86638777777</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.33704921296</v>
+        <v>46197.50371587963</v>
       </c>
       <c r="D65" s="8">
-        <v>46198.658947268515</v>
+        <v>46198.82561393519</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5324,13 +5324,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.69971853009</v>
+        <v>46065.86638519676</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.3371128125</v>
+        <v>46197.50377947917</v>
       </c>
       <c r="D66" s="5">
-        <v>46198.657474120366</v>
+        <v>46198.82414078704</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5389,11 +5389,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.69971893518</v>
+        <v>46065.866385601854</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46197.337120219905</v>
+        <v>46197.50378688658</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5452,13 +5452,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.69971929398</v>
+        <v>46065.866385960646</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.440461817125</v>
+        <v>46197.607128483796</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.44059673611</v>
+        <v>46197.60726340278</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5517,11 +5517,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.69971959491</v>
+        <v>46065.86638626158</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.44046730324</v>
+        <v>46197.60713396991</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5578,11 +5578,11 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.699719895834</v>
+        <v>46065.8663865625</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46171.038164756945</v>
+        <v>46171.204831423616</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5639,11 +5639,11 @@
         <v>251</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.69972019676</v>
+        <v>46065.866386863425</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.58864962963</v>
+        <v>46090.7553162963</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>252</v>
@@ -5686,11 +5686,11 @@
         <v>254</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.69972052083</v>
+        <v>46065.8663871875</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46172.01269791667</v>
+        <v>46172.17936458334</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>
@@ -5747,11 +5747,11 @@
         <v>257</v>
       </c>
       <c r="B73" s="8">
-        <v>46065.69972081018</v>
+        <v>46065.86638747685</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46177.03259962963</v>
+        <v>46177.199266296295</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>258</v>
@@ -5810,11 +5810,11 @@
         <v>261</v>
       </c>
       <c r="B74" s="5">
-        <v>46065.69972109953</v>
+        <v>46065.866387766204</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46178.036477013884</v>
+        <v>46178.203143680556</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>262</v>
@@ -5871,11 +5871,11 @@
         <v>266</v>
       </c>
       <c r="B75" s="8">
-        <v>46065.69972150463</v>
+        <v>46065.8663881713</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46179.018358518515</v>
+        <v>46179.18502518519</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>267</v>
@@ -5932,11 +5932,11 @@
         <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46065.69971767361</v>
+        <v>46065.866384340276</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.58864890046</v>
+        <v>46090.755315567134</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>270</v>
@@ -5979,11 +5979,11 @@
         <v>272</v>
       </c>
       <c r="B77" s="8">
-        <v>46065.69971847222</v>
+        <v>46065.866385138885</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46190.03867523148</v>
+        <v>46190.20534189815</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>273</v>
@@ -6042,11 +6042,11 @@
         <v>277</v>
       </c>
       <c r="B78" s="5">
-        <v>46065.699718749995</v>
+        <v>46065.866385416666</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46190.03868153935</v>
+        <v>46190.205348206015</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>278</v>
@@ -6105,11 +6105,11 @@
         <v>279</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.583335821764</v>
+        <v>46090.75000248842</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.58969721065</v>
+        <v>46090.75636387731</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>280</v>
@@ -6158,11 +6158,11 @@
         <v>282</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.58361796296</v>
+        <v>46090.75028462963</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46190.038675868054</v>
+        <v>46190.205342534726</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>283</v>
@@ -6221,11 +6221,11 @@
         <v>285</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.58391190972</v>
+        <v>46090.75057857639</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46199.02745175926</v>
+        <v>46199.19411842593</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>286</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="289">
   <si>
     <t xml:space="preserve">50001497 - XEMORTIZ IMMSA STA. BBR  </t>
   </si>
@@ -779,6 +779,12 @@
   </si>
   <si>
     <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
   </si>
   <si>
     <t>Embalaje,Logistica:</t>
@@ -5690,7 +5696,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46172.17936458334</v>
+        <v>46210.603462604166</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>
@@ -5699,10 +5705,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>35</v>
+        <v>256</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>36</v>
+        <v>257</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5724,7 +5730,7 @@
         <v>182</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q72" s="5">
         <v>46171</v>
@@ -5744,7 +5750,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B73" s="8">
         <v>46065.86638747685</v>
@@ -5754,7 +5760,7 @@
         <v>46177.199266296295</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5784,10 +5790,10 @@
         <v>252</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q73" s="8">
         <v>46174</v>
@@ -5807,7 +5813,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B74" s="5">
         <v>46065.866387766204</v>
@@ -5817,16 +5823,16 @@
         <v>46178.203143680556</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5845,10 +5851,10 @@
         <v>252</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q74" s="5">
         <v>46177</v>
@@ -5868,7 +5874,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B75" s="8">
         <v>46065.8663881713</v>
@@ -5878,16 +5884,16 @@
         <v>46179.18502518519</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5906,10 +5912,10 @@
         <v>252</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q75" s="8">
         <v>46147</v>
@@ -5929,7 +5935,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B76" s="5">
         <v>46065.866384340276</v>
@@ -5939,7 +5945,7 @@
         <v>46090.755315567134</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5963,7 +5969,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5976,7 +5982,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B77" s="8">
         <v>46065.866385138885</v>
@@ -5986,16 +5992,16 @@
         <v>46190.20534189815</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I77" s="8">
         <v>46181</v>
@@ -6013,13 +6019,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q77" s="8">
         <v>46181</v>
@@ -6039,7 +6045,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B78" s="5">
         <v>46065.866385416666</v>
@@ -6049,16 +6055,16 @@
         <v>46190.205348206015</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I78" s="5">
         <v>46181</v>
@@ -6076,13 +6082,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q78" s="5">
         <v>46181</v>
@@ -6102,7 +6108,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B79" s="8">
         <v>46090.75000248842</v>
@@ -6112,7 +6118,7 @@
         <v>46090.75636387731</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6136,7 +6142,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6155,7 +6161,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B80" s="5">
         <v>46090.75028462963</v>
@@ -6165,7 +6171,7 @@
         <v>46190.205342534726</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6192,13 +6198,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q80" s="5">
         <v>46181</v>
@@ -6218,7 +6224,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B81" s="8">
         <v>46090.75057857639</v>
@@ -6228,7 +6234,7 @@
         <v>46199.19411842593</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6255,13 +6261,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q81" s="8">
         <v>46190</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46198.825604212965</v>
+        <v>46210.61193216435</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4893,9 +4893,11 @@
       <c r="B59" s="8">
         <v>46065.86638590277</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="8">
+        <v>46210.61192333333</v>
+      </c>
       <c r="D59" s="8">
-        <v>46155.89156913194</v>
+        <v>46210.611941863426</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4940,10 +4942,10 @@
         <v>46056</v>
       </c>
       <c r="S59" s="9">
-        <v>0</v>
-      </c>
-      <c r="T59" s="12" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="T59" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U59" s="11" t="s">
         <v>32</v>
@@ -5153,7 +5155,7 @@
         <v>46197.59918284722</v>
       </c>
       <c r="D63" s="8">
-        <v>46197.60713444444</v>
+        <v>46210.61246145834</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5397,9 +5399,11 @@
       <c r="B67" s="8">
         <v>46065.866385601854</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="8">
+        <v>46210.61245306713</v>
+      </c>
       <c r="D67" s="8">
-        <v>46197.50378688658</v>
+        <v>46210.61246942129</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5444,10 +5448,10 @@
         <v>46154</v>
       </c>
       <c r="S67" s="9">
-        <v>0</v>
-      </c>
-      <c r="T67" s="11" t="s">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="T67" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U67" s="11" t="s">
         <v>32</v>
@@ -5527,7 +5531,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.60713396991</v>
+        <v>46210.61246953704</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5572,8 +5576,8 @@
       <c r="S69" s="9">
         <v>0</v>
       </c>
-      <c r="T69" s="11" t="s">
-        <v>56</v>
+      <c r="T69" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="U69" s="11" t="s">
         <v>32</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -5155,7 +5155,7 @@
         <v>46197.59918284722</v>
       </c>
       <c r="D63" s="8">
-        <v>46210.61246145834</v>
+        <v>46210.640153368055</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5399,11 +5399,9 @@
       <c r="B67" s="8">
         <v>46065.866385601854</v>
       </c>
-      <c r="C67" s="8">
-        <v>46210.61245306713</v>
-      </c>
+      <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46210.61246942129</v>
+        <v>46210.640305451394</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5531,7 +5529,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46210.61246953704</v>
+        <v>46210.640152928245</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -5401,7 +5401,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46210.640305451394</v>
+        <v>46211.647106944445</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -1504,13 +1504,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.86638708333</v>
+        <v>46065.69972041667</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.72195689815</v>
+        <v>46092.55529023148</v>
       </c>
       <c r="D4" s="5">
-        <v>46133.77031836806</v>
+        <v>46133.603651701385</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1553,13 +1553,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.866387546295</v>
+        <v>46065.69972087963</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72192355324</v>
+        <v>46092.555256886575</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.72195766204</v>
+        <v>46092.55529099537</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1618,13 +1618,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.866388055554</v>
+        <v>46065.69972138889</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.721924108795</v>
+        <v>46092.55525744213</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.721958553244</v>
+        <v>46092.55529188657</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1683,13 +1683,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.866388587965</v>
+        <v>46065.69972192129</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.72192459491</v>
+        <v>46092.55525792824</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.72195796296</v>
+        <v>46092.555291296296</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1748,13 +1748,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.86638902778</v>
+        <v>46065.69972236111</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.721925081016</v>
+        <v>46092.55525841435</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.79000630787</v>
+        <v>46100.6233396412</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1813,13 +1813,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.86638950232</v>
+        <v>46065.69972283565</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.721925879625</v>
+        <v>46092.55525921297</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.721958587965</v>
+        <v>46092.55529192129</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1878,11 +1878,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.866389999996</v>
+        <v>46065.69972333334</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.55431952546</v>
+        <v>46097.3876528588</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1925,13 +1925,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.86639034722</v>
+        <v>46065.699723680555</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.55430884259</v>
+        <v>46097.38764217593</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.55432767361</v>
+        <v>46097.38766100694</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1990,11 +1990,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.866390717594</v>
+        <v>46065.69972405092</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46137.193168541664</v>
+        <v>46137.026501875</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2053,13 +2053,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.86639111111</v>
+        <v>46065.69972444444</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.522557662036</v>
+        <v>46114.35589099537</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.52257165509</v>
+        <v>46114.35590498842</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2106,13 +2106,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.866385104164</v>
+        <v>46065.6997184375</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.55338545139</v>
+        <v>46097.38671878472</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.55340334491</v>
+        <v>46097.386736678236</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2171,13 +2171,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.86639079861</v>
+        <v>46065.69972413195</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.72433622685</v>
+        <v>46107.557669560185</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.72435567129</v>
+        <v>46107.55768900463</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2236,13 +2236,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.86639224537</v>
+        <v>46065.6997255787</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.72438612269</v>
+        <v>46107.55771945602</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.72440368056</v>
+        <v>46107.55773701389</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2301,13 +2301,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.866393055556</v>
+        <v>46065.69972638889</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.522542349536</v>
+        <v>46114.35587568287</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.52255778935</v>
+        <v>46114.35589112269</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2366,13 +2366,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.866393414355</v>
+        <v>46065.69972674768</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.522602199075</v>
+        <v>46114.35593553241</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.52262466435</v>
+        <v>46114.355957997686</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2419,13 +2419,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.866393749995</v>
+        <v>46065.69972708334</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.55342099537</v>
+        <v>46097.386754328705</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.55415841435</v>
+        <v>46097.387491747686</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -2484,13 +2484,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.86639414352</v>
+        <v>46065.69972747685</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.553338831014</v>
+        <v>46097.38667216436</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.72435928241</v>
+        <v>46107.55769261574</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2549,13 +2549,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.866394571756</v>
+        <v>46065.69972790509</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.55436326389</v>
+        <v>46097.38769659722</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.55438569444</v>
+        <v>46097.38771902778</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2614,13 +2614,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.86639490741</v>
+        <v>46065.69972824074</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.5602749074</v>
+        <v>46113.393608240745</v>
       </c>
       <c r="D22" s="5">
-        <v>46113.56027699074</v>
+        <v>46113.39361032407</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2679,13 +2679,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.86638537037</v>
+        <v>46065.699718703705</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.52258550926</v>
+        <v>46114.35591884259</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.52306825231</v>
+        <v>46114.35640158565</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2744,13 +2744,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.86638577546</v>
+        <v>46065.6997191088</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.72465984954</v>
+        <v>46107.55799318287</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.724677314814</v>
+        <v>46107.55801064815</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2809,11 +2809,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.86638607639</v>
+        <v>46065.69971940972</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46174.653070949076</v>
+        <v>46174.486404282405</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2858,13 +2858,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.86638636574</v>
+        <v>46065.69971969907</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.875902604166</v>
+        <v>46155.709235937495</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.87591685185</v>
+        <v>46155.70925018519</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2923,13 +2923,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.866386678244</v>
+        <v>46065.69972001157</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.553488425925</v>
+        <v>46097.38682175926</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.553490011574</v>
+        <v>46097.3868233449</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2984,13 +2984,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.866386967595</v>
+        <v>46065.69972030092</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.87588472222</v>
+        <v>46155.709218055556</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.87588597222</v>
+        <v>46155.70921930556</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3045,13 +3045,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.866387256945</v>
+        <v>46065.69972059027</v>
       </c>
       <c r="C29" s="8">
-        <v>46122.645094444444</v>
+        <v>46122.47842777778</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.18276325232</v>
+        <v>46128.01609658565</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3110,13 +3110,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.86638756945</v>
+        <v>46065.699720902776</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.55455555556</v>
+        <v>46097.38788888889</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.55455702546</v>
+        <v>46097.3878903588</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3171,13 +3171,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.86638787037</v>
+        <v>46065.6997212037</v>
       </c>
       <c r="C31" s="8">
-        <v>46122.64507917824</v>
+        <v>46122.47841251157</v>
       </c>
       <c r="D31" s="8">
-        <v>46122.64508055555</v>
+        <v>46122.47841388889</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3232,13 +3232,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.8663881713</v>
+        <v>46065.69972150463</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.891567349536</v>
+        <v>46155.72490068287</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.89158689815</v>
+        <v>46155.724920231485</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3297,13 +3297,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.86638436343</v>
+        <v>46065.699717696756</v>
       </c>
       <c r="C33" s="8">
-        <v>46139.793677395835</v>
+        <v>46139.627010729164</v>
       </c>
       <c r="D33" s="8">
-        <v>46139.79497809028</v>
+        <v>46139.628311423614</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3358,13 +3358,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46065.86638475694</v>
+        <v>46065.699718090276</v>
       </c>
       <c r="C34" s="5">
-        <v>46155.89155255787</v>
+        <v>46155.724885891206</v>
       </c>
       <c r="D34" s="5">
-        <v>46155.89155403935</v>
+        <v>46155.724887372686</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3419,13 +3419,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46065.866385057874</v>
+        <v>46065.6997183912</v>
       </c>
       <c r="C35" s="8">
-        <v>46174.6530503588</v>
+        <v>46174.48638369213</v>
       </c>
       <c r="D35" s="8">
-        <v>46174.65306150463</v>
+        <v>46174.486394837964</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3484,13 +3484,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46065.866385347224</v>
+        <v>46065.69971868055</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.55406501157</v>
+        <v>46097.38739834491</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.84157347222</v>
+        <v>46169.67490680555</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3545,13 +3545,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46065.866385636575</v>
+        <v>46065.6997189699</v>
       </c>
       <c r="C37" s="8">
-        <v>46174.652990393515</v>
+        <v>46174.48632372685</v>
       </c>
       <c r="D37" s="8">
-        <v>46174.652992372685</v>
+        <v>46174.48632570602</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3606,13 +3606,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.8663859375</v>
+        <v>46065.69971927084</v>
       </c>
       <c r="C38" s="5">
-        <v>46174.653035868054</v>
+        <v>46174.48636920139</v>
       </c>
       <c r="D38" s="5">
-        <v>46174.653037488424</v>
+        <v>46174.48637082176</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3667,13 +3667,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.866386215275</v>
+        <v>46065.69971954861</v>
       </c>
       <c r="C39" s="8">
-        <v>46118.83673671296</v>
+        <v>46118.6700700463</v>
       </c>
       <c r="D39" s="8">
-        <v>46118.83674979166</v>
+        <v>46118.670083125</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3732,13 +3732,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.86638649306</v>
+        <v>46065.699719826385</v>
       </c>
       <c r="C40" s="5">
-        <v>46118.83650719907</v>
+        <v>46118.669840532406</v>
       </c>
       <c r="D40" s="5">
-        <v>46118.83650899306</v>
+        <v>46118.66984232639</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3793,13 +3793,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.86638677084</v>
+        <v>46065.69972010417</v>
       </c>
       <c r="C41" s="8">
-        <v>46118.836723506945</v>
+        <v>46118.670056840274</v>
       </c>
       <c r="D41" s="8">
-        <v>46118.836724988425</v>
+        <v>46118.67005832176</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3854,13 +3854,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46065.86638704861</v>
+        <v>46065.69972038195</v>
       </c>
       <c r="C42" s="5">
-        <v>46118.83891240741</v>
+        <v>46118.672245740745</v>
       </c>
       <c r="D42" s="5">
-        <v>46133.19587135417</v>
+        <v>46133.0292046875</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3919,13 +3919,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.86638668981</v>
+        <v>46065.69972002315</v>
       </c>
       <c r="C43" s="8">
-        <v>46118.83884881945</v>
+        <v>46118.672182152775</v>
       </c>
       <c r="D43" s="8">
-        <v>46118.83885034722</v>
+        <v>46118.67218368055</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3980,13 +3980,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46065.86638707176</v>
+        <v>46065.69972040509</v>
       </c>
       <c r="C44" s="5">
-        <v>46118.838897800924</v>
+        <v>46118.67223113426</v>
       </c>
       <c r="D44" s="5">
-        <v>46118.83889917824</v>
+        <v>46118.67223251157</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4041,11 +4041,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46065.866387372684</v>
+        <v>46065.69972070602</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46107.72587710648</v>
+        <v>46107.55921043982</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4090,13 +4090,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.744155486114</v>
+        <v>46070.57748881944</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.72579283565</v>
+        <v>46107.559126168984</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.725811412034</v>
+        <v>46107.55914474537</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4155,13 +4155,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.86638765046</v>
+        <v>46065.6997209838</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.72585664352</v>
+        <v>46107.55918997685</v>
       </c>
       <c r="D47" s="8">
-        <v>46174.653052037036</v>
+        <v>46174.48638537037</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4220,13 +4220,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46090.74964866898</v>
+        <v>46090.582982002314</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.725927673615</v>
+        <v>46107.55926100694</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.72595083334</v>
+        <v>46107.559284166666</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4285,11 +4285,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46090.74982369213</v>
+        <v>46090.58315702547</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46170.18363959491</v>
+        <v>46170.01697292824</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4348,13 +4348,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.866387939815</v>
+        <v>46065.69972127315</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.635591377315</v>
+        <v>46127.46892471064</v>
       </c>
       <c r="D50" s="5">
-        <v>46127.63560765046</v>
+        <v>46127.468940983796</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4401,13 +4401,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.86638821759</v>
+        <v>46065.699721550925</v>
       </c>
       <c r="C51" s="8">
-        <v>46122.64297173611</v>
+        <v>46122.476305069446</v>
       </c>
       <c r="D51" s="8">
-        <v>46122.64298887731</v>
+        <v>46122.47632221065</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>185</v>
@@ -4466,13 +4466,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.86638849537</v>
+        <v>46065.6997218287</v>
       </c>
       <c r="C52" s="5">
-        <v>46127.635570196755</v>
+        <v>46127.4689035301</v>
       </c>
       <c r="D52" s="5">
-        <v>46127.63559171296</v>
+        <v>46127.4689250463</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4531,13 +4531,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.86638876157</v>
+        <v>46065.69972209491</v>
       </c>
       <c r="C53" s="8">
-        <v>46167.59797371528</v>
+        <v>46167.43130704861</v>
       </c>
       <c r="D53" s="8">
-        <v>46167.59798559028</v>
+        <v>46167.43131892361</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4584,13 +4584,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.8663890162</v>
+        <v>46065.69972234954</v>
       </c>
       <c r="C54" s="5">
-        <v>46167.545010891205</v>
+        <v>46167.37834422453</v>
       </c>
       <c r="D54" s="5">
-        <v>46167.5450264699</v>
+        <v>46167.378359803246</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4649,13 +4649,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.86638931713</v>
+        <v>46065.69972265046</v>
       </c>
       <c r="C55" s="8">
-        <v>46167.59790540509</v>
+        <v>46167.43123873843</v>
       </c>
       <c r="D55" s="8">
-        <v>46167.597926319446</v>
+        <v>46167.431259652774</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4714,13 +4714,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.86638487269</v>
+        <v>46065.699718206015</v>
       </c>
       <c r="C56" s="5">
-        <v>46167.59795763889</v>
+        <v>46167.43129097222</v>
       </c>
       <c r="D56" s="5">
-        <v>46167.59797377315</v>
+        <v>46167.43130710648</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4779,11 +4779,11 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.86638528935</v>
+        <v>46065.69971862268</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46210.61193216435</v>
+        <v>46210.445265497685</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4826,13 +4826,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.866385601854</v>
+        <v>46065.69971893518</v>
       </c>
       <c r="C58" s="5">
-        <v>46198.824122164355</v>
+        <v>46198.65745549768</v>
       </c>
       <c r="D58" s="5">
-        <v>46198.824139675926</v>
+        <v>46198.657473009254</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4891,13 +4891,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.86638590277</v>
+        <v>46065.699719236116</v>
       </c>
       <c r="C59" s="8">
-        <v>46210.61192333333</v>
+        <v>46210.445256666666</v>
       </c>
       <c r="D59" s="8">
-        <v>46210.611941863426</v>
+        <v>46210.44527519676</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4956,13 +4956,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.86638623843</v>
+        <v>46065.699719571756</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.82559879629</v>
+        <v>46198.658932129634</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.82561377315</v>
+        <v>46198.65894710648</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5021,11 +5021,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.86638653935</v>
+        <v>46065.69971987269</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46130.175001006945</v>
+        <v>46130.00833434028</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5084,13 +5084,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.866386828704</v>
+        <v>46065.69972016204</v>
       </c>
       <c r="C62" s="5">
-        <v>46122.64522528935</v>
+        <v>46122.478558622686</v>
       </c>
       <c r="D62" s="5">
-        <v>46143.17235355324</v>
+        <v>46143.00568688658</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -5149,13 +5149,13 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.8663871412</v>
+        <v>46065.69972047454</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.59918284722</v>
+        <v>46197.43251618056</v>
       </c>
       <c r="D63" s="8">
-        <v>46210.640153368055</v>
+        <v>46210.47348670139</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5202,13 +5202,13 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.86638744213</v>
+        <v>46065.69972077546</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.866510844906</v>
+        <v>46195.69984417824</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.86652894676</v>
+        <v>46195.69986228009</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5267,13 +5267,13 @@
         <v>232</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.86638777777</v>
+        <v>46065.699721111116</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.50371587963</v>
+        <v>46197.33704921296</v>
       </c>
       <c r="D65" s="8">
-        <v>46198.82561393519</v>
+        <v>46198.658947268515</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5332,13 +5332,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.86638519676</v>
+        <v>46065.69971853009</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.50377947917</v>
+        <v>46197.3371128125</v>
       </c>
       <c r="D66" s="5">
-        <v>46198.82414078704</v>
+        <v>46198.657474120366</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5397,11 +5397,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.866385601854</v>
+        <v>46065.69971893518</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46211.647106944445</v>
+        <v>46211.48044027778</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5460,13 +5460,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.866385960646</v>
+        <v>46065.69971929398</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.607128483796</v>
+        <v>46197.440461817125</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.60726340278</v>
+        <v>46197.44059673611</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5525,11 +5525,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.86638626158</v>
+        <v>46065.69971959491</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46210.640152928245</v>
+        <v>46210.47348626157</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5586,11 +5586,11 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.8663865625</v>
+        <v>46065.699719895834</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46171.204831423616</v>
+        <v>46171.038164756945</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5647,11 +5647,11 @@
         <v>251</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.866386863425</v>
+        <v>46065.69972019676</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.7553162963</v>
+        <v>46090.58864962963</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>252</v>
@@ -5694,11 +5694,11 @@
         <v>254</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.8663871875</v>
+        <v>46065.69972052083</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46210.603462604166</v>
+        <v>46210.4367959375</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>
@@ -5755,11 +5755,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46065.86638747685</v>
+        <v>46065.69972081018</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46177.199266296295</v>
+        <v>46177.03259962963</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5818,11 +5818,11 @@
         <v>263</v>
       </c>
       <c r="B74" s="5">
-        <v>46065.866387766204</v>
+        <v>46065.69972109953</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46178.203143680556</v>
+        <v>46178.036477013884</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5879,11 +5879,11 @@
         <v>268</v>
       </c>
       <c r="B75" s="8">
-        <v>46065.8663881713</v>
+        <v>46065.69972150463</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46179.18502518519</v>
+        <v>46179.018358518515</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>269</v>
@@ -5940,11 +5940,11 @@
         <v>271</v>
       </c>
       <c r="B76" s="5">
-        <v>46065.866384340276</v>
+        <v>46065.69971767361</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.755315567134</v>
+        <v>46090.58864890046</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>272</v>
@@ -5987,11 +5987,11 @@
         <v>274</v>
       </c>
       <c r="B77" s="8">
-        <v>46065.866385138885</v>
+        <v>46065.69971847222</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46190.20534189815</v>
+        <v>46190.03867523148</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>275</v>
@@ -6050,11 +6050,11 @@
         <v>279</v>
       </c>
       <c r="B78" s="5">
-        <v>46065.866385416666</v>
+        <v>46065.699718749995</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46190.205348206015</v>
+        <v>46190.03868153935</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>280</v>
@@ -6113,11 +6113,11 @@
         <v>281</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.75000248842</v>
+        <v>46090.583335821764</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.75636387731</v>
+        <v>46090.58969721065</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>282</v>
@@ -6166,11 +6166,11 @@
         <v>284</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.75028462963</v>
+        <v>46090.58361796296</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46190.205342534726</v>
+        <v>46190.038675868054</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>285</v>
@@ -6229,11 +6229,11 @@
         <v>287</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.75057857639</v>
+        <v>46090.58391190972</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46199.19411842593</v>
+        <v>46199.02745175926</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -1504,13 +1504,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46065.69972041667</v>
+        <v>46065.86638708333</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55529023148</v>
+        <v>46092.72195689815</v>
       </c>
       <c r="D4" s="5">
-        <v>46133.603651701385</v>
+        <v>46133.77031836806</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1553,13 +1553,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46065.69972087963</v>
+        <v>46065.866387546295</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.555256886575</v>
+        <v>46092.72192355324</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55529099537</v>
+        <v>46092.72195766204</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1618,13 +1618,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46065.69972138889</v>
+        <v>46065.866388055554</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55525744213</v>
+        <v>46092.721924108795</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55529188657</v>
+        <v>46092.721958553244</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1683,13 +1683,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46065.69972192129</v>
+        <v>46065.866388587965</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55525792824</v>
+        <v>46092.72192459491</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.555291296296</v>
+        <v>46092.72195796296</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1748,13 +1748,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46065.69972236111</v>
+        <v>46065.86638902778</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55525841435</v>
+        <v>46092.721925081016</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.6233396412</v>
+        <v>46100.79000630787</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1813,13 +1813,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46065.69972283565</v>
+        <v>46065.86638950232</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55525921297</v>
+        <v>46092.721925879625</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55529192129</v>
+        <v>46092.721958587965</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1878,11 +1878,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46065.69972333334</v>
+        <v>46065.866389999996</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46097.3876528588</v>
+        <v>46097.55431952546</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1925,13 +1925,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46065.699723680555</v>
+        <v>46065.86639034722</v>
       </c>
       <c r="C11" s="8">
-        <v>46097.38764217593</v>
+        <v>46097.55430884259</v>
       </c>
       <c r="D11" s="8">
-        <v>46097.38766100694</v>
+        <v>46097.55432767361</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1990,11 +1990,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46065.69972405092</v>
+        <v>46065.866390717594</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46137.026501875</v>
+        <v>46137.193168541664</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2053,13 +2053,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46065.69972444444</v>
+        <v>46065.86639111111</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.35589099537</v>
+        <v>46114.522557662036</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.35590498842</v>
+        <v>46114.52257165509</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2106,13 +2106,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46065.6997184375</v>
+        <v>46065.866385104164</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.38671878472</v>
+        <v>46097.55338545139</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.386736678236</v>
+        <v>46097.55340334491</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2171,13 +2171,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46065.69972413195</v>
+        <v>46065.86639079861</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.557669560185</v>
+        <v>46107.72433622685</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.55768900463</v>
+        <v>46107.72435567129</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2236,13 +2236,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46065.6997255787</v>
+        <v>46065.86639224537</v>
       </c>
       <c r="C16" s="5">
-        <v>46107.55771945602</v>
+        <v>46107.72438612269</v>
       </c>
       <c r="D16" s="5">
-        <v>46107.55773701389</v>
+        <v>46107.72440368056</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2301,13 +2301,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46065.69972638889</v>
+        <v>46065.866393055556</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.35587568287</v>
+        <v>46114.522542349536</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.35589112269</v>
+        <v>46114.52255778935</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2366,13 +2366,13 @@
         <v>73</v>
       </c>
       <c r="B18" s="5">
-        <v>46065.69972674768</v>
+        <v>46065.866393414355</v>
       </c>
       <c r="C18" s="5">
-        <v>46114.35593553241</v>
+        <v>46114.522602199075</v>
       </c>
       <c r="D18" s="5">
-        <v>46114.355957997686</v>
+        <v>46114.52262466435</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>74</v>
@@ -2419,13 +2419,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="8">
-        <v>46065.69972708334</v>
+        <v>46065.866393749995</v>
       </c>
       <c r="C19" s="8">
-        <v>46097.386754328705</v>
+        <v>46097.55342099537</v>
       </c>
       <c r="D19" s="8">
-        <v>46097.387491747686</v>
+        <v>46097.55415841435</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>77</v>
@@ -2484,13 +2484,13 @@
         <v>79</v>
       </c>
       <c r="B20" s="5">
-        <v>46065.69972747685</v>
+        <v>46065.86639414352</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.38667216436</v>
+        <v>46097.553338831014</v>
       </c>
       <c r="D20" s="5">
-        <v>46107.55769261574</v>
+        <v>46107.72435928241</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>80</v>
@@ -2549,13 +2549,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46065.69972790509</v>
+        <v>46065.866394571756</v>
       </c>
       <c r="C21" s="8">
-        <v>46097.38769659722</v>
+        <v>46097.55436326389</v>
       </c>
       <c r="D21" s="8">
-        <v>46097.38771902778</v>
+        <v>46097.55438569444</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2614,13 +2614,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46065.69972824074</v>
+        <v>46065.86639490741</v>
       </c>
       <c r="C22" s="5">
-        <v>46113.393608240745</v>
+        <v>46113.5602749074</v>
       </c>
       <c r="D22" s="5">
-        <v>46113.39361032407</v>
+        <v>46113.56027699074</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2679,13 +2679,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46065.699718703705</v>
+        <v>46065.86638537037</v>
       </c>
       <c r="C23" s="8">
-        <v>46114.35591884259</v>
+        <v>46114.52258550926</v>
       </c>
       <c r="D23" s="8">
-        <v>46114.35640158565</v>
+        <v>46114.52306825231</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2744,13 +2744,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46065.6997191088</v>
+        <v>46065.86638577546</v>
       </c>
       <c r="C24" s="5">
-        <v>46107.55799318287</v>
+        <v>46107.72465984954</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.55801064815</v>
+        <v>46107.724677314814</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2809,11 +2809,11 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46065.69971940972</v>
+        <v>46065.86638607639</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46174.486404282405</v>
+        <v>46174.653070949076</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2858,13 +2858,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46065.69971969907</v>
+        <v>46065.86638636574</v>
       </c>
       <c r="C26" s="5">
-        <v>46155.709235937495</v>
+        <v>46155.875902604166</v>
       </c>
       <c r="D26" s="5">
-        <v>46155.70925018519</v>
+        <v>46155.87591685185</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2923,13 +2923,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46065.69972001157</v>
+        <v>46065.866386678244</v>
       </c>
       <c r="C27" s="8">
-        <v>46097.38682175926</v>
+        <v>46097.553488425925</v>
       </c>
       <c r="D27" s="8">
-        <v>46097.3868233449</v>
+        <v>46097.553490011574</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2984,13 +2984,13 @@
         <v>110</v>
       </c>
       <c r="B28" s="5">
-        <v>46065.69972030092</v>
+        <v>46065.866386967595</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.709218055556</v>
+        <v>46155.87588472222</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.70921930556</v>
+        <v>46155.87588597222</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>111</v>
@@ -3045,13 +3045,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46065.69972059027</v>
+        <v>46065.866387256945</v>
       </c>
       <c r="C29" s="8">
-        <v>46122.47842777778</v>
+        <v>46122.645094444444</v>
       </c>
       <c r="D29" s="8">
-        <v>46128.01609658565</v>
+        <v>46128.18276325232</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3110,13 +3110,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46065.699720902776</v>
+        <v>46065.86638756945</v>
       </c>
       <c r="C30" s="5">
-        <v>46097.38788888889</v>
+        <v>46097.55455555556</v>
       </c>
       <c r="D30" s="5">
-        <v>46097.3878903588</v>
+        <v>46097.55455702546</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3171,13 +3171,13 @@
         <v>119</v>
       </c>
       <c r="B31" s="8">
-        <v>46065.6997212037</v>
+        <v>46065.86638787037</v>
       </c>
       <c r="C31" s="8">
-        <v>46122.47841251157</v>
+        <v>46122.64507917824</v>
       </c>
       <c r="D31" s="8">
-        <v>46122.47841388889</v>
+        <v>46122.64508055555</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>120</v>
@@ -3232,13 +3232,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="5">
-        <v>46065.69972150463</v>
+        <v>46065.8663881713</v>
       </c>
       <c r="C32" s="5">
-        <v>46155.72490068287</v>
+        <v>46155.891567349536</v>
       </c>
       <c r="D32" s="5">
-        <v>46155.724920231485</v>
+        <v>46155.89158689815</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3297,13 +3297,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46065.699717696756</v>
+        <v>46065.86638436343</v>
       </c>
       <c r="C33" s="8">
-        <v>46139.627010729164</v>
+        <v>46139.793677395835</v>
       </c>
       <c r="D33" s="8">
-        <v>46139.628311423614</v>
+        <v>46139.79497809028</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3358,13 +3358,13 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46065.699718090276</v>
+        <v>46065.86638475694</v>
       </c>
       <c r="C34" s="5">
-        <v>46155.724885891206</v>
+        <v>46155.89155255787</v>
       </c>
       <c r="D34" s="5">
-        <v>46155.724887372686</v>
+        <v>46155.89155403935</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3419,13 +3419,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46065.6997183912</v>
+        <v>46065.866385057874</v>
       </c>
       <c r="C35" s="8">
-        <v>46174.48638369213</v>
+        <v>46174.6530503588</v>
       </c>
       <c r="D35" s="8">
-        <v>46174.486394837964</v>
+        <v>46174.65306150463</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -3484,13 +3484,13 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46065.69971868055</v>
+        <v>46065.866385347224</v>
       </c>
       <c r="C36" s="5">
-        <v>46097.38739834491</v>
+        <v>46097.55406501157</v>
       </c>
       <c r="D36" s="5">
-        <v>46169.67490680555</v>
+        <v>46169.84157347222</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -3545,13 +3545,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46065.6997189699</v>
+        <v>46065.866385636575</v>
       </c>
       <c r="C37" s="8">
-        <v>46174.48632372685</v>
+        <v>46174.652990393515</v>
       </c>
       <c r="D37" s="8">
-        <v>46174.48632570602</v>
+        <v>46174.652992372685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -3606,13 +3606,13 @@
         <v>140</v>
       </c>
       <c r="B38" s="5">
-        <v>46065.69971927084</v>
+        <v>46065.8663859375</v>
       </c>
       <c r="C38" s="5">
-        <v>46174.48636920139</v>
+        <v>46174.653035868054</v>
       </c>
       <c r="D38" s="5">
-        <v>46174.48637082176</v>
+        <v>46174.653037488424</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>141</v>
@@ -3667,13 +3667,13 @@
         <v>143</v>
       </c>
       <c r="B39" s="8">
-        <v>46065.69971954861</v>
+        <v>46065.866386215275</v>
       </c>
       <c r="C39" s="8">
-        <v>46118.6700700463</v>
+        <v>46118.83673671296</v>
       </c>
       <c r="D39" s="8">
-        <v>46118.670083125</v>
+        <v>46118.83674979166</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>144</v>
@@ -3732,13 +3732,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46065.699719826385</v>
+        <v>46065.86638649306</v>
       </c>
       <c r="C40" s="5">
-        <v>46118.669840532406</v>
+        <v>46118.83650719907</v>
       </c>
       <c r="D40" s="5">
-        <v>46118.66984232639</v>
+        <v>46118.83650899306</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>149</v>
@@ -3793,13 +3793,13 @@
         <v>151</v>
       </c>
       <c r="B41" s="8">
-        <v>46065.69972010417</v>
+        <v>46065.86638677084</v>
       </c>
       <c r="C41" s="8">
-        <v>46118.670056840274</v>
+        <v>46118.836723506945</v>
       </c>
       <c r="D41" s="8">
-        <v>46118.67005832176</v>
+        <v>46118.836724988425</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>152</v>
@@ -3854,13 +3854,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46065.69972038195</v>
+        <v>46065.86638704861</v>
       </c>
       <c r="C42" s="5">
-        <v>46118.672245740745</v>
+        <v>46118.83891240741</v>
       </c>
       <c r="D42" s="5">
-        <v>46133.0292046875</v>
+        <v>46133.19587135417</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>155</v>
@@ -3919,13 +3919,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46065.69972002315</v>
+        <v>46065.86638668981</v>
       </c>
       <c r="C43" s="8">
-        <v>46118.672182152775</v>
+        <v>46118.83884881945</v>
       </c>
       <c r="D43" s="8">
-        <v>46118.67218368055</v>
+        <v>46118.83885034722</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3980,13 +3980,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46065.69972040509</v>
+        <v>46065.86638707176</v>
       </c>
       <c r="C44" s="5">
-        <v>46118.67223113426</v>
+        <v>46118.838897800924</v>
       </c>
       <c r="D44" s="5">
-        <v>46118.67223251157</v>
+        <v>46118.83889917824</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4041,11 +4041,11 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46065.69972070602</v>
+        <v>46065.866387372684</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46107.55921043982</v>
+        <v>46107.72587710648</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4090,13 +4090,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46070.57748881944</v>
+        <v>46070.744155486114</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.559126168984</v>
+        <v>46107.72579283565</v>
       </c>
       <c r="D46" s="5">
-        <v>46107.55914474537</v>
+        <v>46107.725811412034</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4155,13 +4155,13 @@
         <v>171</v>
       </c>
       <c r="B47" s="8">
-        <v>46065.6997209838</v>
+        <v>46065.86638765046</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.55918997685</v>
+        <v>46107.72585664352</v>
       </c>
       <c r="D47" s="8">
-        <v>46174.48638537037</v>
+        <v>46174.653052037036</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>166</v>
@@ -4220,13 +4220,13 @@
         <v>174</v>
       </c>
       <c r="B48" s="5">
-        <v>46090.582982002314</v>
+        <v>46090.74964866898</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.55926100694</v>
+        <v>46107.725927673615</v>
       </c>
       <c r="D48" s="5">
-        <v>46107.559284166666</v>
+        <v>46107.72595083334</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>175</v>
@@ -4285,11 +4285,11 @@
         <v>177</v>
       </c>
       <c r="B49" s="8">
-        <v>46090.58315702547</v>
+        <v>46090.74982369213</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46170.01697292824</v>
+        <v>46170.18363959491</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>178</v>
@@ -4348,13 +4348,13 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46065.69972127315</v>
+        <v>46065.866387939815</v>
       </c>
       <c r="C50" s="5">
-        <v>46127.46892471064</v>
+        <v>46127.635591377315</v>
       </c>
       <c r="D50" s="5">
-        <v>46127.468940983796</v>
+        <v>46127.63560765046</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4401,13 +4401,13 @@
         <v>186</v>
       </c>
       <c r="B51" s="8">
-        <v>46065.699721550925</v>
+        <v>46065.86638821759</v>
       </c>
       <c r="C51" s="8">
-        <v>46122.476305069446</v>
+        <v>46122.64297173611</v>
       </c>
       <c r="D51" s="8">
-        <v>46122.47632221065</v>
+        <v>46122.64298887731</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>185</v>
@@ -4466,13 +4466,13 @@
         <v>190</v>
       </c>
       <c r="B52" s="5">
-        <v>46065.6997218287</v>
+        <v>46065.86638849537</v>
       </c>
       <c r="C52" s="5">
-        <v>46127.4689035301</v>
+        <v>46127.635570196755</v>
       </c>
       <c r="D52" s="5">
-        <v>46127.4689250463</v>
+        <v>46127.63559171296</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>191</v>
@@ -4531,13 +4531,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46065.69972209491</v>
+        <v>46065.86638876157</v>
       </c>
       <c r="C53" s="8">
-        <v>46167.43130704861</v>
+        <v>46167.59797371528</v>
       </c>
       <c r="D53" s="8">
-        <v>46167.43131892361</v>
+        <v>46167.59798559028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4584,13 +4584,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46065.69972234954</v>
+        <v>46065.8663890162</v>
       </c>
       <c r="C54" s="5">
-        <v>46167.37834422453</v>
+        <v>46167.545010891205</v>
       </c>
       <c r="D54" s="5">
-        <v>46167.378359803246</v>
+        <v>46167.5450264699</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4649,13 +4649,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46065.69972265046</v>
+        <v>46065.86638931713</v>
       </c>
       <c r="C55" s="8">
-        <v>46167.43123873843</v>
+        <v>46167.59790540509</v>
       </c>
       <c r="D55" s="8">
-        <v>46167.431259652774</v>
+        <v>46167.597926319446</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4714,13 +4714,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46065.699718206015</v>
+        <v>46065.86638487269</v>
       </c>
       <c r="C56" s="5">
-        <v>46167.43129097222</v>
+        <v>46167.59795763889</v>
       </c>
       <c r="D56" s="5">
-        <v>46167.43130710648</v>
+        <v>46167.59797377315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4779,11 +4779,11 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.69971862268</v>
+        <v>46065.86638528935</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46210.445265497685</v>
+        <v>46210.61193216435</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -4826,13 +4826,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46065.69971893518</v>
+        <v>46065.866385601854</v>
       </c>
       <c r="C58" s="5">
-        <v>46198.65745549768</v>
+        <v>46198.824122164355</v>
       </c>
       <c r="D58" s="5">
-        <v>46198.657473009254</v>
+        <v>46198.824139675926</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4891,13 +4891,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46065.699719236116</v>
+        <v>46065.86638590277</v>
       </c>
       <c r="C59" s="8">
-        <v>46210.445256666666</v>
+        <v>46210.61192333333</v>
       </c>
       <c r="D59" s="8">
-        <v>46210.44527519676</v>
+        <v>46210.611941863426</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4956,13 +4956,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46065.699719571756</v>
+        <v>46065.86638623843</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.658932129634</v>
+        <v>46198.82559879629</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.65894710648</v>
+        <v>46198.82561377315</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5021,11 +5021,11 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46065.69971987269</v>
+        <v>46065.86638653935</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46130.00833434028</v>
+        <v>46130.175001006945</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5084,13 +5084,13 @@
         <v>223</v>
       </c>
       <c r="B62" s="5">
-        <v>46065.69972016204</v>
+        <v>46065.866386828704</v>
       </c>
       <c r="C62" s="5">
-        <v>46122.478558622686</v>
+        <v>46122.64522528935</v>
       </c>
       <c r="D62" s="5">
-        <v>46143.00568688658</v>
+        <v>46143.17235355324</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>224</v>
@@ -5149,13 +5149,13 @@
         <v>226</v>
       </c>
       <c r="B63" s="8">
-        <v>46065.69972047454</v>
+        <v>46065.8663871412</v>
       </c>
       <c r="C63" s="8">
-        <v>46197.43251618056</v>
+        <v>46197.59918284722</v>
       </c>
       <c r="D63" s="8">
-        <v>46210.47348670139</v>
+        <v>46210.640153368055</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5202,13 +5202,13 @@
         <v>229</v>
       </c>
       <c r="B64" s="5">
-        <v>46065.69972077546</v>
+        <v>46065.86638744213</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.69984417824</v>
+        <v>46195.866510844906</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.69986228009</v>
+        <v>46195.86652894676</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>230</v>
@@ -5267,13 +5267,13 @@
         <v>232</v>
       </c>
       <c r="B65" s="8">
-        <v>46065.699721111116</v>
+        <v>46065.86638777777</v>
       </c>
       <c r="C65" s="8">
-        <v>46197.33704921296</v>
+        <v>46197.50371587963</v>
       </c>
       <c r="D65" s="8">
-        <v>46198.658947268515</v>
+        <v>46198.82561393519</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>233</v>
@@ -5332,13 +5332,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46065.69971853009</v>
+        <v>46065.86638519676</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.3371128125</v>
+        <v>46197.50377947917</v>
       </c>
       <c r="D66" s="5">
-        <v>46198.657474120366</v>
+        <v>46198.82414078704</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5397,11 +5397,11 @@
         <v>240</v>
       </c>
       <c r="B67" s="8">
-        <v>46065.69971893518</v>
+        <v>46065.866385601854</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46211.48044027778</v>
+        <v>46211.647106944445</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5460,13 +5460,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46065.69971929398</v>
+        <v>46065.866385960646</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.440461817125</v>
+        <v>46197.607128483796</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.44059673611</v>
+        <v>46197.60726340278</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5525,11 +5525,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46065.69971959491</v>
+        <v>46065.86638626158</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46210.47348626157</v>
+        <v>46210.640152928245</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5586,11 +5586,11 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46065.699719895834</v>
+        <v>46065.8663865625</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46171.038164756945</v>
+        <v>46171.204831423616</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5647,11 +5647,11 @@
         <v>251</v>
       </c>
       <c r="B71" s="8">
-        <v>46065.69972019676</v>
+        <v>46065.866386863425</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.58864962963</v>
+        <v>46090.7553162963</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>252</v>
@@ -5694,11 +5694,11 @@
         <v>254</v>
       </c>
       <c r="B72" s="5">
-        <v>46065.69972052083</v>
+        <v>46065.8663871875</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46210.4367959375</v>
+        <v>46210.603462604166</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>
@@ -5755,11 +5755,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46065.69972081018</v>
+        <v>46065.86638747685</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46177.03259962963</v>
+        <v>46177.199266296295</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5818,11 +5818,11 @@
         <v>263</v>
       </c>
       <c r="B74" s="5">
-        <v>46065.69972109953</v>
+        <v>46065.866387766204</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46178.036477013884</v>
+        <v>46178.203143680556</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5879,11 +5879,11 @@
         <v>268</v>
       </c>
       <c r="B75" s="8">
-        <v>46065.69972150463</v>
+        <v>46065.8663881713</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46179.018358518515</v>
+        <v>46179.18502518519</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>269</v>
@@ -5940,11 +5940,11 @@
         <v>271</v>
       </c>
       <c r="B76" s="5">
-        <v>46065.69971767361</v>
+        <v>46065.866384340276</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46090.58864890046</v>
+        <v>46090.755315567134</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>272</v>
@@ -5987,11 +5987,11 @@
         <v>274</v>
       </c>
       <c r="B77" s="8">
-        <v>46065.69971847222</v>
+        <v>46065.866385138885</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46190.03867523148</v>
+        <v>46190.20534189815</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>275</v>
@@ -6050,11 +6050,11 @@
         <v>279</v>
       </c>
       <c r="B78" s="5">
-        <v>46065.699718749995</v>
+        <v>46065.866385416666</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46190.03868153935</v>
+        <v>46190.205348206015</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>280</v>
@@ -6113,11 +6113,11 @@
         <v>281</v>
       </c>
       <c r="B79" s="8">
-        <v>46090.583335821764</v>
+        <v>46090.75000248842</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46090.58969721065</v>
+        <v>46090.75636387731</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>282</v>
@@ -6166,11 +6166,11 @@
         <v>284</v>
       </c>
       <c r="B80" s="5">
-        <v>46090.58361796296</v>
+        <v>46090.75028462963</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46190.038675868054</v>
+        <v>46190.205342534726</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>285</v>
@@ -6229,11 +6229,11 @@
         <v>287</v>
       </c>
       <c r="B81" s="8">
-        <v>46090.58391190972</v>
+        <v>46090.75057857639</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46199.02745175926</v>
+        <v>46199.19411842593</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>288</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -175,10 +175,10 @@
     <t>Revision tableros pruebas</t>
   </si>
   <si>
-    <t>Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>Ingenieria de servicio:,Embalaje</t>
+    <t xml:space="preserve"> 4197-4198 Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>Ingenieria de servicio:,ot 4196 - 4197-4198 Embalaje</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -376,7 +376,7 @@
     <t>Fabricación Tablero</t>
   </si>
   <si>
-    <t>Tablero,Recepcion Tableros</t>
+    <t>Tablero, 4197-4198 Recepcion Tableros</t>
   </si>
   <si>
     <t>1213249277752978</t>
@@ -541,7 +541,7 @@
     <t>Check Planos</t>
   </si>
   <si>
-    <t>Armado FABRICACIÓN EXTERNA ,Control de calidad Armado,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensores y accesorios</t>
+    <t>Armado FABRICACIÓN EXTERNA ,Control de calidad Armado,Montaje motor,Montaje Alabe,ot 4196 Montaje Rodete,Montaje sensores y accesorios</t>
   </si>
   <si>
     <t>1213575386156441</t>
@@ -556,10 +556,10 @@
     <t>francisca.gonzalez@zitron.com</t>
   </si>
   <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
+    <t>ot 4196 Pruebas FAT</t>
+  </si>
+  <si>
+    <t>ot 4196 RE-PINTADO</t>
   </si>
   <si>
     <t>1213249277752993</t>
@@ -646,7 +646,7 @@
     <t>1213249277753000</t>
   </si>
   <si>
-    <t>Recepcion Alabe,Recepcion Rodete,Recepcion Motor,Recepcion Tableros,Recepcion sensores y accesorios</t>
+    <t>Recepcion Alabe,Recepcion Rodete,Recepcion Motor, 4197-4198 Recepcion Tableros,Recepcion sensores y accesorios</t>
   </si>
   <si>
     <t>1213249277753001</t>
@@ -664,7 +664,7 @@
     <t>Recepcion Rodete</t>
   </si>
   <si>
-    <t>Bodega:,Montaje Rodete</t>
+    <t>Bodega:,ot 4196 Montaje Rodete</t>
   </si>
   <si>
     <t>1213249277753003</t>
@@ -697,7 +697,7 @@
     <t>Montaje:</t>
   </si>
   <si>
-    <t>Revestimiento,Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensores y accesorios,Pruebas FAT,RE-PINTADO</t>
+    <t>Revestimiento,Montaje motor,Montaje Alabe,ot 4196 Montaje Rodete,Montaje sensores y accesorios,ot 4196 Pruebas FAT,ot 4196 RE-PINTADO</t>
   </si>
   <si>
     <t>1213249277753007</t>
@@ -706,7 +706,7 @@
     <t>Revestimiento</t>
   </si>
   <si>
-    <t>Montaje Alabe,Montaje Rodete,Montaje:</t>
+    <t>Montaje Alabe,ot 4196 Montaje Rodete,Montaje:</t>
   </si>
   <si>
     <t>1213249277753008</t>
@@ -718,7 +718,7 @@
     <t>Revestimiento,Recepcion Motor,Check Planos</t>
   </si>
   <si>
-    <t>Pruebas FAT,Montaje:</t>
+    <t>ot 4196 Pruebas FAT,Montaje:</t>
   </si>
   <si>
     <t>1213249277753009</t>
@@ -730,13 +730,13 @@
     <t>Recepcion Alabe,Revestimiento,Check Planos</t>
   </si>
   <si>
-    <t>Pruebas FAT,Montaje:,Montaje Rodete</t>
+    <t>ot 4196 Pruebas FAT,Montaje:,ot 4196 Montaje Rodete</t>
   </si>
   <si>
     <t>1213249277753010</t>
   </si>
   <si>
-    <t>Montaje Rodete</t>
+    <t>ot 4196 Montaje Rodete</t>
   </si>
   <si>
     <t>Recepcion Rodete,Revestimiento,Montaje Alabe,Check Planos</t>
@@ -754,7 +754,7 @@
     <t>1213249277753012</t>
   </si>
   <si>
-    <t>Montaje motor,Montaje Alabe,Montaje Rodete,Montaje sensores y accesorios</t>
+    <t>Montaje motor,Montaje Alabe,ot 4196 Montaje Rodete,Montaje sensores y accesorios</t>
   </si>
   <si>
     <t>Montaje:,Check pruebas FAT</t>
@@ -763,7 +763,7 @@
     <t>1213249277753013</t>
   </si>
   <si>
-    <t>Coordinacion Entrega con Cliente,Montaje:</t>
+    <t>ot 4196 - 4197-4198 Coordinacion Entrega con Cliente,Montaje:</t>
   </si>
   <si>
     <t>1213249277753014</t>
@@ -772,13 +772,13 @@
     <t>Logistica:</t>
   </si>
   <si>
-    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
+    <t>ot 4196 - 4197-4198 Coordinacion Entrega con Cliente,ot 4196 - 4197-4198 Embalaje,ot 4196 - 4197-4198 PACKING LIST,ot 4196 - 4197-4198 Despacho</t>
   </si>
   <si>
     <t>1213249277753015</t>
   </si>
   <si>
-    <t>Coordinacion Entrega con Cliente</t>
+    <t>ot 4196 - 4197-4198 Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>Karin Pinto</t>
@@ -787,25 +787,25 @@
     <t>kpinto@zitron.com</t>
   </si>
   <si>
-    <t>Embalaje,Logistica:</t>
+    <t>ot 4196 - 4197-4198 Embalaje,Logistica:</t>
   </si>
   <si>
     <t>1213249277753016</t>
   </si>
   <si>
-    <t>Embalaje</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Revision tableros pruebas</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Logistica:</t>
+    <t>ot 4196 - 4197-4198 Embalaje</t>
+  </si>
+  <si>
+    <t>ot 4196 - 4197-4198 Coordinacion Entrega con Cliente,Revision tableros pruebas</t>
+  </si>
+  <si>
+    <t>ot 4196 - 4197-4198 PACKING LIST,Logistica:</t>
   </si>
   <si>
     <t>1213249277753017</t>
   </si>
   <si>
-    <t>PACKING LIST</t>
+    <t>ot 4196 - 4197-4198 PACKING LIST</t>
   </si>
   <si>
     <t>Nicolás Mol</t>
@@ -814,13 +814,13 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>Despacho,Logistica:</t>
+    <t>ot 4196 - 4197-4198 Despacho,Logistica:</t>
   </si>
   <si>
     <t>1213249277753018</t>
   </si>
   <si>
-    <t>Despacho</t>
+    <t>ot 4196 - 4197-4198 Despacho</t>
   </si>
   <si>
     <t>Costos,Gestion,Logistica:,Logistica:,instalación Componentes</t>
@@ -847,7 +847,7 @@
     <t>nicolas.tello@zitron.com</t>
   </si>
   <si>
-    <t>Despacho,Analisis de costeo</t>
+    <t>ot 4196 - 4197-4198 Despacho,Analisis de costeo</t>
   </si>
   <si>
     <t>1213249277753022</t>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46137.193168541664</v>
+        <v>46212.62892070602</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46210.61193216435</v>
+        <v>46212.6289187963</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>184</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46130.175001006945</v>
+        <v>46212.62895899305</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>54</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46211.647106944445</v>
+        <v>46212.628313912035</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46210.640152928245</v>
+        <v>46212.62834962963</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46171.204831423616</v>
+        <v>46212.6283765625</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>182</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46210.603462604166</v>
+        <v>46212.62862773148</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>255</v>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46177.199266296295</v>
+        <v>46212.62856337963</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46178.203143680556</v>
+        <v>46212.62864408565</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46179.18502518519</v>
+        <v>46212.62866971065</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>269</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -5155,7 +5155,7 @@
         <v>46197.59918284722</v>
       </c>
       <c r="D63" s="8">
-        <v>46210.640153368055</v>
+        <v>46213.50833928241</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>227</v>
@@ -5399,9 +5399,11 @@
       <c r="B67" s="8">
         <v>46065.866385601854</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="8">
+        <v>46213.50832861111</v>
+      </c>
       <c r="D67" s="8">
-        <v>46212.628313912035</v>
+        <v>46213.508331516205</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5529,7 +5531,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46212.62834962963</v>
+        <v>46213.508337974534</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>181</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="286">
   <si>
     <t xml:space="preserve">50001497 - XEMORTIZ IMMSA STA. BBR  </t>
   </si>
@@ -277,9 +277,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
   </si>
   <si>
@@ -296,12 +293,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales</t>
@@ -2629,11 +2620,9 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="5">
         <v>46017</v>
       </c>
@@ -2656,7 +2645,7 @@
         <v>64</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q22" s="5">
         <v>46017</v>
@@ -2676,7 +2665,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B23" s="8">
         <v>46065.86638537037</v>
@@ -2688,7 +2677,7 @@
         <v>46114.52306825231</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2721,7 +2710,7 @@
         <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="8">
         <v>46017</v>
@@ -2741,7 +2730,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
         <v>46065.86638577546</v>
@@ -2753,17 +2742,15 @@
         <v>46107.724677314814</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>96</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H24" s="6"/>
       <c r="I24" s="5">
         <v>46017</v>
       </c>
@@ -2786,7 +2773,7 @@
         <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Q24" s="5">
         <v>46017</v>
@@ -2806,7 +2793,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B25" s="8">
         <v>46065.86638607639</v>
@@ -2816,7 +2803,7 @@
         <v>46174.653070949076</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2840,7 +2827,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2855,7 +2842,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B26" s="5">
         <v>46065.86638636574</v>
@@ -2867,16 +2854,16 @@
         <v>46155.87591685185</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I26" s="5">
         <v>46030</v>
@@ -2894,13 +2881,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q26" s="5">
         <v>46030</v>
@@ -2920,7 +2907,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B27" s="8">
         <v>46065.866386678244</v>
@@ -2932,16 +2919,16 @@
         <v>46097.553490011574</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I27" s="8">
         <v>46030</v>
@@ -2959,13 +2946,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2976,12 +2963,12 @@
         <v>56</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B28" s="5">
         <v>46065.866386967595</v>
@@ -2993,16 +2980,16 @@
         <v>46155.87588597222</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I28" s="5">
         <v>46034</v>
@@ -3020,13 +3007,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3037,12 +3024,12 @@
         <v>56</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B29" s="8">
         <v>46065.866387256945</v>
@@ -3054,16 +3041,16 @@
         <v>46128.18276325232</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I29" s="8">
         <v>46021</v>
@@ -3081,13 +3068,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q29" s="8">
         <v>46021</v>
@@ -3107,7 +3094,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5">
         <v>46065.86638756945</v>
@@ -3119,16 +3106,16 @@
         <v>46097.55455702546</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I30" s="5">
         <v>46021</v>
@@ -3146,13 +3133,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3163,12 +3150,12 @@
         <v>56</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B31" s="8">
         <v>46065.86638787037</v>
@@ -3180,16 +3167,16 @@
         <v>46122.64508055555</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I31" s="8">
         <v>46030</v>
@@ -3207,13 +3194,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="O31" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="O31" s="9" t="s">
-        <v>117</v>
-      </c>
       <c r="P31" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3224,12 +3211,12 @@
         <v>56</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B32" s="5">
         <v>46065.8663881713</v>
@@ -3241,16 +3228,16 @@
         <v>46155.89158689815</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I32" s="5">
         <v>46030</v>
@@ -3268,13 +3255,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q32" s="5">
         <v>46030</v>
@@ -3294,7 +3281,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B33" s="8">
         <v>46065.86638436343</v>
@@ -3306,16 +3293,16 @@
         <v>46139.79497809028</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I33" s="8">
         <v>46030</v>
@@ -3333,13 +3320,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>87</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3350,12 +3337,12 @@
         <v>56</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46065.86638475694</v>
@@ -3367,16 +3354,16 @@
         <v>46155.89155403935</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I34" s="5">
         <v>46034</v>
@@ -3394,13 +3381,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="O34" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="O34" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3411,12 +3398,12 @@
         <v>56</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B35" s="8">
         <v>46065.866385057874</v>
@@ -3428,16 +3415,16 @@
         <v>46174.65306150463</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I35" s="8">
         <v>46013</v>
@@ -3455,13 +3442,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q35" s="8">
         <v>46013</v>
@@ -3481,7 +3468,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46065.866385347224</v>
@@ -3493,16 +3480,16 @@
         <v>46169.84157347222</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I36" s="5">
         <v>46013</v>
@@ -3520,13 +3507,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3537,12 +3524,12 @@
         <v>56</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B37" s="8">
         <v>46065.866385636575</v>
@@ -3554,16 +3541,16 @@
         <v>46174.652992372685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I37" s="8">
         <v>46036</v>
@@ -3581,13 +3568,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="O37" s="9" t="s">
-        <v>135</v>
-      </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3598,12 +3585,12 @@
         <v>56</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46065.8663859375</v>
@@ -3615,16 +3602,16 @@
         <v>46174.653037488424</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I38" s="5">
         <v>46036</v>
@@ -3642,13 +3629,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="O38" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="O38" s="6" t="s">
-        <v>135</v>
-      </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3659,12 +3646,12 @@
         <v>56</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B39" s="8">
         <v>46065.866386215275</v>
@@ -3676,16 +3663,16 @@
         <v>46118.83674979166</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I39" s="8">
         <v>46030</v>
@@ -3703,13 +3690,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q39" s="8">
         <v>46030</v>
@@ -3729,7 +3716,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46065.86638649306</v>
@@ -3741,16 +3728,16 @@
         <v>46118.83650899306</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I40" s="5">
         <v>46030</v>
@@ -3768,13 +3755,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3785,12 +3772,12 @@
         <v>56</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B41" s="8">
         <v>46065.86638677084</v>
@@ -3802,16 +3789,16 @@
         <v>46118.836724988425</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I41" s="8">
         <v>46050</v>
@@ -3829,13 +3816,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3846,12 +3833,12 @@
         <v>56</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5">
         <v>46065.86638704861</v>
@@ -3863,16 +3850,16 @@
         <v>46133.19587135417</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I42" s="5">
         <v>46030</v>
@@ -3890,13 +3877,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q42" s="5">
         <v>46030</v>
@@ -3911,12 +3898,12 @@
         <v>31</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B43" s="8">
         <v>46065.86638668981</v>
@@ -3928,16 +3915,16 @@
         <v>46118.83885034722</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I43" s="8">
         <v>46030</v>
@@ -3955,13 +3942,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3972,12 +3959,12 @@
         <v>56</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46065.86638707176</v>
@@ -3989,16 +3976,16 @@
         <v>46118.83889917824</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I44" s="5">
         <v>46059</v>
@@ -4016,13 +4003,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4033,12 +4020,12 @@
         <v>56</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B45" s="8">
         <v>46065.866387372684</v>
@@ -4048,7 +4035,7 @@
         <v>46107.72587710648</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4072,7 +4059,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4087,7 +4074,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46070.744155486114</v>
@@ -4099,16 +4086,16 @@
         <v>46107.725811412034</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I46" s="5">
         <v>46017</v>
@@ -4126,13 +4113,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="Q46" s="5">
         <v>46017</v>
@@ -4152,7 +4139,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B47" s="8">
         <v>46065.86638765046</v>
@@ -4164,16 +4151,16 @@
         <v>46174.653052037036</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>169</v>
-      </c>
       <c r="H47" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I47" s="8">
         <v>46076</v>
@@ -4191,13 +4178,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="Q47" s="8">
         <v>46076</v>
@@ -4217,7 +4204,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5">
         <v>46090.74964866898</v>
@@ -4229,16 +4216,16 @@
         <v>46107.72595083334</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I48" s="5">
         <v>46083</v>
@@ -4256,13 +4243,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q48" s="5">
         <v>46083</v>
@@ -4282,7 +4269,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B49" s="8">
         <v>46090.74982369213</v>
@@ -4292,16 +4279,16 @@
         <v>46170.18363959491</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I49" s="8">
         <v>46169</v>
@@ -4319,13 +4306,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q49" s="8">
         <v>46169</v>
@@ -4345,7 +4332,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
         <v>46065.866387939815</v>
@@ -4357,7 +4344,7 @@
         <v>46127.63560765046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4381,7 +4368,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4398,7 +4385,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B51" s="8">
         <v>46065.86638821759</v>
@@ -4410,16 +4397,16 @@
         <v>46122.64298887731</v>
       </c>
       <c r="E51" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="I51" s="8">
         <v>46079</v>
@@ -4437,13 +4424,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="8">
         <v>46079</v>
@@ -4463,7 +4450,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46065.86638849537</v>
@@ -4475,16 +4462,16 @@
         <v>46127.63559171296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I52" s="5">
         <v>46083</v>
@@ -4502,13 +4489,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q52" s="5">
         <v>46083</v>
@@ -4528,7 +4515,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B53" s="8">
         <v>46065.86638876157</v>
@@ -4540,7 +4527,7 @@
         <v>46167.59798559028</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4564,7 +4551,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4581,7 +4568,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46065.8663890162</v>
@@ -4593,16 +4580,16 @@
         <v>46167.5450264699</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I54" s="5">
         <v>46085</v>
@@ -4620,13 +4607,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q54" s="5">
         <v>46085</v>
@@ -4646,7 +4633,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B55" s="8">
         <v>46065.86638931713</v>
@@ -4658,16 +4645,16 @@
         <v>46167.597926319446</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I55" s="8">
         <v>46094</v>
@@ -4685,13 +4672,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q55" s="8">
         <v>46094</v>
@@ -4711,7 +4698,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B56" s="5">
         <v>46065.86638487269</v>
@@ -4723,16 +4710,16 @@
         <v>46167.59797377315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -4750,13 +4737,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q56" s="5">
         <v>46125</v>
@@ -4776,7 +4763,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B57" s="8">
         <v>46065.86638528935</v>
@@ -4786,7 +4773,7 @@
         <v>46212.6289187963</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4810,7 +4797,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4823,7 +4810,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46065.866385601854</v>
@@ -4835,16 +4822,16 @@
         <v>46198.824139675926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I58" s="5">
         <v>46147</v>
@@ -4862,13 +4849,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q58" s="5">
         <v>46147</v>
@@ -4888,7 +4875,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B59" s="8">
         <v>46065.86638590277</v>
@@ -4900,16 +4887,16 @@
         <v>46210.611941863426</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I59" s="8">
         <v>46083</v>
@@ -4927,13 +4914,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Q59" s="8">
         <v>46083</v>
@@ -4953,7 +4940,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46065.86638623843</v>
@@ -4965,16 +4952,16 @@
         <v>46198.82561377315</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I60" s="5">
         <v>46162</v>
@@ -4992,13 +4979,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q60" s="5">
         <v>46162</v>
@@ -5018,7 +5005,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B61" s="8">
         <v>46065.86638653935</v>
@@ -5034,10 +5021,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I61" s="8">
         <v>46128</v>
@@ -5055,13 +5042,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Q61" s="8">
         <v>46128</v>
@@ -5081,7 +5068,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5">
         <v>46065.866386828704</v>
@@ -5093,16 +5080,16 @@
         <v>46143.17235355324</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I62" s="5">
         <v>46141</v>
@@ -5120,13 +5107,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Q62" s="5">
         <v>46141</v>
@@ -5146,7 +5133,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B63" s="8">
         <v>46065.8663871412</v>
@@ -5158,7 +5145,7 @@
         <v>46213.50833928241</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5182,7 +5169,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5199,7 +5186,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
         <v>46065.86638744213</v>
@@ -5211,17 +5198,15 @@
         <v>46195.86652894676</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H64" s="6"/>
       <c r="I64" s="5">
         <v>46127</v>
       </c>
@@ -5238,13 +5223,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Q64" s="5">
         <v>46127</v>
@@ -5264,7 +5249,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B65" s="8">
         <v>46065.86638777777</v>
@@ -5276,17 +5261,15 @@
         <v>46198.82561393519</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H65" s="9"/>
       <c r="I65" s="8">
         <v>46164</v>
       </c>
@@ -5303,13 +5286,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q65" s="8">
         <v>46164</v>
@@ -5329,7 +5312,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46065.86638519676</v>
@@ -5341,17 +5324,15 @@
         <v>46198.82414078704</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H66" s="6"/>
       <c r="I66" s="5">
         <v>46149</v>
       </c>
@@ -5368,13 +5349,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q66" s="5">
         <v>46149</v>
@@ -5394,7 +5375,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B67" s="8">
         <v>46065.866385601854</v>
@@ -5406,17 +5387,15 @@
         <v>46213.508331516205</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H67" s="9"/>
       <c r="I67" s="8">
         <v>46153</v>
       </c>
@@ -5433,13 +5412,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q67" s="8">
         <v>46153</v>
@@ -5459,7 +5438,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B68" s="5">
         <v>46065.866385960646</v>
@@ -5471,17 +5450,15 @@
         <v>46197.60726340278</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H68" s="6"/>
       <c r="I68" s="5">
         <v>46146</v>
       </c>
@@ -5498,13 +5475,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q68" s="5">
         <v>46146</v>
@@ -5524,7 +5501,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B69" s="8">
         <v>46065.86638626158</v>
@@ -5534,17 +5511,15 @@
         <v>46213.508337974534</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H69" s="9"/>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
         <v>46168</v>
@@ -5559,13 +5534,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q69" s="8">
         <v>46168</v>
@@ -5585,7 +5560,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B70" s="5">
         <v>46065.8663865625</v>
@@ -5595,17 +5570,15 @@
         <v>46212.6283765625</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H70" s="6"/>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
         <v>46170</v>
@@ -5620,13 +5593,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="Q70" s="5">
         <v>46170</v>
@@ -5646,7 +5619,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B71" s="8">
         <v>46065.866386863425</v>
@@ -5656,7 +5629,7 @@
         <v>46090.7553162963</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5680,7 +5653,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5693,7 +5666,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B72" s="5">
         <v>46065.8663871875</v>
@@ -5703,16 +5676,16 @@
         <v>46212.62862773148</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5728,13 +5701,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q72" s="5">
         <v>46171</v>
@@ -5754,7 +5727,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B73" s="8">
         <v>46065.86638747685</v>
@@ -5764,17 +5737,15 @@
         <v>46212.62856337963</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H73" s="9"/>
       <c r="I73" s="8">
         <v>46174</v>
       </c>
@@ -5791,13 +5762,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q73" s="8">
         <v>46174</v>
@@ -5817,7 +5788,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
         <v>46065.866387766204</v>
@@ -5827,16 +5798,16 @@
         <v>46212.62864408565</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5852,13 +5823,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Q74" s="5">
         <v>46177</v>
@@ -5878,7 +5849,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B75" s="8">
         <v>46065.8663881713</v>
@@ -5888,16 +5859,16 @@
         <v>46212.62866971065</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5913,13 +5884,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q75" s="8">
         <v>46147</v>
@@ -5939,7 +5910,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B76" s="5">
         <v>46065.866384340276</v>
@@ -5949,7 +5920,7 @@
         <v>46090.755315567134</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5973,7 +5944,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5986,7 +5957,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B77" s="8">
         <v>46065.866385138885</v>
@@ -5996,16 +5967,16 @@
         <v>46190.20534189815</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I77" s="8">
         <v>46181</v>
@@ -6023,13 +5994,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q77" s="8">
         <v>46181</v>
@@ -6049,7 +6020,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B78" s="5">
         <v>46065.866385416666</v>
@@ -6059,16 +6030,16 @@
         <v>46190.205348206015</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I78" s="5">
         <v>46181</v>
@@ -6086,13 +6057,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>272</v>
       </c>
       <c r="Q78" s="5">
         <v>46181</v>
@@ -6112,7 +6083,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B79" s="8">
         <v>46090.75000248842</v>
@@ -6122,7 +6093,7 @@
         <v>46090.75636387731</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6146,7 +6117,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6160,12 +6131,12 @@
         <v>56</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B80" s="5">
         <v>46090.75028462963</v>
@@ -6175,7 +6146,7 @@
         <v>46190.205342534726</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6202,13 +6173,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="Q80" s="5">
         <v>46181</v>
@@ -6228,7 +6199,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B81" s="8">
         <v>46090.75057857639</v>
@@ -6238,7 +6209,7 @@
         <v>46199.19411842593</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6265,13 +6236,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="O81" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="O81" s="9" t="s">
-        <v>285</v>
-      </c>
       <c r="P81" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q81" s="8">
         <v>46190</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="287">
   <si>
     <t xml:space="preserve">50001497 - XEMORTIZ IMMSA STA. BBR  </t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
@@ -2611,7 +2614,7 @@
         <v>46113.5602749074</v>
       </c>
       <c r="D22" s="5">
-        <v>46113.56027699074</v>
+        <v>46223.81276079861</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2620,9 +2623,11 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="I22" s="5">
         <v>46017</v>
       </c>
@@ -2645,7 +2650,7 @@
         <v>64</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="5">
         <v>46017</v>
@@ -2665,7 +2670,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="8">
         <v>46065.86638537037</v>
@@ -2677,7 +2682,7 @@
         <v>46114.52306825231</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2710,7 +2715,7 @@
         <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="8">
         <v>46017</v>
@@ -2730,7 +2735,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46065.86638577546</v>
@@ -2739,18 +2744,20 @@
         <v>46107.72465984954</v>
       </c>
       <c r="D24" s="5">
-        <v>46107.724677314814</v>
+        <v>46223.812757314816</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="I24" s="5">
         <v>46017</v>
       </c>
@@ -2773,7 +2780,7 @@
         <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="5">
         <v>46017</v>
@@ -2793,7 +2800,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B25" s="8">
         <v>46065.86638607639</v>
@@ -2803,7 +2810,7 @@
         <v>46174.653070949076</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2827,7 +2834,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2842,7 +2849,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5">
         <v>46065.86638636574</v>
@@ -2854,16 +2861,16 @@
         <v>46155.87591685185</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I26" s="5">
         <v>46030</v>
@@ -2881,13 +2888,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q26" s="5">
         <v>46030</v>
@@ -2907,7 +2914,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B27" s="8">
         <v>46065.866386678244</v>
@@ -2919,16 +2926,16 @@
         <v>46097.553490011574</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I27" s="8">
         <v>46030</v>
@@ -2946,13 +2953,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2963,12 +2970,12 @@
         <v>56</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>46065.866386967595</v>
@@ -2980,16 +2987,16 @@
         <v>46155.87588597222</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I28" s="5">
         <v>46034</v>
@@ -3007,13 +3014,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3024,12 +3031,12 @@
         <v>56</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B29" s="8">
         <v>46065.866387256945</v>
@@ -3041,16 +3048,16 @@
         <v>46128.18276325232</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I29" s="8">
         <v>46021</v>
@@ -3068,13 +3075,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q29" s="8">
         <v>46021</v>
@@ -3094,7 +3101,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B30" s="5">
         <v>46065.86638756945</v>
@@ -3106,16 +3113,16 @@
         <v>46097.55455702546</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" s="5">
         <v>46021</v>
@@ -3133,13 +3140,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3150,12 +3157,12 @@
         <v>56</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B31" s="8">
         <v>46065.86638787037</v>
@@ -3167,16 +3174,16 @@
         <v>46122.64508055555</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I31" s="8">
         <v>46030</v>
@@ -3194,13 +3201,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3211,12 +3218,12 @@
         <v>56</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" s="5">
         <v>46065.8663881713</v>
@@ -3228,16 +3235,16 @@
         <v>46155.89158689815</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I32" s="5">
         <v>46030</v>
@@ -3255,13 +3262,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q32" s="5">
         <v>46030</v>
@@ -3281,7 +3288,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B33" s="8">
         <v>46065.86638436343</v>
@@ -3293,16 +3300,16 @@
         <v>46139.79497809028</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I33" s="8">
         <v>46030</v>
@@ -3320,13 +3327,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>87</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3337,12 +3344,12 @@
         <v>56</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46065.86638475694</v>
@@ -3354,16 +3361,16 @@
         <v>46155.89155403935</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I34" s="5">
         <v>46034</v>
@@ -3381,13 +3388,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3398,12 +3405,12 @@
         <v>56</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46065.866385057874</v>
@@ -3415,16 +3422,16 @@
         <v>46174.65306150463</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I35" s="8">
         <v>46013</v>
@@ -3442,13 +3449,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q35" s="8">
         <v>46013</v>
@@ -3468,7 +3475,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46065.866385347224</v>
@@ -3480,16 +3487,16 @@
         <v>46169.84157347222</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I36" s="5">
         <v>46013</v>
@@ -3507,13 +3514,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3524,12 +3531,12 @@
         <v>56</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46065.866385636575</v>
@@ -3541,16 +3548,16 @@
         <v>46174.652992372685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I37" s="8">
         <v>46036</v>
@@ -3568,13 +3575,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3585,12 +3592,12 @@
         <v>56</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46065.8663859375</v>
@@ -3602,16 +3609,16 @@
         <v>46174.653037488424</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I38" s="5">
         <v>46036</v>
@@ -3629,13 +3636,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3646,12 +3653,12 @@
         <v>56</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46065.866386215275</v>
@@ -3663,16 +3670,16 @@
         <v>46118.83674979166</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I39" s="8">
         <v>46030</v>
@@ -3690,13 +3697,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q39" s="8">
         <v>46030</v>
@@ -3716,7 +3723,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46065.86638649306</v>
@@ -3728,16 +3735,16 @@
         <v>46118.83650899306</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I40" s="5">
         <v>46030</v>
@@ -3755,13 +3762,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3772,12 +3779,12 @@
         <v>56</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46065.86638677084</v>
@@ -3789,16 +3796,16 @@
         <v>46118.836724988425</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I41" s="8">
         <v>46050</v>
@@ -3816,13 +3823,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3833,12 +3840,12 @@
         <v>56</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46065.86638704861</v>
@@ -3850,16 +3857,16 @@
         <v>46133.19587135417</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I42" s="5">
         <v>46030</v>
@@ -3877,13 +3884,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q42" s="5">
         <v>46030</v>
@@ -3898,12 +3905,12 @@
         <v>31</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
         <v>46065.86638668981</v>
@@ -3915,16 +3922,16 @@
         <v>46118.83885034722</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I43" s="8">
         <v>46030</v>
@@ -3942,13 +3949,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3959,12 +3966,12 @@
         <v>56</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46065.86638707176</v>
@@ -3976,16 +3983,16 @@
         <v>46118.83889917824</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I44" s="5">
         <v>46059</v>
@@ -4003,13 +4010,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4020,12 +4027,12 @@
         <v>56</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46065.866387372684</v>
@@ -4035,7 +4042,7 @@
         <v>46107.72587710648</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4059,7 +4066,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4074,7 +4081,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46070.744155486114</v>
@@ -4086,16 +4093,16 @@
         <v>46107.725811412034</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I46" s="5">
         <v>46017</v>
@@ -4113,13 +4120,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q46" s="5">
         <v>46017</v>
@@ -4139,7 +4146,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46065.86638765046</v>
@@ -4151,16 +4158,16 @@
         <v>46174.653052037036</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I47" s="8">
         <v>46076</v>
@@ -4178,13 +4185,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q47" s="8">
         <v>46076</v>
@@ -4204,7 +4211,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46090.74964866898</v>
@@ -4216,16 +4223,16 @@
         <v>46107.72595083334</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I48" s="5">
         <v>46083</v>
@@ -4243,13 +4250,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q48" s="5">
         <v>46083</v>
@@ -4269,7 +4276,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B49" s="8">
         <v>46090.74982369213</v>
@@ -4279,16 +4286,16 @@
         <v>46170.18363959491</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I49" s="8">
         <v>46169</v>
@@ -4306,13 +4313,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q49" s="8">
         <v>46169</v>
@@ -4332,7 +4339,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46065.866387939815</v>
@@ -4344,7 +4351,7 @@
         <v>46127.63560765046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4368,7 +4375,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4385,7 +4392,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46065.86638821759</v>
@@ -4397,16 +4404,16 @@
         <v>46122.64298887731</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I51" s="8">
         <v>46079</v>
@@ -4424,13 +4431,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="8">
         <v>46079</v>
@@ -4450,7 +4457,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46065.86638849537</v>
@@ -4462,16 +4469,16 @@
         <v>46127.63559171296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I52" s="5">
         <v>46083</v>
@@ -4489,13 +4496,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="5">
         <v>46083</v>
@@ -4515,7 +4522,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B53" s="8">
         <v>46065.86638876157</v>
@@ -4527,7 +4534,7 @@
         <v>46167.59798559028</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4551,7 +4558,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4568,7 +4575,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46065.8663890162</v>
@@ -4580,16 +4587,16 @@
         <v>46167.5450264699</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I54" s="5">
         <v>46085</v>
@@ -4607,13 +4614,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q54" s="5">
         <v>46085</v>
@@ -4633,7 +4640,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B55" s="8">
         <v>46065.86638931713</v>
@@ -4645,16 +4652,16 @@
         <v>46167.597926319446</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I55" s="8">
         <v>46094</v>
@@ -4672,13 +4679,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q55" s="8">
         <v>46094</v>
@@ -4698,7 +4705,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
         <v>46065.86638487269</v>
@@ -4710,16 +4717,16 @@
         <v>46167.59797377315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -4737,13 +4744,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q56" s="5">
         <v>46125</v>
@@ -4763,7 +4770,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B57" s="8">
         <v>46065.86638528935</v>
@@ -4773,7 +4780,7 @@
         <v>46212.6289187963</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4797,7 +4804,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4810,7 +4817,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B58" s="5">
         <v>46065.866385601854</v>
@@ -4822,16 +4829,16 @@
         <v>46198.824139675926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I58" s="5">
         <v>46147</v>
@@ -4849,13 +4856,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q58" s="5">
         <v>46147</v>
@@ -4875,7 +4882,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B59" s="8">
         <v>46065.86638590277</v>
@@ -4887,16 +4894,16 @@
         <v>46210.611941863426</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I59" s="8">
         <v>46083</v>
@@ -4914,13 +4921,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q59" s="8">
         <v>46083</v>
@@ -4940,7 +4947,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46065.86638623843</v>
@@ -4952,16 +4959,16 @@
         <v>46198.82561377315</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I60" s="5">
         <v>46162</v>
@@ -4979,13 +4986,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q60" s="5">
         <v>46162</v>
@@ -5005,7 +5012,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B61" s="8">
         <v>46065.86638653935</v>
@@ -5021,10 +5028,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I61" s="8">
         <v>46128</v>
@@ -5042,13 +5049,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="8">
         <v>46128</v>
@@ -5068,7 +5075,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46065.866386828704</v>
@@ -5080,16 +5087,16 @@
         <v>46143.17235355324</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I62" s="5">
         <v>46141</v>
@@ -5107,13 +5114,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q62" s="5">
         <v>46141</v>
@@ -5133,7 +5140,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B63" s="8">
         <v>46065.8663871412</v>
@@ -5145,7 +5152,7 @@
         <v>46213.50833928241</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5169,7 +5176,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5186,7 +5193,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B64" s="5">
         <v>46065.86638744213</v>
@@ -5195,18 +5202,20 @@
         <v>46195.866510844906</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.86652894676</v>
+        <v>46223.812908252316</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="I64" s="5">
         <v>46127</v>
       </c>
@@ -5223,13 +5232,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q64" s="5">
         <v>46127</v>
@@ -5249,7 +5258,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B65" s="8">
         <v>46065.86638777777</v>
@@ -5258,18 +5267,20 @@
         <v>46197.50371587963</v>
       </c>
       <c r="D65" s="8">
-        <v>46198.82561393519</v>
+        <v>46223.81290435186</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="I65" s="8">
         <v>46164</v>
       </c>
@@ -5286,13 +5297,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q65" s="8">
         <v>46164</v>
@@ -5312,7 +5323,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46065.86638519676</v>
@@ -5321,18 +5332,20 @@
         <v>46197.50377947917</v>
       </c>
       <c r="D66" s="5">
-        <v>46198.82414078704</v>
+        <v>46223.81290034722</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H66" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="I66" s="5">
         <v>46149</v>
       </c>
@@ -5349,13 +5362,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q66" s="5">
         <v>46149</v>
@@ -5375,7 +5388,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B67" s="8">
         <v>46065.866385601854</v>
@@ -5384,18 +5397,20 @@
         <v>46213.50832861111</v>
       </c>
       <c r="D67" s="8">
-        <v>46213.508331516205</v>
+        <v>46223.812896539355</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="I67" s="8">
         <v>46153</v>
       </c>
@@ -5412,13 +5427,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q67" s="8">
         <v>46153</v>
@@ -5438,7 +5453,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B68" s="5">
         <v>46065.866385960646</v>
@@ -5447,18 +5462,20 @@
         <v>46197.607128483796</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.60726340278</v>
+        <v>46223.81289273148</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="I68" s="5">
         <v>46146</v>
       </c>
@@ -5475,13 +5492,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="5">
         <v>46146</v>
@@ -5501,25 +5518,27 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B69" s="8">
         <v>46065.86638626158</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46213.508337974534</v>
+        <v>46223.81288570602</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H69" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
         <v>46168</v>
@@ -5534,13 +5553,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q69" s="8">
         <v>46168</v>
@@ -5560,25 +5579,27 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B70" s="5">
         <v>46065.8663865625</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46212.6283765625</v>
+        <v>46223.812885127314</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H70" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
         <v>46170</v>
@@ -5593,13 +5614,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q70" s="5">
         <v>46170</v>
@@ -5619,7 +5640,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B71" s="8">
         <v>46065.866386863425</v>
@@ -5629,7 +5650,7 @@
         <v>46090.7553162963</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5653,7 +5674,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5666,7 +5687,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B72" s="5">
         <v>46065.8663871875</v>
@@ -5676,16 +5697,16 @@
         <v>46212.62862773148</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5701,13 +5722,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q72" s="5">
         <v>46171</v>
@@ -5727,25 +5748,27 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B73" s="8">
         <v>46065.86638747685</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46212.62856337963</v>
+        <v>46223.81293800926</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="I73" s="8">
         <v>46174</v>
       </c>
@@ -5762,13 +5785,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q73" s="8">
         <v>46174</v>
@@ -5788,7 +5811,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B74" s="5">
         <v>46065.866387766204</v>
@@ -5798,16 +5821,16 @@
         <v>46212.62864408565</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5823,13 +5846,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q74" s="5">
         <v>46177</v>
@@ -5849,7 +5872,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B75" s="8">
         <v>46065.8663881713</v>
@@ -5859,16 +5882,16 @@
         <v>46212.62866971065</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5884,13 +5907,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q75" s="8">
         <v>46147</v>
@@ -5910,7 +5933,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B76" s="5">
         <v>46065.866384340276</v>
@@ -5920,7 +5943,7 @@
         <v>46090.755315567134</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5944,7 +5967,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5957,7 +5980,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B77" s="8">
         <v>46065.866385138885</v>
@@ -5967,16 +5990,16 @@
         <v>46190.20534189815</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I77" s="8">
         <v>46181</v>
@@ -5994,13 +6017,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q77" s="8">
         <v>46181</v>
@@ -6020,7 +6043,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B78" s="5">
         <v>46065.866385416666</v>
@@ -6030,16 +6053,16 @@
         <v>46190.205348206015</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I78" s="5">
         <v>46181</v>
@@ -6057,13 +6080,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q78" s="5">
         <v>46181</v>
@@ -6083,7 +6106,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B79" s="8">
         <v>46090.75000248842</v>
@@ -6093,7 +6116,7 @@
         <v>46090.75636387731</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6117,7 +6140,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6131,12 +6154,12 @@
         <v>56</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B80" s="5">
         <v>46090.75028462963</v>
@@ -6146,7 +6169,7 @@
         <v>46190.205342534726</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6173,13 +6196,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q80" s="5">
         <v>46181</v>
@@ -6199,7 +6222,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B81" s="8">
         <v>46090.75057857639</v>
@@ -6209,7 +6232,7 @@
         <v>46199.19411842593</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6236,13 +6259,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q81" s="8">
         <v>46190</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="288">
   <si>
     <t xml:space="preserve">50001497 - XEMORTIZ IMMSA STA. BBR  </t>
   </si>
@@ -178,7 +178,7 @@
     <t xml:space="preserve"> 4197-4198 Recepcion Tableros</t>
   </si>
   <si>
-    <t>Ingenieria de servicio:,ot 4196 - 4197-4198 Embalaje</t>
+    <t>Ingenieria de servicio:,ot 4196 - 4197-4198 Palatizado y  Embalaje</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -277,6 +277,9 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
     <t>nespinoza@zitron.com</t>
   </si>
   <si>
@@ -535,7 +538,7 @@
     <t>Check Planos</t>
   </si>
   <si>
-    <t>Armado FABRICACIÓN EXTERNA ,Control de calidad Armado,Montaje motor,Montaje Alabe,ot 4196 Montaje Rodete,Montaje sensores y accesorios</t>
+    <t>Armado FABRICACIÓN EXTERNA ,Control de calidad Armado,Montaje motor,Montaje Alabe,ot 4196 Montaje Rodete,ot 4196  accesorios</t>
   </si>
   <si>
     <t>1213575386156441</t>
@@ -682,7 +685,7 @@
     <t>Recepcion sensores y accesorios</t>
   </si>
   <si>
-    <t>Bodega:,Montaje sensores y accesorios</t>
+    <t>Bodega:,ot 4196  accesorios</t>
   </si>
   <si>
     <t>1213249277753006</t>
@@ -691,7 +694,7 @@
     <t>Montaje:</t>
   </si>
   <si>
-    <t>Revestimiento,Montaje motor,Montaje Alabe,ot 4196 Montaje Rodete,Montaje sensores y accesorios,ot 4196 Pruebas FAT,ot 4196 RE-PINTADO</t>
+    <t>Revestimiento,Montaje motor,Montaje Alabe,ot 4196 Montaje Rodete,ot 4196  accesorios,ot 4196 Pruebas FAT,ot 4196 RE-PINTADO</t>
   </si>
   <si>
     <t>1213249277753007</t>
@@ -739,7 +742,7 @@
     <t>1213249277753011</t>
   </si>
   <si>
-    <t>Montaje sensores y accesorios</t>
+    <t>ot 4196  accesorios</t>
   </si>
   <si>
     <t>Recepcion sensores y accesorios,Check Planos</t>
@@ -748,7 +751,7 @@
     <t>1213249277753012</t>
   </si>
   <si>
-    <t>Montaje motor,Montaje Alabe,ot 4196 Montaje Rodete,Montaje sensores y accesorios</t>
+    <t>Montaje motor,Montaje Alabe,ot 4196 Montaje Rodete,ot 4196  accesorios</t>
   </si>
   <si>
     <t>Montaje:,Check pruebas FAT</t>
@@ -766,7 +769,7 @@
     <t>Logistica:</t>
   </si>
   <si>
-    <t>ot 4196 - 4197-4198 Coordinacion Entrega con Cliente,ot 4196 - 4197-4198 Embalaje,ot 4196 - 4197-4198 PACKING LIST,ot 4196 - 4197-4198 Despacho</t>
+    <t>ot 4196 - 4197-4198 Coordinacion Entrega con Cliente,ot 4196 - 4197-4198 Palatizado y  Embalaje,ot 4196 - 4197-4198 PACKING LIST,ot 4196 - 4197-4198 Despacho</t>
   </si>
   <si>
     <t>1213249277753015</t>
@@ -781,13 +784,13 @@
     <t>kpinto@zitron.com</t>
   </si>
   <si>
-    <t>ot 4196 - 4197-4198 Embalaje,Logistica:</t>
+    <t>ot 4196 - 4197-4198 Palatizado y  Embalaje,Logistica:</t>
   </si>
   <si>
     <t>1213249277753016</t>
   </si>
   <si>
-    <t>ot 4196 - 4197-4198 Embalaje</t>
+    <t>ot 4196 - 4197-4198 Palatizado y  Embalaje</t>
   </si>
   <si>
     <t>ot 4196 - 4197-4198 Coordinacion Entrega con Cliente,Revision tableros pruebas</t>
@@ -2626,7 +2629,7 @@
         <v>88</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I22" s="5">
         <v>46017</v>
@@ -2650,7 +2653,7 @@
         <v>64</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46017</v>
@@ -2670,7 +2673,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46065.86638537037</v>
@@ -2682,7 +2685,7 @@
         <v>46114.52306825231</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2715,7 +2718,7 @@
         <v>67</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="8">
         <v>46017</v>
@@ -2735,7 +2738,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46065.86638577546</v>
@@ -2747,7 +2750,7 @@
         <v>46223.812757314816</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2756,7 +2759,7 @@
         <v>88</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I24" s="5">
         <v>46017</v>
@@ -2780,7 +2783,7 @@
         <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="5">
         <v>46017</v>
@@ -2800,7 +2803,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" s="8">
         <v>46065.86638607639</v>
@@ -2810,7 +2813,7 @@
         <v>46174.653070949076</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>25</v>
@@ -2834,7 +2837,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>26</v>
@@ -2849,7 +2852,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5">
         <v>46065.86638636574</v>
@@ -2861,16 +2864,16 @@
         <v>46155.87591685185</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I26" s="5">
         <v>46030</v>
@@ -2888,13 +2891,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="5">
         <v>46030</v>
@@ -2914,7 +2917,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" s="8">
         <v>46065.866386678244</v>
@@ -2926,16 +2929,16 @@
         <v>46097.553490011574</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I27" s="8">
         <v>46030</v>
@@ -2953,13 +2956,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2970,12 +2973,12 @@
         <v>56</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46065.866386967595</v>
@@ -2987,16 +2990,16 @@
         <v>46155.87588597222</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I28" s="5">
         <v>46034</v>
@@ -3014,13 +3017,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3031,12 +3034,12 @@
         <v>56</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="8">
         <v>46065.866387256945</v>
@@ -3048,16 +3051,16 @@
         <v>46128.18276325232</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I29" s="8">
         <v>46021</v>
@@ -3075,13 +3078,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q29" s="8">
         <v>46021</v>
@@ -3101,7 +3104,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46065.86638756945</v>
@@ -3113,16 +3116,16 @@
         <v>46097.55455702546</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I30" s="5">
         <v>46021</v>
@@ -3140,13 +3143,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3157,12 +3160,12 @@
         <v>56</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46065.86638787037</v>
@@ -3174,16 +3177,16 @@
         <v>46122.64508055555</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I31" s="8">
         <v>46030</v>
@@ -3201,13 +3204,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3218,12 +3221,12 @@
         <v>56</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46065.8663881713</v>
@@ -3235,16 +3238,16 @@
         <v>46155.89158689815</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I32" s="5">
         <v>46030</v>
@@ -3262,13 +3265,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q32" s="5">
         <v>46030</v>
@@ -3288,7 +3291,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B33" s="8">
         <v>46065.86638436343</v>
@@ -3300,16 +3303,16 @@
         <v>46139.79497809028</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I33" s="8">
         <v>46030</v>
@@ -3327,13 +3330,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>87</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3344,12 +3347,12 @@
         <v>56</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46065.86638475694</v>
@@ -3361,16 +3364,16 @@
         <v>46155.89155403935</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I34" s="5">
         <v>46034</v>
@@ -3388,13 +3391,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3405,12 +3408,12 @@
         <v>56</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46065.866385057874</v>
@@ -3422,16 +3425,16 @@
         <v>46174.65306150463</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I35" s="8">
         <v>46013</v>
@@ -3449,13 +3452,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q35" s="8">
         <v>46013</v>
@@ -3475,7 +3478,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46065.866385347224</v>
@@ -3487,16 +3490,16 @@
         <v>46169.84157347222</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I36" s="5">
         <v>46013</v>
@@ -3514,13 +3517,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3531,12 +3534,12 @@
         <v>56</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B37" s="8">
         <v>46065.866385636575</v>
@@ -3548,16 +3551,16 @@
         <v>46174.652992372685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I37" s="8">
         <v>46036</v>
@@ -3575,13 +3578,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3592,12 +3595,12 @@
         <v>56</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46065.8663859375</v>
@@ -3609,16 +3612,16 @@
         <v>46174.653037488424</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I38" s="5">
         <v>46036</v>
@@ -3636,13 +3639,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3653,12 +3656,12 @@
         <v>56</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B39" s="8">
         <v>46065.866386215275</v>
@@ -3670,16 +3673,16 @@
         <v>46118.83674979166</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I39" s="8">
         <v>46030</v>
@@ -3697,13 +3700,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q39" s="8">
         <v>46030</v>
@@ -3723,7 +3726,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46065.86638649306</v>
@@ -3735,16 +3738,16 @@
         <v>46118.83650899306</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I40" s="5">
         <v>46030</v>
@@ -3762,13 +3765,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3779,12 +3782,12 @@
         <v>56</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46065.86638677084</v>
@@ -3796,16 +3799,16 @@
         <v>46118.836724988425</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I41" s="8">
         <v>46050</v>
@@ -3823,13 +3826,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3840,12 +3843,12 @@
         <v>56</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46065.86638704861</v>
@@ -3857,16 +3860,16 @@
         <v>46133.19587135417</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I42" s="5">
         <v>46030</v>
@@ -3884,13 +3887,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q42" s="5">
         <v>46030</v>
@@ -3905,12 +3908,12 @@
         <v>31</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46065.86638668981</v>
@@ -3922,16 +3925,16 @@
         <v>46118.83885034722</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I43" s="8">
         <v>46030</v>
@@ -3949,13 +3952,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -3966,12 +3969,12 @@
         <v>56</v>
       </c>
       <c r="U43" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46065.86638707176</v>
@@ -3983,16 +3986,16 @@
         <v>46118.83889917824</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I44" s="5">
         <v>46059</v>
@@ -4010,13 +4013,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4027,12 +4030,12 @@
         <v>56</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="8">
         <v>46065.866387372684</v>
@@ -4042,7 +4045,7 @@
         <v>46107.72587710648</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>25</v>
@@ -4066,7 +4069,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4081,7 +4084,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46070.744155486114</v>
@@ -4093,16 +4096,16 @@
         <v>46107.725811412034</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I46" s="5">
         <v>46017</v>
@@ -4120,13 +4123,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q46" s="5">
         <v>46017</v>
@@ -4146,7 +4149,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46065.86638765046</v>
@@ -4158,16 +4161,16 @@
         <v>46174.653052037036</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I47" s="8">
         <v>46076</v>
@@ -4185,13 +4188,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q47" s="8">
         <v>46076</v>
@@ -4211,7 +4214,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46090.74964866898</v>
@@ -4223,16 +4226,16 @@
         <v>46107.72595083334</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I48" s="5">
         <v>46083</v>
@@ -4250,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q48" s="5">
         <v>46083</v>
@@ -4276,7 +4279,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>46090.74982369213</v>
@@ -4286,16 +4289,16 @@
         <v>46170.18363959491</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I49" s="8">
         <v>46169</v>
@@ -4313,13 +4316,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q49" s="8">
         <v>46169</v>
@@ -4339,7 +4342,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46065.866387939815</v>
@@ -4351,7 +4354,7 @@
         <v>46127.63560765046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4375,7 +4378,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4392,7 +4395,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46065.86638821759</v>
@@ -4404,16 +4407,16 @@
         <v>46122.64298887731</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I51" s="8">
         <v>46079</v>
@@ -4431,13 +4434,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="8">
         <v>46079</v>
@@ -4457,7 +4460,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46065.86638849537</v>
@@ -4469,16 +4472,16 @@
         <v>46127.63559171296</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I52" s="5">
         <v>46083</v>
@@ -4496,13 +4499,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="5">
         <v>46083</v>
@@ -4522,7 +4525,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46065.86638876157</v>
@@ -4534,7 +4537,7 @@
         <v>46167.59798559028</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4558,7 +4561,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4575,7 +4578,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46065.8663890162</v>
@@ -4587,16 +4590,16 @@
         <v>46167.5450264699</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I54" s="5">
         <v>46085</v>
@@ -4614,13 +4617,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46085</v>
@@ -4640,7 +4643,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B55" s="8">
         <v>46065.86638931713</v>
@@ -4652,16 +4655,16 @@
         <v>46167.597926319446</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I55" s="8">
         <v>46094</v>
@@ -4679,13 +4682,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q55" s="8">
         <v>46094</v>
@@ -4705,7 +4708,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46065.86638487269</v>
@@ -4717,16 +4720,16 @@
         <v>46167.59797377315</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I56" s="5">
         <v>46125</v>
@@ -4744,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q56" s="5">
         <v>46125</v>
@@ -4770,7 +4773,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B57" s="8">
         <v>46065.86638528935</v>
@@ -4780,7 +4783,7 @@
         <v>46212.6289187963</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4804,7 +4807,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4817,7 +4820,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B58" s="5">
         <v>46065.866385601854</v>
@@ -4829,16 +4832,16 @@
         <v>46198.824139675926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I58" s="5">
         <v>46147</v>
@@ -4856,13 +4859,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q58" s="5">
         <v>46147</v>
@@ -4882,7 +4885,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B59" s="8">
         <v>46065.86638590277</v>
@@ -4894,16 +4897,16 @@
         <v>46210.611941863426</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I59" s="8">
         <v>46083</v>
@@ -4921,13 +4924,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q59" s="8">
         <v>46083</v>
@@ -4947,7 +4950,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46065.86638623843</v>
@@ -4959,16 +4962,16 @@
         <v>46198.82561377315</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I60" s="5">
         <v>46162</v>
@@ -4986,13 +4989,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q60" s="5">
         <v>46162</v>
@@ -5012,7 +5015,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B61" s="8">
         <v>46065.86638653935</v>
@@ -5028,10 +5031,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I61" s="8">
         <v>46128</v>
@@ -5049,13 +5052,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q61" s="8">
         <v>46128</v>
@@ -5075,7 +5078,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B62" s="5">
         <v>46065.866386828704</v>
@@ -5087,16 +5090,16 @@
         <v>46143.17235355324</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I62" s="5">
         <v>46141</v>
@@ -5114,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q62" s="5">
         <v>46141</v>
@@ -5140,7 +5143,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B63" s="8">
         <v>46065.8663871412</v>
@@ -5149,10 +5152,10 @@
         <v>46197.59918284722</v>
       </c>
       <c r="D63" s="8">
-        <v>46213.50833928241</v>
+        <v>46225.81612420139</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>25</v>
@@ -5176,7 +5179,7 @@
         <v>26</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5193,7 +5196,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46065.86638744213</v>
@@ -5205,7 +5208,7 @@
         <v>46223.812908252316</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5214,7 +5217,7 @@
         <v>88</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I64" s="5">
         <v>46127</v>
@@ -5232,13 +5235,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q64" s="5">
         <v>46127</v>
@@ -5258,7 +5261,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B65" s="8">
         <v>46065.86638777777</v>
@@ -5267,10 +5270,10 @@
         <v>46197.50371587963</v>
       </c>
       <c r="D65" s="8">
-        <v>46223.81290435186</v>
+        <v>46225.815382824076</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5279,7 +5282,7 @@
         <v>88</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I65" s="8">
         <v>46164</v>
@@ -5297,13 +5300,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q65" s="8">
         <v>46164</v>
@@ -5314,8 +5317,8 @@
       <c r="S65" s="9">
         <v>1</v>
       </c>
-      <c r="T65" s="12" t="s">
-        <v>82</v>
+      <c r="T65" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U65" s="11" t="s">
         <v>32</v>
@@ -5323,7 +5326,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B66" s="5">
         <v>46065.86638519676</v>
@@ -5335,7 +5338,7 @@
         <v>46223.81290034722</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5344,7 +5347,7 @@
         <v>88</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I66" s="5">
         <v>46149</v>
@@ -5362,13 +5365,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="5">
         <v>46149</v>
@@ -5388,19 +5391,17 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B67" s="8">
         <v>46065.866385601854</v>
       </c>
-      <c r="C67" s="8">
-        <v>46213.50832861111</v>
-      </c>
+      <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46223.812896539355</v>
+        <v>46225.81594211806</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5409,7 +5410,7 @@
         <v>88</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I67" s="8">
         <v>46153</v>
@@ -5427,13 +5428,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q67" s="8">
         <v>46153</v>
@@ -5444,8 +5445,8 @@
       <c r="S67" s="9">
         <v>1</v>
       </c>
-      <c r="T67" s="10" t="s">
-        <v>31</v>
+      <c r="T67" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="U67" s="11" t="s">
         <v>32</v>
@@ -5453,19 +5454,17 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46065.866385960646</v>
       </c>
-      <c r="C68" s="5">
-        <v>46197.607128483796</v>
-      </c>
+      <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46223.81289273148</v>
+        <v>46225.815918078704</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5474,7 +5473,7 @@
         <v>88</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I68" s="5">
         <v>46146</v>
@@ -5492,13 +5491,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q68" s="5">
         <v>46146</v>
@@ -5509,8 +5508,8 @@
       <c r="S68" s="6">
         <v>1</v>
       </c>
-      <c r="T68" s="10" t="s">
-        <v>31</v>
+      <c r="T68" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="U68" s="11" t="s">
         <v>32</v>
@@ -5518,17 +5517,17 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B69" s="8">
         <v>46065.86638626158</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46223.81288570602</v>
+        <v>46225.81599849537</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5537,7 +5536,7 @@
         <v>88</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5553,13 +5552,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q69" s="8">
         <v>46168</v>
@@ -5570,8 +5569,8 @@
       <c r="S69" s="9">
         <v>0</v>
       </c>
-      <c r="T69" s="12" t="s">
-        <v>82</v>
+      <c r="T69" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="U69" s="11" t="s">
         <v>32</v>
@@ -5579,7 +5578,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B70" s="5">
         <v>46065.8663865625</v>
@@ -5589,7 +5588,7 @@
         <v>46223.812885127314</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5598,7 +5597,7 @@
         <v>88</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I70" s="6"/>
       <c r="J70" s="5">
@@ -5614,13 +5613,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q70" s="5">
         <v>46170</v>
@@ -5640,7 +5639,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B71" s="8">
         <v>46065.866386863425</v>
@@ -5650,7 +5649,7 @@
         <v>46090.7553162963</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5674,7 +5673,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -5687,7 +5686,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B72" s="5">
         <v>46065.8663871875</v>
@@ -5697,16 +5696,16 @@
         <v>46212.62862773148</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -5722,13 +5721,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q72" s="5">
         <v>46171</v>
@@ -5748,17 +5747,17 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B73" s="8">
         <v>46065.86638747685</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46223.81293800926</v>
+        <v>46225.81667247685</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5767,7 +5766,7 @@
         <v>88</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I73" s="8">
         <v>46174</v>
@@ -5785,13 +5784,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q73" s="8">
         <v>46174</v>
@@ -5811,7 +5810,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B74" s="5">
         <v>46065.866387766204</v>
@@ -5821,16 +5820,16 @@
         <v>46212.62864408565</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="5">
@@ -5846,13 +5845,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q74" s="5">
         <v>46177</v>
@@ -5872,7 +5871,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B75" s="8">
         <v>46065.8663881713</v>
@@ -5882,16 +5881,16 @@
         <v>46212.62866971065</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I75" s="9"/>
       <c r="J75" s="8">
@@ -5907,13 +5906,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q75" s="8">
         <v>46147</v>
@@ -5933,7 +5932,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B76" s="5">
         <v>46065.866384340276</v>
@@ -5943,7 +5942,7 @@
         <v>46090.755315567134</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -5967,7 +5966,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -5980,7 +5979,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B77" s="8">
         <v>46065.866385138885</v>
@@ -5990,16 +5989,16 @@
         <v>46190.20534189815</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I77" s="8">
         <v>46181</v>
@@ -6017,13 +6016,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q77" s="8">
         <v>46181</v>
@@ -6043,7 +6042,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B78" s="5">
         <v>46065.866385416666</v>
@@ -6053,16 +6052,16 @@
         <v>46190.205348206015</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I78" s="5">
         <v>46181</v>
@@ -6080,13 +6079,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="5">
         <v>46181</v>
@@ -6106,7 +6105,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B79" s="8">
         <v>46090.75000248842</v>
@@ -6116,7 +6115,7 @@
         <v>46090.75636387731</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>25</v>
@@ -6140,7 +6139,7 @@
         <v>26</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6154,12 +6153,12 @@
         <v>56</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B80" s="5">
         <v>46090.75028462963</v>
@@ -6169,7 +6168,7 @@
         <v>46190.205342534726</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6196,13 +6195,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q80" s="5">
         <v>46181</v>
@@ -6222,7 +6221,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B81" s="8">
         <v>46090.75057857639</v>
@@ -6232,7 +6231,7 @@
         <v>46199.19411842593</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6259,13 +6258,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q81" s="8">
         <v>46190</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -2810,7 +2810,7 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46174.653070949076</v>
+        <v>46229.28567442129</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>98</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -2808,9 +2808,11 @@
       <c r="B25" s="8">
         <v>46065.86638607639</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="8">
+        <v>46233.631018935186</v>
+      </c>
       <c r="D25" s="8">
-        <v>46229.28567442129</v>
+        <v>46233.63103746528</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>98</v>
@@ -2844,9 +2846,11 @@
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="12" t="s">
-        <v>82</v>
+      <c r="S25" s="9">
+        <v>1</v>
+      </c>
+      <c r="T25" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U25" s="9"/>
     </row>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -5156,7 +5156,7 @@
         <v>46197.59918284722</v>
       </c>
       <c r="D63" s="8">
-        <v>46225.81612420139</v>
+        <v>46237.55475265047</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>226</v>
@@ -5339,7 +5339,7 @@
         <v>46197.50377947917</v>
       </c>
       <c r="D66" s="5">
-        <v>46223.81290034722</v>
+        <v>46237.514292974534</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>236</v>
@@ -5386,8 +5386,8 @@
       <c r="S66" s="6">
         <v>1</v>
       </c>
-      <c r="T66" s="12" t="s">
-        <v>82</v>
+      <c r="T66" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>32</v>
@@ -5463,9 +5463,11 @@
       <c r="B68" s="5">
         <v>46065.866385960646</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46237.55474612268</v>
+      </c>
       <c r="D68" s="5">
-        <v>46225.815918078704</v>
+        <v>46237.554748298615</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>243</v>
@@ -5512,8 +5514,8 @@
       <c r="S68" s="6">
         <v>1</v>
       </c>
-      <c r="T68" s="12" t="s">
-        <v>82</v>
+      <c r="T68" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U68" s="11" t="s">
         <v>32</v>
@@ -5528,7 +5530,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46225.81599849537</v>
+        <v>46237.55475195602</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>180</v>
@@ -5758,7 +5760,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46225.81667247685</v>
+        <v>46237.514527974534</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>259</v>
@@ -5805,8 +5807,8 @@
       <c r="S73" s="9">
         <v>0</v>
       </c>
-      <c r="T73" s="11" t="s">
-        <v>56</v>
+      <c r="T73" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="U73" s="11" t="s">
         <v>32</v>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="280">
   <si>
     <t xml:space="preserve">50001497 - XEMORTIZ IMMSA STA. BBR  </t>
   </si>
@@ -820,7 +820,7 @@
     <t>ot 4196 - 4197-4198 Despacho</t>
   </si>
   <si>
-    <t>Costos,Gestion,Logistica:,Logistica:,instalación Componentes</t>
+    <t>Costos,Gestion,Logistica:,Logistica:</t>
   </si>
   <si>
     <t>1213249277753019</t>
@@ -851,30 +851,6 @@
   </si>
   <si>
     <t>Gestion</t>
-  </si>
-  <si>
-    <t>1213575386156442</t>
-  </si>
-  <si>
-    <t>Puesta en Marcha Servicios</t>
-  </si>
-  <si>
-    <t>instalación Componentes,Pruebas de instalación Componentes</t>
-  </si>
-  <si>
-    <t>1213575386156444</t>
-  </si>
-  <si>
-    <t>instalación Componentes</t>
-  </si>
-  <si>
-    <t>Pruebas de instalación Componentes,Puesta en Marcha Servicios</t>
-  </si>
-  <si>
-    <t>1213575386156448</t>
-  </si>
-  <si>
-    <t>Pruebas de instalación Componentes</t>
   </si>
 </sst>
 </file>
@@ -1398,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U81"/>
+  <dimension ref="A1:U78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5884,7 +5860,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46212.62866971065</v>
+        <v>46240.72161555555</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>
@@ -6106,185 +6082,6 @@
         <v>56</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="B79" s="8">
-        <v>46090.75000248842</v>
-      </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="8">
-        <v>46090.75636387731</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="9"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
-      <c r="K79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q79" s="9"/>
-      <c r="R79" s="9"/>
-      <c r="S79" s="9">
-        <v>0</v>
-      </c>
-      <c r="T79" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="U79" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B80" s="5">
-        <v>46090.75028462963</v>
-      </c>
-      <c r="C80" s="6"/>
-      <c r="D80" s="5">
-        <v>46190.205342534726</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G80" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I80" s="5">
-        <v>46181</v>
-      </c>
-      <c r="J80" s="5">
-        <v>46189</v>
-      </c>
-      <c r="K80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>46181</v>
-      </c>
-      <c r="R80" s="5">
-        <v>46189</v>
-      </c>
-      <c r="S80" s="6">
-        <v>0</v>
-      </c>
-      <c r="T80" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="U80" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B81" s="8">
-        <v>46090.75057857639</v>
-      </c>
-      <c r="C81" s="9"/>
-      <c r="D81" s="8">
-        <v>46199.19411842593</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I81" s="8">
-        <v>46190</v>
-      </c>
-      <c r="J81" s="8">
-        <v>46198</v>
-      </c>
-      <c r="K81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q81" s="8">
-        <v>46190</v>
-      </c>
-      <c r="R81" s="8">
-        <v>46198</v>
-      </c>
-      <c r="S81" s="9">
-        <v>0</v>
-      </c>
-      <c r="T81" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="U81" s="11" t="s">
         <v>32</v>
       </c>
     </row>

--- a/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
+++ b/data/50001497 - XEMORTIZ IMMSA STA BBR.xlsx
@@ -1967,7 +1967,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46212.62892070602</v>
+        <v>46246.741893645834</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
